--- a/templates/ERC000055/metadata_template_ERC000055.xlsx
+++ b/templates/ERC000055/metadata_template_ERC000055.xlsx
@@ -19,14 +19,14 @@
   <definedNames>
     <definedName name="drainageclassification">'cv_sample'!$CQ$1:$CQ$6</definedName>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$BT$1:$BT$289</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$BT$1:$BT$294</definedName>
     <definedName name="historytillage">'cv_sample'!$DK$1:$DK$9</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$87</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
     <definedName name="oxygenationstatusofsample">'cv_sample'!$AB$1:$AB$2</definedName>
-    <definedName name="platform">'cv_experiment'!$M$1:$M$17</definedName>
+    <definedName name="platform">'cv_experiment'!$M$1:$M$18</definedName>
     <definedName name="profileposition">'cv_sample'!$CV$1:$CV$5</definedName>
     <definedName name="relationshiptooxygen">'cv_sample'!$J$1:$J$7</definedName>
     <definedName name="sequencequalitycheck">'cv_sample'!$AW$1:$AW$3</definedName>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1031" uniqueCount="1023">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1038" uniqueCount="1030">
   <si>
     <t>alias</t>
   </si>
@@ -457,6 +457,9 @@
     <t>ELEMENT</t>
   </si>
   <si>
+    <t>AVITI</t>
+  </si>
+  <si>
     <t>ULTIMA</t>
   </si>
   <si>
@@ -547,6 +550,9 @@
     <t>AB SOLiD System 3.0</t>
   </si>
   <si>
+    <t>AVITI 24</t>
+  </si>
+  <si>
     <t>BGISEQ-50</t>
   </si>
   <si>
@@ -1039,13 +1045,13 @@
     <t>size-fraction lower threshold</t>
   </si>
   <si>
-    <t>(Optional) Refers to the mesh/pore size used to retain the sample. materials smaller than the size threshold are excluded from the sample (Units: µm)</t>
+    <t>(Optional) Refers to the mesh/pore size used to retain the sample. materials smaller than the size threshold are excluded from the sample (Units: nm)</t>
   </si>
   <si>
     <t>size-fraction upper threshold</t>
   </si>
   <si>
-    <t>(Optional) Refers to the mesh/pore size used to pre-filter/pre-sort the sample. materials larger than the size threshold are excluded from the sample (Units: µm)</t>
+    <t>(Optional) Refers to the mesh/pore size used to pre-filter/pre-sort the sample. materials larger than the size threshold are excluded from the sample (Units: nm)</t>
   </si>
   <si>
     <t>soil_taxonomic/FAO classification</t>
@@ -1696,9 +1702,6 @@
     <t>Dominican Republic</t>
   </si>
   <si>
-    <t>East Timor</t>
-  </si>
-  <si>
     <t>Ecuador</t>
   </si>
   <si>
@@ -1717,6 +1720,9 @@
     <t>Estonia</t>
   </si>
   <si>
+    <t>Eswatini</t>
+  </si>
+  <si>
     <t>Ethiopia</t>
   </si>
   <si>
@@ -1918,6 +1924,9 @@
     <t>Liechtenstein</t>
   </si>
   <si>
+    <t>Line Islands</t>
+  </si>
+  <si>
     <t>Lithuania</t>
   </si>
   <si>
@@ -1927,9 +1936,6 @@
     <t>Macau</t>
   </si>
   <si>
-    <t>Macedonia</t>
-  </si>
-  <si>
     <t>Madagascar</t>
   </si>
   <si>
@@ -1969,7 +1975,7 @@
     <t>Mexico</t>
   </si>
   <si>
-    <t>Micronesia</t>
+    <t>Micronesia, Federated States of</t>
   </si>
   <si>
     <t>Midway Islands</t>
@@ -2038,6 +2044,9 @@
     <t>North Korea</t>
   </si>
   <si>
+    <t>North Macedonia</t>
+  </si>
+  <si>
     <t>North Sea</t>
   </si>
   <si>
@@ -2113,6 +2122,9 @@
     <t>Rwanda</t>
   </si>
   <si>
+    <t>Saint Barthelemy</t>
+  </si>
+  <si>
     <t>Saint Helena</t>
   </si>
   <si>
@@ -2134,6 +2146,9 @@
     <t>San Marino</t>
   </si>
   <si>
+    <t>Saint Martin</t>
+  </si>
+  <si>
     <t>Sao Tome and Principe</t>
   </si>
   <si>
@@ -2179,6 +2194,9 @@
     <t>South Korea</t>
   </si>
   <si>
+    <t>South Sudan</t>
+  </si>
+  <si>
     <t>Southern Ocean</t>
   </si>
   <si>
@@ -2191,6 +2209,9 @@
     <t>Sri Lanka</t>
   </si>
   <si>
+    <t>State of Palestine</t>
+  </si>
+  <si>
     <t>Sudan</t>
   </si>
   <si>
@@ -2200,9 +2221,6 @@
     <t>Svalbard</t>
   </si>
   <si>
-    <t>Swaziland</t>
-  </si>
-  <si>
     <t>Sweden</t>
   </si>
   <si>
@@ -2227,6 +2245,9 @@
     <t>Thailand</t>
   </si>
   <si>
+    <t>Timor-Leste</t>
+  </si>
+  <si>
     <t>Togo</t>
   </si>
   <si>
@@ -2287,12 +2308,12 @@
     <t>Viet Nam</t>
   </si>
   <si>
+    <t>Wake Island</t>
+  </si>
+  <si>
     <t>Virgin Islands</t>
   </si>
   <si>
-    <t>Wake Island</t>
-  </si>
-  <si>
     <t>Wallis and Futuna</t>
   </si>
   <si>
@@ -2389,13 +2410,13 @@
     <t>host height</t>
   </si>
   <si>
-    <t>(Optional) The height of subject (Units: mm)</t>
+    <t>(Optional) The height of subject (Units: m)</t>
   </si>
   <si>
     <t>host length</t>
   </si>
   <si>
-    <t>(Optional) The length of subject (Units: mm)</t>
+    <t>(Optional) The length of subject (Units: m)</t>
   </si>
   <si>
     <t>host total mass</t>
@@ -2461,7 +2482,7 @@
     <t>humidity</t>
   </si>
   <si>
-    <t>(Recommended) Amount of water vapour in the air, at the time of sampling (Units: g/m3)</t>
+    <t>(Recommended) Amount of water vapour in the air, at the time of sampling (Units: %)</t>
   </si>
   <si>
     <t>current vegetation method</t>
@@ -2590,7 +2611,7 @@
     <t>total phosphate</t>
   </si>
   <si>
-    <t>(Recommended) Total amount or concentration of phosphate (Units: µmol/L)</t>
+    <t>(Recommended) Total amount or concentration of phosphate (Units: µg/L)</t>
   </si>
   <si>
     <t>total nitrogen concentration</t>
@@ -2713,7 +2734,7 @@
     <t>mean seasonal humidity</t>
   </si>
   <si>
-    <t>(Optional) Average humidity of the region throughout the growing season. (Units: g/m3)</t>
+    <t>(Optional) Average humidity of the region throughout the growing season. (Units: %)</t>
   </si>
   <si>
     <t>mean seasonal temperature</t>
@@ -2761,7 +2782,7 @@
     <t>host dry mass</t>
   </si>
   <si>
-    <t>(Optional) Measurement of dry mass (Units: mg)</t>
+    <t>(Optional) Measurement of dry mass (Units: kg)</t>
   </si>
   <si>
     <t>spike-in microbial strain</t>
@@ -2929,7 +2950,7 @@
     <t>sample volume or weight for DNA extraction</t>
   </si>
   <si>
-    <t>(Optional) Volume (ml) or mass (g) of total collected sample processed for dna extraction. note: total sample collected should be entered under the term 'sample size'. (Units: ng)</t>
+    <t>(Optional) Volume (ml) or mass (g) of total collected sample processed for dna extraction. note: total sample collected should be entered under the term 'sample size'. (Units: mL)</t>
   </si>
   <si>
     <t>nucleic acid extraction</t>
@@ -3043,7 +3064,7 @@
     <t>depth</t>
   </si>
   <si>
-    <t>(Recommended) The vertical distance below local surface, e.g. for sediment or soil samples depth is measured from sediment or soil surface, respectively. depth can be reported as an interval for subsurface samples. (Units: mm)</t>
+    <t>(Recommended) The vertical distance below local surface, e.g. for sediment or soil samples depth is measured from sediment or soil surface, respectively. depth can be reported as an interval for subsurface samples. (Units: m)</t>
   </si>
   <si>
     <t>environment adjacent to site</t>
@@ -3636,10 +3657,10 @@
         <v>124</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -3680,10 +3701,10 @@
         <v>125</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -3710,7 +3731,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N87"/>
+  <dimension ref="G1:N88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -3727,7 +3748,7 @@
         <v>126</v>
       </c>
       <c r="N1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="7:14">
@@ -3744,7 +3765,7 @@
         <v>127</v>
       </c>
       <c r="N2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="7:14">
@@ -3761,7 +3782,7 @@
         <v>128</v>
       </c>
       <c r="N3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="7:14">
@@ -3778,7 +3799,7 @@
         <v>129</v>
       </c>
       <c r="N4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="7:14">
@@ -3795,7 +3816,7 @@
         <v>130</v>
       </c>
       <c r="N5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="7:14">
@@ -3812,7 +3833,7 @@
         <v>131</v>
       </c>
       <c r="N6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="7:14">
@@ -3829,7 +3850,7 @@
         <v>132</v>
       </c>
       <c r="N7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="7:14">
@@ -3846,7 +3867,7 @@
         <v>133</v>
       </c>
       <c r="N8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="7:14">
@@ -3863,7 +3884,7 @@
         <v>134</v>
       </c>
       <c r="N9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="7:14">
@@ -3877,7 +3898,7 @@
         <v>135</v>
       </c>
       <c r="N10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="7:14">
@@ -3891,7 +3912,7 @@
         <v>136</v>
       </c>
       <c r="N11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="7:14">
@@ -3905,7 +3926,7 @@
         <v>137</v>
       </c>
       <c r="N12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="7:14">
@@ -3919,7 +3940,7 @@
         <v>138</v>
       </c>
       <c r="N13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="7:14">
@@ -3933,7 +3954,7 @@
         <v>139</v>
       </c>
       <c r="N14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="7:14">
@@ -3947,7 +3968,7 @@
         <v>140</v>
       </c>
       <c r="N15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" spans="7:14">
@@ -3961,7 +3982,7 @@
         <v>141</v>
       </c>
       <c r="N16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" spans="7:14">
@@ -3975,7 +3996,7 @@
         <v>142</v>
       </c>
       <c r="N17" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" spans="7:14">
@@ -3985,8 +4006,11 @@
       <c r="I18" t="s">
         <v>54</v>
       </c>
+      <c r="M18" t="s">
+        <v>143</v>
+      </c>
       <c r="N18" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19" spans="7:14">
@@ -3997,7 +4021,7 @@
         <v>105</v>
       </c>
       <c r="N19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="7:14">
@@ -4008,7 +4032,7 @@
         <v>106</v>
       </c>
       <c r="N20" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21" spans="7:14">
@@ -4019,7 +4043,7 @@
         <v>107</v>
       </c>
       <c r="N21" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22" spans="7:14">
@@ -4030,7 +4054,7 @@
         <v>108</v>
       </c>
       <c r="N22" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="7:14">
@@ -4041,7 +4065,7 @@
         <v>109</v>
       </c>
       <c r="N23" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24" spans="7:14">
@@ -4052,7 +4076,7 @@
         <v>110</v>
       </c>
       <c r="N24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="7:14">
@@ -4063,7 +4087,7 @@
         <v>111</v>
       </c>
       <c r="N25" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26" spans="7:14">
@@ -4074,7 +4098,7 @@
         <v>112</v>
       </c>
       <c r="N26" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="7:14">
@@ -4085,7 +4109,7 @@
         <v>113</v>
       </c>
       <c r="N27" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="7:14">
@@ -4096,7 +4120,7 @@
         <v>114</v>
       </c>
       <c r="N28" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="7:14">
@@ -4107,7 +4131,7 @@
         <v>115</v>
       </c>
       <c r="N29" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="7:14">
@@ -4118,7 +4142,7 @@
         <v>116</v>
       </c>
       <c r="N30" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="7:14">
@@ -4129,7 +4153,7 @@
         <v>117</v>
       </c>
       <c r="N31" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="7:14">
@@ -4137,7 +4161,7 @@
         <v>66</v>
       </c>
       <c r="N32" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" spans="7:14">
@@ -4145,7 +4169,7 @@
         <v>67</v>
       </c>
       <c r="N33" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34" spans="7:14">
@@ -4153,7 +4177,7 @@
         <v>68</v>
       </c>
       <c r="N34" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35" spans="7:14">
@@ -4161,7 +4185,7 @@
         <v>69</v>
       </c>
       <c r="N35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="7:14">
@@ -4169,7 +4193,7 @@
         <v>70</v>
       </c>
       <c r="N36" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37" spans="7:14">
@@ -4177,7 +4201,7 @@
         <v>71</v>
       </c>
       <c r="N37" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="38" spans="7:14">
@@ -4185,7 +4209,7 @@
         <v>72</v>
       </c>
       <c r="N38" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="39" spans="7:14">
@@ -4193,7 +4217,7 @@
         <v>73</v>
       </c>
       <c r="N39" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="40" spans="7:14">
@@ -4201,7 +4225,7 @@
         <v>74</v>
       </c>
       <c r="N40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="41" spans="7:14">
@@ -4209,236 +4233,241 @@
         <v>75</v>
       </c>
       <c r="N41" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42" spans="7:14">
       <c r="N42" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="43" spans="7:14">
       <c r="N43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" spans="7:14">
       <c r="N44" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="45" spans="7:14">
       <c r="N45" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="46" spans="7:14">
       <c r="N46" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="47" spans="7:14">
       <c r="N47" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="48" spans="7:14">
       <c r="N48" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="49" spans="14:14">
       <c r="N49" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="50" spans="14:14">
       <c r="N50" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="51" spans="14:14">
       <c r="N51" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="52" spans="14:14">
       <c r="N52" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="53" spans="14:14">
       <c r="N53" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="54" spans="14:14">
       <c r="N54" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="55" spans="14:14">
       <c r="N55" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="56" spans="14:14">
       <c r="N56" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="57" spans="14:14">
       <c r="N57" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="58" spans="14:14">
       <c r="N58" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="59" spans="14:14">
       <c r="N59" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="60" spans="14:14">
       <c r="N60" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="61" spans="14:14">
       <c r="N61" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="62" spans="14:14">
       <c r="N62" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="63" spans="14:14">
       <c r="N63" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="64" spans="14:14">
       <c r="N64" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="65" spans="14:14">
       <c r="N65" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="66" spans="14:14">
       <c r="N66" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="67" spans="14:14">
       <c r="N67" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="68" spans="14:14">
       <c r="N68" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="69" spans="14:14">
       <c r="N69" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="70" spans="14:14">
       <c r="N70" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="71" spans="14:14">
       <c r="N71" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="72" spans="14:14">
       <c r="N72" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="73" spans="14:14">
       <c r="N73" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="74" spans="14:14">
       <c r="N74" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="75" spans="14:14">
       <c r="N75" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="76" spans="14:14">
       <c r="N76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="77" spans="14:14">
       <c r="N77" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="78" spans="14:14">
       <c r="N78" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="79" spans="14:14">
       <c r="N79" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="80" spans="14:14">
       <c r="N80" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="81" spans="14:14">
       <c r="N81" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="82" spans="14:14">
       <c r="N82" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="83" spans="14:14">
       <c r="N83" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="84" spans="14:14">
       <c r="N84" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="85" spans="14:14">
       <c r="N85" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="86" spans="14:14">
       <c r="N86" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="87" spans="14:14">
       <c r="N87" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="88" spans="14:14">
+      <c r="N88" t="s">
         <v>117</v>
       </c>
     </row>
@@ -4460,27 +4489,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -4500,122 +4529,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -4639,1098 +4668,1098 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="BK1" s="1" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="BM1" s="1" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="BN1" s="1" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="BO1" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="BP1" s="1" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="BQ1" s="1" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="BS1" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="BT1" s="1" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="BU1" s="1" t="s">
-        <v>771</v>
+        <v>778</v>
       </c>
       <c r="BV1" s="1" t="s">
-        <v>773</v>
+        <v>780</v>
       </c>
       <c r="BW1" s="1" t="s">
-        <v>775</v>
+        <v>782</v>
       </c>
       <c r="BX1" s="1" t="s">
-        <v>777</v>
+        <v>784</v>
       </c>
       <c r="BY1" s="1" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="BZ1" s="1" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
       <c r="CA1" s="1" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="CB1" s="1" t="s">
-        <v>785</v>
+        <v>792</v>
       </c>
       <c r="CC1" s="1" t="s">
-        <v>787</v>
+        <v>794</v>
       </c>
       <c r="CD1" s="1" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
       <c r="CE1" s="1" t="s">
-        <v>791</v>
+        <v>798</v>
       </c>
       <c r="CF1" s="1" t="s">
-        <v>793</v>
+        <v>800</v>
       </c>
       <c r="CG1" s="1" t="s">
-        <v>795</v>
+        <v>802</v>
       </c>
       <c r="CH1" s="1" t="s">
-        <v>797</v>
+        <v>804</v>
       </c>
       <c r="CI1" s="1" t="s">
-        <v>799</v>
+        <v>806</v>
       </c>
       <c r="CJ1" s="1" t="s">
-        <v>801</v>
+        <v>808</v>
       </c>
       <c r="CK1" s="1" t="s">
-        <v>803</v>
+        <v>810</v>
       </c>
       <c r="CL1" s="1" t="s">
-        <v>805</v>
+        <v>812</v>
       </c>
       <c r="CM1" s="1" t="s">
-        <v>807</v>
+        <v>814</v>
       </c>
       <c r="CN1" s="1" t="s">
-        <v>809</v>
+        <v>816</v>
       </c>
       <c r="CO1" s="1" t="s">
-        <v>817</v>
+        <v>824</v>
       </c>
       <c r="CP1" s="1" t="s">
-        <v>819</v>
+        <v>826</v>
       </c>
       <c r="CQ1" s="1" t="s">
-        <v>827</v>
+        <v>834</v>
       </c>
       <c r="CR1" s="1" t="s">
-        <v>829</v>
+        <v>836</v>
       </c>
       <c r="CS1" s="1" t="s">
-        <v>831</v>
+        <v>838</v>
       </c>
       <c r="CT1" s="1" t="s">
-        <v>833</v>
+        <v>840</v>
       </c>
       <c r="CU1" s="1" t="s">
-        <v>835</v>
+        <v>842</v>
       </c>
       <c r="CV1" s="1" t="s">
-        <v>842</v>
+        <v>849</v>
       </c>
       <c r="CW1" s="1" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
       <c r="CX1" s="1" t="s">
-        <v>846</v>
+        <v>853</v>
       </c>
       <c r="CY1" s="1" t="s">
-        <v>848</v>
+        <v>855</v>
       </c>
       <c r="CZ1" s="1" t="s">
-        <v>850</v>
+        <v>857</v>
       </c>
       <c r="DA1" s="1" t="s">
-        <v>852</v>
+        <v>859</v>
       </c>
       <c r="DB1" s="1" t="s">
-        <v>854</v>
+        <v>861</v>
       </c>
       <c r="DC1" s="1" t="s">
-        <v>856</v>
+        <v>863</v>
       </c>
       <c r="DD1" s="1" t="s">
-        <v>858</v>
+        <v>865</v>
       </c>
       <c r="DE1" s="1" t="s">
-        <v>860</v>
+        <v>867</v>
       </c>
       <c r="DF1" s="1" t="s">
-        <v>862</v>
+        <v>869</v>
       </c>
       <c r="DG1" s="1" t="s">
-        <v>864</v>
+        <v>871</v>
       </c>
       <c r="DH1" s="1" t="s">
-        <v>866</v>
+        <v>873</v>
       </c>
       <c r="DI1" s="1" t="s">
-        <v>868</v>
+        <v>875</v>
       </c>
       <c r="DJ1" s="1" t="s">
-        <v>870</v>
+        <v>877</v>
       </c>
       <c r="DK1" s="1" t="s">
-        <v>881</v>
+        <v>888</v>
       </c>
       <c r="DL1" s="1" t="s">
-        <v>883</v>
+        <v>890</v>
       </c>
       <c r="DM1" s="1" t="s">
-        <v>885</v>
+        <v>892</v>
       </c>
       <c r="DN1" s="1" t="s">
-        <v>887</v>
+        <v>894</v>
       </c>
       <c r="DO1" s="1" t="s">
-        <v>889</v>
+        <v>896</v>
       </c>
       <c r="DP1" s="1" t="s">
-        <v>891</v>
+        <v>898</v>
       </c>
       <c r="DQ1" s="1" t="s">
-        <v>893</v>
+        <v>900</v>
       </c>
       <c r="DR1" s="1" t="s">
-        <v>895</v>
+        <v>902</v>
       </c>
       <c r="DS1" s="1" t="s">
-        <v>897</v>
+        <v>904</v>
       </c>
       <c r="DT1" s="1" t="s">
-        <v>899</v>
+        <v>906</v>
       </c>
       <c r="DU1" s="1" t="s">
-        <v>901</v>
+        <v>908</v>
       </c>
       <c r="DV1" s="1" t="s">
-        <v>903</v>
+        <v>910</v>
       </c>
       <c r="DW1" s="1" t="s">
-        <v>905</v>
+        <v>912</v>
       </c>
       <c r="DX1" s="1" t="s">
-        <v>907</v>
+        <v>914</v>
       </c>
       <c r="DY1" s="1" t="s">
-        <v>909</v>
+        <v>916</v>
       </c>
       <c r="DZ1" s="1" t="s">
-        <v>911</v>
+        <v>918</v>
       </c>
       <c r="EA1" s="1" t="s">
-        <v>913</v>
+        <v>920</v>
       </c>
       <c r="EB1" s="1" t="s">
-        <v>915</v>
+        <v>922</v>
       </c>
       <c r="EC1" s="1" t="s">
-        <v>917</v>
+        <v>924</v>
       </c>
       <c r="ED1" s="1" t="s">
-        <v>919</v>
+        <v>926</v>
       </c>
       <c r="EE1" s="1" t="s">
-        <v>921</v>
+        <v>928</v>
       </c>
       <c r="EF1" s="1" t="s">
-        <v>923</v>
+        <v>930</v>
       </c>
       <c r="EG1" s="1" t="s">
-        <v>925</v>
+        <v>932</v>
       </c>
       <c r="EH1" s="1" t="s">
-        <v>927</v>
+        <v>934</v>
       </c>
       <c r="EI1" s="1" t="s">
-        <v>929</v>
+        <v>936</v>
       </c>
       <c r="EJ1" s="1" t="s">
-        <v>931</v>
+        <v>938</v>
       </c>
       <c r="EK1" s="1" t="s">
-        <v>933</v>
+        <v>940</v>
       </c>
       <c r="EL1" s="1" t="s">
-        <v>935</v>
+        <v>942</v>
       </c>
       <c r="EM1" s="1" t="s">
-        <v>937</v>
+        <v>944</v>
       </c>
       <c r="EN1" s="1" t="s">
-        <v>939</v>
+        <v>946</v>
       </c>
       <c r="EO1" s="1" t="s">
-        <v>941</v>
+        <v>948</v>
       </c>
       <c r="EP1" s="1" t="s">
-        <v>943</v>
+        <v>950</v>
       </c>
       <c r="EQ1" s="1" t="s">
-        <v>945</v>
+        <v>952</v>
       </c>
       <c r="ER1" s="1" t="s">
-        <v>947</v>
+        <v>954</v>
       </c>
       <c r="ES1" s="1" t="s">
-        <v>953</v>
+        <v>960</v>
       </c>
       <c r="ET1" s="1" t="s">
-        <v>955</v>
+        <v>962</v>
       </c>
       <c r="EU1" s="1" t="s">
-        <v>957</v>
+        <v>964</v>
       </c>
       <c r="EV1" s="1" t="s">
-        <v>959</v>
+        <v>966</v>
       </c>
       <c r="EW1" s="1" t="s">
-        <v>961</v>
+        <v>968</v>
       </c>
       <c r="EX1" s="1" t="s">
-        <v>963</v>
+        <v>970</v>
       </c>
       <c r="EY1" s="1" t="s">
-        <v>965</v>
+        <v>972</v>
       </c>
       <c r="EZ1" s="1" t="s">
-        <v>967</v>
+        <v>974</v>
       </c>
       <c r="FA1" s="1" t="s">
-        <v>969</v>
+        <v>976</v>
       </c>
       <c r="FB1" s="1" t="s">
-        <v>971</v>
+        <v>978</v>
       </c>
       <c r="FC1" s="1" t="s">
-        <v>973</v>
+        <v>980</v>
       </c>
       <c r="FD1" s="1" t="s">
-        <v>975</v>
+        <v>982</v>
       </c>
       <c r="FE1" s="1" t="s">
-        <v>977</v>
+        <v>984</v>
       </c>
       <c r="FF1" s="1" t="s">
-        <v>979</v>
+        <v>986</v>
       </c>
       <c r="FG1" s="1" t="s">
-        <v>981</v>
+        <v>988</v>
       </c>
       <c r="FH1" s="1" t="s">
-        <v>983</v>
+        <v>990</v>
       </c>
       <c r="FI1" s="1" t="s">
-        <v>985</v>
+        <v>992</v>
       </c>
       <c r="FJ1" s="1" t="s">
-        <v>987</v>
+        <v>994</v>
       </c>
       <c r="FK1" s="1" t="s">
-        <v>989</v>
+        <v>996</v>
       </c>
       <c r="FL1" s="1" t="s">
-        <v>991</v>
+        <v>998</v>
       </c>
       <c r="FM1" s="1" t="s">
-        <v>993</v>
+        <v>1000</v>
       </c>
       <c r="FN1" s="1" t="s">
-        <v>995</v>
+        <v>1002</v>
       </c>
       <c r="FO1" s="1" t="s">
-        <v>997</v>
+        <v>1004</v>
       </c>
       <c r="FP1" s="1" t="s">
-        <v>999</v>
+        <v>1006</v>
       </c>
       <c r="FQ1" s="1" t="s">
-        <v>1001</v>
+        <v>1008</v>
       </c>
       <c r="FR1" s="1" t="s">
-        <v>1003</v>
+        <v>1010</v>
       </c>
       <c r="FS1" s="1" t="s">
-        <v>1005</v>
+        <v>1012</v>
       </c>
       <c r="FT1" s="1" t="s">
-        <v>1007</v>
+        <v>1014</v>
       </c>
       <c r="FU1" s="1" t="s">
-        <v>1009</v>
+        <v>1016</v>
       </c>
       <c r="FV1" s="1" t="s">
-        <v>1011</v>
+        <v>1018</v>
       </c>
       <c r="FW1" s="1" t="s">
-        <v>1013</v>
+        <v>1020</v>
       </c>
       <c r="FX1" s="1" t="s">
-        <v>1015</v>
+        <v>1022</v>
       </c>
       <c r="FY1" s="1" t="s">
-        <v>1017</v>
+        <v>1024</v>
       </c>
       <c r="FZ1" s="1" t="s">
-        <v>1019</v>
+        <v>1026</v>
       </c>
       <c r="GA1" s="1" t="s">
-        <v>1021</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="2" spans="1:183" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AP2" s="2" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AQ2" s="2" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AR2" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AS2" s="2" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AU2" s="2" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AV2" s="2" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AW2" s="2" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AX2" s="2" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AY2" s="2" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AZ2" s="2" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="BA2" s="2" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="BB2" s="2" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="BC2" s="2" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="BD2" s="2" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="BE2" s="2" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="BF2" s="2" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="BG2" s="2" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="BH2" s="2" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="BI2" s="2" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="BJ2" s="2" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="BK2" s="2" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="BL2" s="2" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="BM2" s="2" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="BN2" s="2" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="BO2" s="2" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="BP2" s="2" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="BQ2" s="2" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="BR2" s="2" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="BS2" s="2" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="BT2" s="2" t="s">
-        <v>770</v>
+        <v>777</v>
       </c>
       <c r="BU2" s="2" t="s">
-        <v>772</v>
+        <v>779</v>
       </c>
       <c r="BV2" s="2" t="s">
-        <v>774</v>
+        <v>781</v>
       </c>
       <c r="BW2" s="2" t="s">
-        <v>776</v>
+        <v>783</v>
       </c>
       <c r="BX2" s="2" t="s">
-        <v>778</v>
+        <v>785</v>
       </c>
       <c r="BY2" s="2" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="BZ2" s="2" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="CA2" s="2" t="s">
-        <v>784</v>
+        <v>791</v>
       </c>
       <c r="CB2" s="2" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="CC2" s="2" t="s">
-        <v>788</v>
+        <v>795</v>
       </c>
       <c r="CD2" s="2" t="s">
-        <v>790</v>
+        <v>797</v>
       </c>
       <c r="CE2" s="2" t="s">
-        <v>792</v>
+        <v>799</v>
       </c>
       <c r="CF2" s="2" t="s">
-        <v>794</v>
+        <v>801</v>
       </c>
       <c r="CG2" s="2" t="s">
-        <v>796</v>
+        <v>803</v>
       </c>
       <c r="CH2" s="2" t="s">
-        <v>798</v>
+        <v>805</v>
       </c>
       <c r="CI2" s="2" t="s">
-        <v>800</v>
+        <v>807</v>
       </c>
       <c r="CJ2" s="2" t="s">
-        <v>802</v>
+        <v>809</v>
       </c>
       <c r="CK2" s="2" t="s">
-        <v>804</v>
+        <v>811</v>
       </c>
       <c r="CL2" s="2" t="s">
-        <v>806</v>
+        <v>813</v>
       </c>
       <c r="CM2" s="2" t="s">
-        <v>808</v>
+        <v>815</v>
       </c>
       <c r="CN2" s="2" t="s">
-        <v>810</v>
+        <v>817</v>
       </c>
       <c r="CO2" s="2" t="s">
-        <v>818</v>
+        <v>825</v>
       </c>
       <c r="CP2" s="2" t="s">
-        <v>820</v>
+        <v>827</v>
       </c>
       <c r="CQ2" s="2" t="s">
-        <v>828</v>
+        <v>835</v>
       </c>
       <c r="CR2" s="2" t="s">
-        <v>830</v>
+        <v>837</v>
       </c>
       <c r="CS2" s="2" t="s">
-        <v>832</v>
+        <v>839</v>
       </c>
       <c r="CT2" s="2" t="s">
-        <v>834</v>
+        <v>841</v>
       </c>
       <c r="CU2" s="2" t="s">
-        <v>836</v>
+        <v>843</v>
       </c>
       <c r="CV2" s="2" t="s">
-        <v>843</v>
+        <v>850</v>
       </c>
       <c r="CW2" s="2" t="s">
-        <v>845</v>
+        <v>852</v>
       </c>
       <c r="CX2" s="2" t="s">
-        <v>847</v>
+        <v>854</v>
       </c>
       <c r="CY2" s="2" t="s">
-        <v>849</v>
+        <v>856</v>
       </c>
       <c r="CZ2" s="2" t="s">
-        <v>851</v>
+        <v>858</v>
       </c>
       <c r="DA2" s="2" t="s">
-        <v>853</v>
+        <v>860</v>
       </c>
       <c r="DB2" s="2" t="s">
-        <v>855</v>
+        <v>862</v>
       </c>
       <c r="DC2" s="2" t="s">
-        <v>857</v>
+        <v>864</v>
       </c>
       <c r="DD2" s="2" t="s">
-        <v>859</v>
+        <v>866</v>
       </c>
       <c r="DE2" s="2" t="s">
-        <v>861</v>
+        <v>868</v>
       </c>
       <c r="DF2" s="2" t="s">
-        <v>863</v>
+        <v>870</v>
       </c>
       <c r="DG2" s="2" t="s">
-        <v>865</v>
+        <v>872</v>
       </c>
       <c r="DH2" s="2" t="s">
-        <v>867</v>
+        <v>874</v>
       </c>
       <c r="DI2" s="2" t="s">
-        <v>869</v>
+        <v>876</v>
       </c>
       <c r="DJ2" s="2" t="s">
-        <v>871</v>
+        <v>878</v>
       </c>
       <c r="DK2" s="2" t="s">
-        <v>882</v>
+        <v>889</v>
       </c>
       <c r="DL2" s="2" t="s">
-        <v>884</v>
+        <v>891</v>
       </c>
       <c r="DM2" s="2" t="s">
-        <v>886</v>
+        <v>893</v>
       </c>
       <c r="DN2" s="2" t="s">
-        <v>888</v>
+        <v>895</v>
       </c>
       <c r="DO2" s="2" t="s">
-        <v>890</v>
+        <v>897</v>
       </c>
       <c r="DP2" s="2" t="s">
-        <v>892</v>
+        <v>899</v>
       </c>
       <c r="DQ2" s="2" t="s">
-        <v>894</v>
+        <v>901</v>
       </c>
       <c r="DR2" s="2" t="s">
-        <v>896</v>
+        <v>903</v>
       </c>
       <c r="DS2" s="2" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="DT2" s="2" t="s">
-        <v>900</v>
+        <v>907</v>
       </c>
       <c r="DU2" s="2" t="s">
-        <v>902</v>
+        <v>909</v>
       </c>
       <c r="DV2" s="2" t="s">
-        <v>904</v>
+        <v>911</v>
       </c>
       <c r="DW2" s="2" t="s">
-        <v>906</v>
+        <v>913</v>
       </c>
       <c r="DX2" s="2" t="s">
-        <v>908</v>
+        <v>915</v>
       </c>
       <c r="DY2" s="2" t="s">
-        <v>910</v>
+        <v>917</v>
       </c>
       <c r="DZ2" s="2" t="s">
-        <v>912</v>
+        <v>919</v>
       </c>
       <c r="EA2" s="2" t="s">
-        <v>914</v>
+        <v>921</v>
       </c>
       <c r="EB2" s="2" t="s">
-        <v>916</v>
+        <v>923</v>
       </c>
       <c r="EC2" s="2" t="s">
-        <v>918</v>
+        <v>925</v>
       </c>
       <c r="ED2" s="2" t="s">
-        <v>920</v>
+        <v>927</v>
       </c>
       <c r="EE2" s="2" t="s">
-        <v>922</v>
+        <v>929</v>
       </c>
       <c r="EF2" s="2" t="s">
-        <v>924</v>
+        <v>931</v>
       </c>
       <c r="EG2" s="2" t="s">
-        <v>926</v>
+        <v>933</v>
       </c>
       <c r="EH2" s="2" t="s">
-        <v>928</v>
+        <v>935</v>
       </c>
       <c r="EI2" s="2" t="s">
-        <v>930</v>
+        <v>937</v>
       </c>
       <c r="EJ2" s="2" t="s">
-        <v>932</v>
+        <v>939</v>
       </c>
       <c r="EK2" s="2" t="s">
-        <v>934</v>
+        <v>941</v>
       </c>
       <c r="EL2" s="2" t="s">
-        <v>936</v>
+        <v>943</v>
       </c>
       <c r="EM2" s="2" t="s">
-        <v>938</v>
+        <v>945</v>
       </c>
       <c r="EN2" s="2" t="s">
-        <v>940</v>
+        <v>947</v>
       </c>
       <c r="EO2" s="2" t="s">
-        <v>942</v>
+        <v>949</v>
       </c>
       <c r="EP2" s="2" t="s">
-        <v>944</v>
+        <v>951</v>
       </c>
       <c r="EQ2" s="2" t="s">
-        <v>946</v>
+        <v>953</v>
       </c>
       <c r="ER2" s="2" t="s">
-        <v>948</v>
+        <v>955</v>
       </c>
       <c r="ES2" s="2" t="s">
-        <v>954</v>
+        <v>961</v>
       </c>
       <c r="ET2" s="2" t="s">
-        <v>956</v>
+        <v>963</v>
       </c>
       <c r="EU2" s="2" t="s">
-        <v>958</v>
+        <v>965</v>
       </c>
       <c r="EV2" s="2" t="s">
-        <v>960</v>
+        <v>967</v>
       </c>
       <c r="EW2" s="2" t="s">
-        <v>962</v>
+        <v>969</v>
       </c>
       <c r="EX2" s="2" t="s">
-        <v>964</v>
+        <v>971</v>
       </c>
       <c r="EY2" s="2" t="s">
-        <v>966</v>
+        <v>973</v>
       </c>
       <c r="EZ2" s="2" t="s">
-        <v>968</v>
+        <v>975</v>
       </c>
       <c r="FA2" s="2" t="s">
-        <v>970</v>
+        <v>977</v>
       </c>
       <c r="FB2" s="2" t="s">
-        <v>972</v>
+        <v>979</v>
       </c>
       <c r="FC2" s="2" t="s">
-        <v>974</v>
+        <v>981</v>
       </c>
       <c r="FD2" s="2" t="s">
-        <v>976</v>
+        <v>983</v>
       </c>
       <c r="FE2" s="2" t="s">
-        <v>978</v>
+        <v>985</v>
       </c>
       <c r="FF2" s="2" t="s">
-        <v>980</v>
+        <v>987</v>
       </c>
       <c r="FG2" s="2" t="s">
-        <v>982</v>
+        <v>989</v>
       </c>
       <c r="FH2" s="2" t="s">
-        <v>984</v>
+        <v>991</v>
       </c>
       <c r="FI2" s="2" t="s">
-        <v>986</v>
+        <v>993</v>
       </c>
       <c r="FJ2" s="2" t="s">
-        <v>988</v>
+        <v>995</v>
       </c>
       <c r="FK2" s="2" t="s">
-        <v>990</v>
+        <v>997</v>
       </c>
       <c r="FL2" s="2" t="s">
-        <v>992</v>
+        <v>999</v>
       </c>
       <c r="FM2" s="2" t="s">
-        <v>994</v>
+        <v>1001</v>
       </c>
       <c r="FN2" s="2" t="s">
-        <v>996</v>
+        <v>1003</v>
       </c>
       <c r="FO2" s="2" t="s">
-        <v>998</v>
+        <v>1005</v>
       </c>
       <c r="FP2" s="2" t="s">
-        <v>1000</v>
+        <v>1007</v>
       </c>
       <c r="FQ2" s="2" t="s">
-        <v>1002</v>
+        <v>1009</v>
       </c>
       <c r="FR2" s="2" t="s">
-        <v>1004</v>
+        <v>1011</v>
       </c>
       <c r="FS2" s="2" t="s">
-        <v>1006</v>
+        <v>1013</v>
       </c>
       <c r="FT2" s="2" t="s">
-        <v>1008</v>
+        <v>1015</v>
       </c>
       <c r="FU2" s="2" t="s">
-        <v>1010</v>
+        <v>1017</v>
       </c>
       <c r="FV2" s="2" t="s">
-        <v>1012</v>
+        <v>1019</v>
       </c>
       <c r="FW2" s="2" t="s">
-        <v>1014</v>
+        <v>1021</v>
       </c>
       <c r="FX2" s="2" t="s">
-        <v>1016</v>
+        <v>1023</v>
       </c>
       <c r="FY2" s="2" t="s">
-        <v>1018</v>
+        <v>1025</v>
       </c>
       <c r="FZ2" s="2" t="s">
-        <v>1020</v>
+        <v>1027</v>
       </c>
       <c r="GA2" s="2" t="s">
-        <v>1022</v>
+        <v>1029</v>
       </c>
     </row>
   </sheetData>
@@ -5778,1770 +5807,1795 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="H1:ES289"/>
+  <dimension ref="H1:ES294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="8:149">
       <c r="H1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="J1" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="V1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AB1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AW1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="BA1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="BT1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="CO1" t="s">
-        <v>811</v>
+        <v>818</v>
       </c>
       <c r="CQ1" t="s">
-        <v>821</v>
+        <v>828</v>
       </c>
       <c r="CV1" t="s">
-        <v>837</v>
+        <v>844</v>
       </c>
       <c r="DK1" t="s">
-        <v>872</v>
+        <v>879</v>
       </c>
       <c r="ES1" t="s">
-        <v>949</v>
+        <v>956</v>
       </c>
     </row>
     <row r="2" spans="8:149">
       <c r="H2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="J2" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="V2" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AB2" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AW2" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="BA2" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="BT2" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="CO2" t="s">
-        <v>812</v>
+        <v>819</v>
       </c>
       <c r="CQ2" t="s">
-        <v>822</v>
+        <v>829</v>
       </c>
       <c r="CV2" t="s">
-        <v>838</v>
+        <v>845</v>
       </c>
       <c r="DK2" t="s">
-        <v>873</v>
+        <v>880</v>
       </c>
       <c r="ES2" t="s">
-        <v>950</v>
+        <v>957</v>
       </c>
     </row>
     <row r="3" spans="8:149">
       <c r="H3" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J3" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="V3" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AW3" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="BT3" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="CO3" t="s">
-        <v>813</v>
+        <v>820</v>
       </c>
       <c r="CQ3" t="s">
-        <v>823</v>
+        <v>830</v>
       </c>
       <c r="CV3" t="s">
-        <v>839</v>
+        <v>846</v>
       </c>
       <c r="DK3" t="s">
-        <v>874</v>
+        <v>881</v>
       </c>
       <c r="ES3" t="s">
-        <v>951</v>
+        <v>958</v>
       </c>
     </row>
     <row r="4" spans="8:149">
       <c r="H4" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="J4" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="V4" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="BT4" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="CO4" t="s">
-        <v>814</v>
+        <v>821</v>
       </c>
       <c r="CQ4" t="s">
-        <v>824</v>
+        <v>831</v>
       </c>
       <c r="CV4" t="s">
-        <v>840</v>
+        <v>847</v>
       </c>
       <c r="DK4" t="s">
-        <v>875</v>
+        <v>882</v>
       </c>
       <c r="ES4" t="s">
-        <v>952</v>
+        <v>959</v>
       </c>
     </row>
     <row r="5" spans="8:149">
       <c r="H5" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J5" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="V5" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="BT5" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="CO5" t="s">
-        <v>815</v>
+        <v>822</v>
       </c>
       <c r="CQ5" t="s">
-        <v>825</v>
+        <v>832</v>
       </c>
       <c r="CV5" t="s">
-        <v>841</v>
+        <v>848</v>
       </c>
       <c r="DK5" t="s">
-        <v>876</v>
+        <v>883</v>
       </c>
     </row>
     <row r="6" spans="8:149">
       <c r="H6" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="J6" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="V6" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="BT6" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="CO6" t="s">
-        <v>816</v>
+        <v>823</v>
       </c>
       <c r="CQ6" t="s">
-        <v>826</v>
+        <v>833</v>
       </c>
       <c r="DK6" t="s">
-        <v>877</v>
+        <v>884</v>
       </c>
     </row>
     <row r="7" spans="8:149">
       <c r="H7" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J7" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="V7" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="BT7" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="DK7" t="s">
-        <v>878</v>
+        <v>885</v>
       </c>
     </row>
     <row r="8" spans="8:149">
       <c r="H8" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="V8" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="BT8" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="DK8" t="s">
-        <v>879</v>
+        <v>886</v>
       </c>
     </row>
     <row r="9" spans="8:149">
       <c r="H9" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="V9" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="BT9" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="DK9" t="s">
-        <v>880</v>
+        <v>887</v>
       </c>
     </row>
     <row r="10" spans="8:149">
       <c r="H10" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="V10" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="BT10" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="11" spans="8:149">
       <c r="H11" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="V11" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="BT11" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="12" spans="8:149">
       <c r="H12" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="V12" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="BT12" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="13" spans="8:149">
       <c r="H13" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="V13" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="BT13" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="14" spans="8:149">
       <c r="H14" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="V14" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="BT14" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="15" spans="8:149">
       <c r="H15" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="V15" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="BT15" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="16" spans="8:149">
       <c r="H16" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="V16" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="BT16" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="17" spans="8:72">
       <c r="H17" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="V17" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="BT17" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="18" spans="8:72">
       <c r="H18" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="V18" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="BT18" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="19" spans="8:72">
       <c r="H19" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="V19" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="BT19" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="20" spans="8:72">
       <c r="H20" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="V20" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="BT20" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="21" spans="8:72">
       <c r="H21" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="V21" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="BT21" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="22" spans="8:72">
       <c r="H22" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="V22" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="BT22" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="23" spans="8:72">
       <c r="H23" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="V23" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="BT23" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="24" spans="8:72">
       <c r="H24" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="V24" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="BT24" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="25" spans="8:72">
       <c r="H25" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="V25" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="BT25" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="26" spans="8:72">
       <c r="H26" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="V26" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="BT26" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="27" spans="8:72">
       <c r="H27" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="V27" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="BT27" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="28" spans="8:72">
       <c r="H28" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="V28" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="BT28" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="29" spans="8:72">
       <c r="H29" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="V29" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="BT29" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="30" spans="8:72">
       <c r="H30" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="V30" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="BT30" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="31" spans="8:72">
       <c r="V31" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="BT31" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="32" spans="8:72">
       <c r="V32" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="BT32" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="33" spans="72:72">
       <c r="BT33" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="34" spans="72:72">
       <c r="BT34" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="35" spans="72:72">
       <c r="BT35" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="36" spans="72:72">
       <c r="BT36" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="37" spans="72:72">
       <c r="BT37" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="38" spans="72:72">
       <c r="BT38" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="39" spans="72:72">
       <c r="BT39" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="40" spans="72:72">
       <c r="BT40" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="41" spans="72:72">
       <c r="BT41" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="42" spans="72:72">
       <c r="BT42" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="43" spans="72:72">
       <c r="BT43" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="44" spans="72:72">
       <c r="BT44" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="45" spans="72:72">
       <c r="BT45" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="46" spans="72:72">
       <c r="BT46" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="47" spans="72:72">
       <c r="BT47" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="48" spans="72:72">
       <c r="BT48" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="49" spans="72:72">
       <c r="BT49" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="50" spans="72:72">
       <c r="BT50" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="51" spans="72:72">
       <c r="BT51" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="52" spans="72:72">
       <c r="BT52" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="53" spans="72:72">
       <c r="BT53" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="54" spans="72:72">
       <c r="BT54" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="55" spans="72:72">
       <c r="BT55" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="56" spans="72:72">
       <c r="BT56" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="57" spans="72:72">
       <c r="BT57" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="58" spans="72:72">
       <c r="BT58" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="59" spans="72:72">
       <c r="BT59" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="60" spans="72:72">
       <c r="BT60" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="61" spans="72:72">
       <c r="BT61" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="62" spans="72:72">
       <c r="BT62" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="63" spans="72:72">
       <c r="BT63" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="64" spans="72:72">
       <c r="BT64" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="65" spans="72:72">
       <c r="BT65" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="66" spans="72:72">
       <c r="BT66" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="67" spans="72:72">
       <c r="BT67" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="68" spans="72:72">
       <c r="BT68" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="69" spans="72:72">
       <c r="BT69" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="70" spans="72:72">
       <c r="BT70" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="71" spans="72:72">
       <c r="BT71" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="72" spans="72:72">
       <c r="BT72" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="73" spans="72:72">
       <c r="BT73" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="74" spans="72:72">
       <c r="BT74" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="75" spans="72:72">
       <c r="BT75" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="76" spans="72:72">
       <c r="BT76" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="77" spans="72:72">
       <c r="BT77" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="78" spans="72:72">
       <c r="BT78" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="79" spans="72:72">
       <c r="BT79" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="80" spans="72:72">
       <c r="BT80" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="81" spans="72:72">
       <c r="BT81" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="82" spans="72:72">
       <c r="BT82" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="83" spans="72:72">
       <c r="BT83" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="84" spans="72:72">
       <c r="BT84" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="85" spans="72:72">
       <c r="BT85" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="86" spans="72:72">
       <c r="BT86" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="87" spans="72:72">
       <c r="BT87" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="88" spans="72:72">
       <c r="BT88" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="89" spans="72:72">
       <c r="BT89" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="90" spans="72:72">
       <c r="BT90" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="91" spans="72:72">
       <c r="BT91" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="92" spans="72:72">
       <c r="BT92" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="93" spans="72:72">
       <c r="BT93" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="94" spans="72:72">
       <c r="BT94" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="95" spans="72:72">
       <c r="BT95" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="96" spans="72:72">
       <c r="BT96" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="97" spans="72:72">
       <c r="BT97" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="98" spans="72:72">
       <c r="BT98" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="99" spans="72:72">
       <c r="BT99" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="100" spans="72:72">
       <c r="BT100" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="101" spans="72:72">
       <c r="BT101" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="102" spans="72:72">
       <c r="BT102" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="103" spans="72:72">
       <c r="BT103" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="104" spans="72:72">
       <c r="BT104" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="105" spans="72:72">
       <c r="BT105" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="106" spans="72:72">
       <c r="BT106" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="107" spans="72:72">
       <c r="BT107" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="108" spans="72:72">
       <c r="BT108" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="109" spans="72:72">
       <c r="BT109" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="110" spans="72:72">
       <c r="BT110" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="111" spans="72:72">
       <c r="BT111" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="112" spans="72:72">
       <c r="BT112" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="113" spans="72:72">
       <c r="BT113" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="114" spans="72:72">
       <c r="BT114" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="115" spans="72:72">
       <c r="BT115" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="116" spans="72:72">
       <c r="BT116" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="117" spans="72:72">
       <c r="BT117" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="118" spans="72:72">
       <c r="BT118" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="119" spans="72:72">
       <c r="BT119" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="120" spans="72:72">
       <c r="BT120" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="121" spans="72:72">
       <c r="BT121" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="122" spans="72:72">
       <c r="BT122" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="123" spans="72:72">
       <c r="BT123" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="124" spans="72:72">
       <c r="BT124" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="125" spans="72:72">
       <c r="BT125" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="126" spans="72:72">
       <c r="BT126" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="127" spans="72:72">
       <c r="BT127" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="128" spans="72:72">
       <c r="BT128" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="129" spans="72:72">
       <c r="BT129" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="130" spans="72:72">
       <c r="BT130" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="131" spans="72:72">
       <c r="BT131" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="132" spans="72:72">
       <c r="BT132" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="133" spans="72:72">
       <c r="BT133" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="134" spans="72:72">
       <c r="BT134" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="135" spans="72:72">
       <c r="BT135" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="136" spans="72:72">
       <c r="BT136" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="137" spans="72:72">
       <c r="BT137" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="138" spans="72:72">
       <c r="BT138" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="139" spans="72:72">
       <c r="BT139" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="140" spans="72:72">
       <c r="BT140" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
     </row>
     <row r="141" spans="72:72">
       <c r="BT141" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="142" spans="72:72">
       <c r="BT142" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
     </row>
     <row r="143" spans="72:72">
       <c r="BT143" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
     </row>
     <row r="144" spans="72:72">
       <c r="BT144" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
     </row>
     <row r="145" spans="72:72">
       <c r="BT145" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="146" spans="72:72">
       <c r="BT146" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
     </row>
     <row r="147" spans="72:72">
       <c r="BT147" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="148" spans="72:72">
       <c r="BT148" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
     <row r="149" spans="72:72">
       <c r="BT149" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
     </row>
     <row r="150" spans="72:72">
       <c r="BT150" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
     </row>
     <row r="151" spans="72:72">
       <c r="BT151" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
     <row r="152" spans="72:72">
       <c r="BT152" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
     </row>
     <row r="153" spans="72:72">
       <c r="BT153" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="154" spans="72:72">
       <c r="BT154" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
     </row>
     <row r="155" spans="72:72">
       <c r="BT155" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
     </row>
     <row r="156" spans="72:72">
       <c r="BT156" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
     </row>
     <row r="157" spans="72:72">
       <c r="BT157" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
     </row>
     <row r="158" spans="72:72">
       <c r="BT158" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
     </row>
     <row r="159" spans="72:72">
       <c r="BT159" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
     </row>
     <row r="160" spans="72:72">
       <c r="BT160" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
     </row>
     <row r="161" spans="72:72">
       <c r="BT161" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
     <row r="162" spans="72:72">
       <c r="BT162" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
     </row>
     <row r="163" spans="72:72">
       <c r="BT163" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="164" spans="72:72">
       <c r="BT164" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
     </row>
     <row r="165" spans="72:72">
       <c r="BT165" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="166" spans="72:72">
       <c r="BT166" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
     </row>
     <row r="167" spans="72:72">
       <c r="BT167" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
     <row r="168" spans="72:72">
       <c r="BT168" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
     </row>
     <row r="169" spans="72:72">
       <c r="BT169" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
     </row>
     <row r="170" spans="72:72">
       <c r="BT170" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
     </row>
     <row r="171" spans="72:72">
       <c r="BT171" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="172" spans="72:72">
       <c r="BT172" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="173" spans="72:72">
       <c r="BT173" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="174" spans="72:72">
       <c r="BT174" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="175" spans="72:72">
       <c r="BT175" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="176" spans="72:72">
       <c r="BT176" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
     </row>
     <row r="177" spans="72:72">
       <c r="BT177" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
     <row r="178" spans="72:72">
       <c r="BT178" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
     </row>
     <row r="179" spans="72:72">
       <c r="BT179" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="180" spans="72:72">
       <c r="BT180" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
     </row>
     <row r="181" spans="72:72">
       <c r="BT181" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="182" spans="72:72">
       <c r="BT182" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
     <row r="183" spans="72:72">
       <c r="BT183" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="184" spans="72:72">
       <c r="BT184" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="185" spans="72:72">
       <c r="BT185" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="186" spans="72:72">
       <c r="BT186" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
     </row>
     <row r="187" spans="72:72">
       <c r="BT187" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="188" spans="72:72">
       <c r="BT188" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="189" spans="72:72">
       <c r="BT189" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
     </row>
     <row r="190" spans="72:72">
       <c r="BT190" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
     </row>
     <row r="191" spans="72:72">
       <c r="BT191" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
     </row>
     <row r="192" spans="72:72">
       <c r="BT192" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
     <row r="193" spans="72:72">
       <c r="BT193" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
     </row>
     <row r="194" spans="72:72">
       <c r="BT194" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
     </row>
     <row r="195" spans="72:72">
       <c r="BT195" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="196" spans="72:72">
       <c r="BT196" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
     </row>
     <row r="197" spans="72:72">
       <c r="BT197" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="198" spans="72:72">
       <c r="BT198" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
     </row>
     <row r="199" spans="72:72">
       <c r="BT199" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
     </row>
     <row r="200" spans="72:72">
       <c r="BT200" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
     </row>
     <row r="201" spans="72:72">
       <c r="BT201" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
     </row>
     <row r="202" spans="72:72">
       <c r="BT202" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
     </row>
     <row r="203" spans="72:72">
       <c r="BT203" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
     </row>
     <row r="204" spans="72:72">
       <c r="BT204" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
     </row>
     <row r="205" spans="72:72">
       <c r="BT205" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
     </row>
     <row r="206" spans="72:72">
       <c r="BT206" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
     </row>
     <row r="207" spans="72:72">
       <c r="BT207" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
     </row>
     <row r="208" spans="72:72">
       <c r="BT208" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
     </row>
     <row r="209" spans="72:72">
       <c r="BT209" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
     </row>
     <row r="210" spans="72:72">
       <c r="BT210" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
     </row>
     <row r="211" spans="72:72">
       <c r="BT211" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
     </row>
     <row r="212" spans="72:72">
       <c r="BT212" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
     </row>
     <row r="213" spans="72:72">
       <c r="BT213" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
     </row>
     <row r="214" spans="72:72">
       <c r="BT214" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
     </row>
     <row r="215" spans="72:72">
       <c r="BT215" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
     </row>
     <row r="216" spans="72:72">
       <c r="BT216" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
     </row>
     <row r="217" spans="72:72">
       <c r="BT217" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
     </row>
     <row r="218" spans="72:72">
       <c r="BT218" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
     </row>
     <row r="219" spans="72:72">
       <c r="BT219" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
     </row>
     <row r="220" spans="72:72">
       <c r="BT220" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
     </row>
     <row r="221" spans="72:72">
       <c r="BT221" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
     </row>
     <row r="222" spans="72:72">
       <c r="BT222" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
     </row>
     <row r="223" spans="72:72">
       <c r="BT223" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
     </row>
     <row r="224" spans="72:72">
       <c r="BT224" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
     </row>
     <row r="225" spans="72:72">
       <c r="BT225" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
     </row>
     <row r="226" spans="72:72">
       <c r="BT226" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
     </row>
     <row r="227" spans="72:72">
       <c r="BT227" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
     </row>
     <row r="228" spans="72:72">
       <c r="BT228" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
     </row>
     <row r="229" spans="72:72">
       <c r="BT229" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
     </row>
     <row r="230" spans="72:72">
       <c r="BT230" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
     </row>
     <row r="231" spans="72:72">
       <c r="BT231" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
     </row>
     <row r="232" spans="72:72">
       <c r="BT232" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
     </row>
     <row r="233" spans="72:72">
       <c r="BT233" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
     </row>
     <row r="234" spans="72:72">
       <c r="BT234" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
     </row>
     <row r="235" spans="72:72">
       <c r="BT235" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
     </row>
     <row r="236" spans="72:72">
       <c r="BT236" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
     </row>
     <row r="237" spans="72:72">
       <c r="BT237" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
     </row>
     <row r="238" spans="72:72">
       <c r="BT238" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
     </row>
     <row r="239" spans="72:72">
       <c r="BT239" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
     </row>
     <row r="240" spans="72:72">
       <c r="BT240" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
     </row>
     <row r="241" spans="72:72">
       <c r="BT241" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
     </row>
     <row r="242" spans="72:72">
       <c r="BT242" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
     </row>
     <row r="243" spans="72:72">
       <c r="BT243" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
     </row>
     <row r="244" spans="72:72">
       <c r="BT244" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
     </row>
     <row r="245" spans="72:72">
       <c r="BT245" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
     </row>
     <row r="246" spans="72:72">
       <c r="BT246" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
     </row>
     <row r="247" spans="72:72">
       <c r="BT247" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
     </row>
     <row r="248" spans="72:72">
       <c r="BT248" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
     </row>
     <row r="249" spans="72:72">
       <c r="BT249" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
     </row>
     <row r="250" spans="72:72">
       <c r="BT250" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
     </row>
     <row r="251" spans="72:72">
       <c r="BT251" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
     </row>
     <row r="252" spans="72:72">
       <c r="BT252" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
     </row>
     <row r="253" spans="72:72">
       <c r="BT253" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
     </row>
     <row r="254" spans="72:72">
       <c r="BT254" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
     </row>
     <row r="255" spans="72:72">
       <c r="BT255" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
     </row>
     <row r="256" spans="72:72">
       <c r="BT256" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
     </row>
     <row r="257" spans="72:72">
       <c r="BT257" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
     </row>
     <row r="258" spans="72:72">
       <c r="BT258" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
     </row>
     <row r="259" spans="72:72">
       <c r="BT259" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
     </row>
     <row r="260" spans="72:72">
       <c r="BT260" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
     </row>
     <row r="261" spans="72:72">
       <c r="BT261" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
     </row>
     <row r="262" spans="72:72">
       <c r="BT262" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
     </row>
     <row r="263" spans="72:72">
       <c r="BT263" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
     </row>
     <row r="264" spans="72:72">
       <c r="BT264" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
     </row>
     <row r="265" spans="72:72">
       <c r="BT265" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
     </row>
     <row r="266" spans="72:72">
       <c r="BT266" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="267" spans="72:72">
       <c r="BT267" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
     </row>
     <row r="268" spans="72:72">
       <c r="BT268" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
     </row>
     <row r="269" spans="72:72">
       <c r="BT269" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
     </row>
     <row r="270" spans="72:72">
       <c r="BT270" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
     </row>
     <row r="271" spans="72:72">
       <c r="BT271" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
     </row>
     <row r="272" spans="72:72">
       <c r="BT272" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
     </row>
     <row r="273" spans="72:72">
       <c r="BT273" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
     </row>
     <row r="274" spans="72:72">
       <c r="BT274" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
     </row>
     <row r="275" spans="72:72">
       <c r="BT275" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
     </row>
     <row r="276" spans="72:72">
       <c r="BT276" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
     </row>
     <row r="277" spans="72:72">
       <c r="BT277" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
     </row>
     <row r="278" spans="72:72">
       <c r="BT278" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
     </row>
     <row r="279" spans="72:72">
       <c r="BT279" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
     </row>
     <row r="280" spans="72:72">
       <c r="BT280" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
     </row>
     <row r="281" spans="72:72">
       <c r="BT281" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
     </row>
     <row r="282" spans="72:72">
       <c r="BT282" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
     </row>
     <row r="283" spans="72:72">
       <c r="BT283" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
     </row>
     <row r="284" spans="72:72">
       <c r="BT284" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
     </row>
     <row r="285" spans="72:72">
       <c r="BT285" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
     </row>
     <row r="286" spans="72:72">
       <c r="BT286" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
     </row>
     <row r="287" spans="72:72">
       <c r="BT287" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
     </row>
     <row r="288" spans="72:72">
       <c r="BT288" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
     </row>
     <row r="289" spans="72:72">
       <c r="BT289" t="s">
-        <v>768</v>
+        <v>770</v>
+      </c>
+    </row>
+    <row r="290" spans="72:72">
+      <c r="BT290" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="291" spans="72:72">
+      <c r="BT291" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="292" spans="72:72">
+      <c r="BT292" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="293" spans="72:72">
+      <c r="BT293" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="294" spans="72:72">
+      <c r="BT294" t="s">
+        <v>775</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000055/metadata_template_ERC000055.xlsx
+++ b/templates/ERC000055/metadata_template_ERC000055.xlsx
@@ -17,31 +17,31 @@
     <sheet name="cv_sample" sheetId="8" state="hidden" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="drainageclassification">'cv_sample'!$CO$1:$CO$6</definedName>
+    <definedName name="drainageclassification">'cv_sample'!$CP$1:$CP$6</definedName>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$BR$1:$BR$289</definedName>
-    <definedName name="historytillage">'cv_sample'!$DI$1:$DI$9</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$87</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$BS$1:$BS$294</definedName>
+    <definedName name="historytillage">'cv_sample'!$DJ$1:$DJ$9</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
-    <definedName name="oxygenationstatusofsample">'cv_sample'!$Z$1:$Z$2</definedName>
-    <definedName name="platform">'cv_experiment'!$M$1:$M$17</definedName>
-    <definedName name="profileposition">'cv_sample'!$CT$1:$CT$5</definedName>
-    <definedName name="relationshiptooxygen">'cv_sample'!$H$1:$H$7</definedName>
-    <definedName name="sequencequalitycheck">'cv_sample'!$AU$1:$AU$3</definedName>
-    <definedName name="singlecellorviralparticlelysisapproach">'cv_sample'!$EQ$1:$EQ$4</definedName>
-    <definedName name="soilhorizon">'cv_sample'!$CM$1:$CM$6</definedName>
-    <definedName name="soiltype">'cv_sample'!$T$1:$T$32</definedName>
+    <definedName name="oxygenationstatusofsample">'cv_sample'!$AA$1:$AA$2</definedName>
+    <definedName name="platform">'cv_experiment'!$M$1:$M$18</definedName>
+    <definedName name="profileposition">'cv_sample'!$CU$1:$CU$5</definedName>
+    <definedName name="relationshiptooxygen">'cv_sample'!$I$1:$I$7</definedName>
+    <definedName name="sequencequalitycheck">'cv_sample'!$AV$1:$AV$3</definedName>
+    <definedName name="singlecellorviralparticlelysisapproach">'cv_sample'!$ER$1:$ER$4</definedName>
+    <definedName name="soilhorizon">'cv_sample'!$CN$1:$CN$6</definedName>
+    <definedName name="soiltype">'cv_sample'!$U$1:$U$32</definedName>
     <definedName name="studytype">'cv_study'!$C$1:$C$15</definedName>
-    <definedName name="trophiclevel">'cv_sample'!$F$1:$F$30</definedName>
+    <definedName name="trophiclevel">'cv_sample'!$G$1:$G$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1027" uniqueCount="1019">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1036" uniqueCount="1028">
   <si>
     <t>alias</t>
   </si>
@@ -457,6 +457,9 @@
     <t>ELEMENT</t>
   </si>
   <si>
+    <t>AVITI</t>
+  </si>
+  <si>
     <t>ULTIMA</t>
   </si>
   <si>
@@ -547,6 +550,9 @@
     <t>AB SOLiD System 3.0</t>
   </si>
   <si>
+    <t>AVITI 24</t>
+  </si>
+  <si>
     <t>BGISEQ-50</t>
   </si>
   <si>
@@ -847,6 +853,12 @@
     <t>(Mandatory) Ncbi taxonomy identifier.  this is appropriate for individual organisms and some environmental samples.</t>
   </si>
   <si>
+    <t>scientific_name</t>
+  </si>
+  <si>
+    <t>(Optional) Scientific name of sample that distinguishes its taxonomy.  please use a name or synonym that is tracked in the insdc taxonomy database. also, this field can be used to confirm the taxon_id setting.</t>
+  </si>
+  <si>
     <t>sample_description</t>
   </si>
   <si>
@@ -1684,9 +1696,6 @@
     <t>Dominican Republic</t>
   </si>
   <si>
-    <t>East Timor</t>
-  </si>
-  <si>
     <t>Ecuador</t>
   </si>
   <si>
@@ -1705,6 +1714,9 @@
     <t>Estonia</t>
   </si>
   <si>
+    <t>Eswatini</t>
+  </si>
+  <si>
     <t>Ethiopia</t>
   </si>
   <si>
@@ -1906,6 +1918,9 @@
     <t>Liechtenstein</t>
   </si>
   <si>
+    <t>Line Islands</t>
+  </si>
+  <si>
     <t>Lithuania</t>
   </si>
   <si>
@@ -1915,9 +1930,6 @@
     <t>Macau</t>
   </si>
   <si>
-    <t>Macedonia</t>
-  </si>
-  <si>
     <t>Madagascar</t>
   </si>
   <si>
@@ -1957,7 +1969,7 @@
     <t>Mexico</t>
   </si>
   <si>
-    <t>Micronesia</t>
+    <t>Micronesia, Federated States of</t>
   </si>
   <si>
     <t>Midway Islands</t>
@@ -2026,6 +2038,9 @@
     <t>North Korea</t>
   </si>
   <si>
+    <t>North Macedonia</t>
+  </si>
+  <si>
     <t>North Sea</t>
   </si>
   <si>
@@ -2101,6 +2116,9 @@
     <t>Rwanda</t>
   </si>
   <si>
+    <t>Saint Barthelemy</t>
+  </si>
+  <si>
     <t>Saint Helena</t>
   </si>
   <si>
@@ -2122,6 +2140,9 @@
     <t>San Marino</t>
   </si>
   <si>
+    <t>Saint Martin</t>
+  </si>
+  <si>
     <t>Sao Tome and Principe</t>
   </si>
   <si>
@@ -2167,6 +2188,9 @@
     <t>South Korea</t>
   </si>
   <si>
+    <t>South Sudan</t>
+  </si>
+  <si>
     <t>Southern Ocean</t>
   </si>
   <si>
@@ -2179,6 +2203,9 @@
     <t>Sri Lanka</t>
   </si>
   <si>
+    <t>State of Palestine</t>
+  </si>
+  <si>
     <t>Sudan</t>
   </si>
   <si>
@@ -2188,9 +2215,6 @@
     <t>Svalbard</t>
   </si>
   <si>
-    <t>Swaziland</t>
-  </si>
-  <si>
     <t>Sweden</t>
   </si>
   <si>
@@ -2215,6 +2239,9 @@
     <t>Thailand</t>
   </si>
   <si>
+    <t>Timor-Leste</t>
+  </si>
+  <si>
     <t>Togo</t>
   </si>
   <si>
@@ -2275,10 +2302,10 @@
     <t>Viet Nam</t>
   </si>
   <si>
+    <t>Wake Island</t>
+  </si>
+  <si>
     <t>Virgin Islands</t>
-  </si>
-  <si>
-    <t>Wake Island</t>
   </si>
   <si>
     <t>Wallis and Futuna</t>
@@ -3624,10 +3651,10 @@
         <v>124</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -3668,10 +3695,10 @@
         <v>125</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -3698,7 +3725,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N87"/>
+  <dimension ref="G1:N88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -3715,7 +3742,7 @@
         <v>126</v>
       </c>
       <c r="N1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="7:14">
@@ -3732,7 +3759,7 @@
         <v>127</v>
       </c>
       <c r="N2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="7:14">
@@ -3749,7 +3776,7 @@
         <v>128</v>
       </c>
       <c r="N3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="7:14">
@@ -3766,7 +3793,7 @@
         <v>129</v>
       </c>
       <c r="N4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="7:14">
@@ -3783,7 +3810,7 @@
         <v>130</v>
       </c>
       <c r="N5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="7:14">
@@ -3800,7 +3827,7 @@
         <v>131</v>
       </c>
       <c r="N6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="7:14">
@@ -3817,7 +3844,7 @@
         <v>132</v>
       </c>
       <c r="N7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="7:14">
@@ -3834,7 +3861,7 @@
         <v>133</v>
       </c>
       <c r="N8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="7:14">
@@ -3851,7 +3878,7 @@
         <v>134</v>
       </c>
       <c r="N9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="7:14">
@@ -3865,7 +3892,7 @@
         <v>135</v>
       </c>
       <c r="N10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="7:14">
@@ -3879,7 +3906,7 @@
         <v>136</v>
       </c>
       <c r="N11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="7:14">
@@ -3893,7 +3920,7 @@
         <v>137</v>
       </c>
       <c r="N12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="7:14">
@@ -3907,7 +3934,7 @@
         <v>138</v>
       </c>
       <c r="N13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="7:14">
@@ -3921,7 +3948,7 @@
         <v>139</v>
       </c>
       <c r="N14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="7:14">
@@ -3935,7 +3962,7 @@
         <v>140</v>
       </c>
       <c r="N15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" spans="7:14">
@@ -3949,7 +3976,7 @@
         <v>141</v>
       </c>
       <c r="N16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" spans="7:14">
@@ -3963,7 +3990,7 @@
         <v>142</v>
       </c>
       <c r="N17" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" spans="7:14">
@@ -3973,8 +4000,11 @@
       <c r="I18" t="s">
         <v>54</v>
       </c>
+      <c r="M18" t="s">
+        <v>143</v>
+      </c>
       <c r="N18" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19" spans="7:14">
@@ -3985,7 +4015,7 @@
         <v>105</v>
       </c>
       <c r="N19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="7:14">
@@ -3996,7 +4026,7 @@
         <v>106</v>
       </c>
       <c r="N20" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21" spans="7:14">
@@ -4007,7 +4037,7 @@
         <v>107</v>
       </c>
       <c r="N21" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22" spans="7:14">
@@ -4018,7 +4048,7 @@
         <v>108</v>
       </c>
       <c r="N22" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="7:14">
@@ -4029,7 +4059,7 @@
         <v>109</v>
       </c>
       <c r="N23" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24" spans="7:14">
@@ -4040,7 +4070,7 @@
         <v>110</v>
       </c>
       <c r="N24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="7:14">
@@ -4051,7 +4081,7 @@
         <v>111</v>
       </c>
       <c r="N25" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26" spans="7:14">
@@ -4062,7 +4092,7 @@
         <v>112</v>
       </c>
       <c r="N26" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="7:14">
@@ -4073,7 +4103,7 @@
         <v>113</v>
       </c>
       <c r="N27" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="7:14">
@@ -4084,7 +4114,7 @@
         <v>114</v>
       </c>
       <c r="N28" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="7:14">
@@ -4095,7 +4125,7 @@
         <v>115</v>
       </c>
       <c r="N29" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="7:14">
@@ -4106,7 +4136,7 @@
         <v>116</v>
       </c>
       <c r="N30" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="7:14">
@@ -4117,7 +4147,7 @@
         <v>117</v>
       </c>
       <c r="N31" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="7:14">
@@ -4125,7 +4155,7 @@
         <v>66</v>
       </c>
       <c r="N32" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" spans="7:14">
@@ -4133,7 +4163,7 @@
         <v>67</v>
       </c>
       <c r="N33" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34" spans="7:14">
@@ -4141,7 +4171,7 @@
         <v>68</v>
       </c>
       <c r="N34" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35" spans="7:14">
@@ -4149,7 +4179,7 @@
         <v>69</v>
       </c>
       <c r="N35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="7:14">
@@ -4157,7 +4187,7 @@
         <v>70</v>
       </c>
       <c r="N36" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37" spans="7:14">
@@ -4165,7 +4195,7 @@
         <v>71</v>
       </c>
       <c r="N37" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="38" spans="7:14">
@@ -4173,7 +4203,7 @@
         <v>72</v>
       </c>
       <c r="N38" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="39" spans="7:14">
@@ -4181,7 +4211,7 @@
         <v>73</v>
       </c>
       <c r="N39" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="40" spans="7:14">
@@ -4189,7 +4219,7 @@
         <v>74</v>
       </c>
       <c r="N40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="41" spans="7:14">
@@ -4197,236 +4227,241 @@
         <v>75</v>
       </c>
       <c r="N41" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42" spans="7:14">
       <c r="N42" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="43" spans="7:14">
       <c r="N43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" spans="7:14">
       <c r="N44" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="45" spans="7:14">
       <c r="N45" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="46" spans="7:14">
       <c r="N46" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="47" spans="7:14">
       <c r="N47" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="48" spans="7:14">
       <c r="N48" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="49" spans="14:14">
       <c r="N49" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="50" spans="14:14">
       <c r="N50" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="51" spans="14:14">
       <c r="N51" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="52" spans="14:14">
       <c r="N52" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="53" spans="14:14">
       <c r="N53" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="54" spans="14:14">
       <c r="N54" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="55" spans="14:14">
       <c r="N55" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="56" spans="14:14">
       <c r="N56" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="57" spans="14:14">
       <c r="N57" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="58" spans="14:14">
       <c r="N58" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="59" spans="14:14">
       <c r="N59" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="60" spans="14:14">
       <c r="N60" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="61" spans="14:14">
       <c r="N61" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="62" spans="14:14">
       <c r="N62" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="63" spans="14:14">
       <c r="N63" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="64" spans="14:14">
       <c r="N64" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="65" spans="14:14">
       <c r="N65" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="66" spans="14:14">
       <c r="N66" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="67" spans="14:14">
       <c r="N67" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="68" spans="14:14">
       <c r="N68" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="69" spans="14:14">
       <c r="N69" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="70" spans="14:14">
       <c r="N70" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="71" spans="14:14">
       <c r="N71" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="72" spans="14:14">
       <c r="N72" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="73" spans="14:14">
       <c r="N73" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="74" spans="14:14">
       <c r="N74" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="75" spans="14:14">
       <c r="N75" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="76" spans="14:14">
       <c r="N76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="77" spans="14:14">
       <c r="N77" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="78" spans="14:14">
       <c r="N78" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="79" spans="14:14">
       <c r="N79" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="80" spans="14:14">
       <c r="N80" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="81" spans="14:14">
       <c r="N81" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="82" spans="14:14">
       <c r="N82" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="83" spans="14:14">
       <c r="N83" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="84" spans="14:14">
       <c r="N84" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="85" spans="14:14">
       <c r="N85" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="86" spans="14:14">
       <c r="N86" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="87" spans="14:14">
       <c r="N87" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="88" spans="14:14">
+      <c r="N88" t="s">
         <v>117</v>
       </c>
     </row>
@@ -4448,27 +4483,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -4488,122 +4523,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -4613,13 +4648,13 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:FY2"/>
+  <dimension ref="A1:FZ2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="301" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:181">
+    <row r="1" spans="1:182">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4627,1124 +4662,1130 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>302</v>
+        <v>274</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>369</v>
+        <v>339</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="Z1" s="1" t="s">
         <v>383</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="AY1" s="1" t="s">
         <v>438</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="BK1" s="1" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="BM1" s="1" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="BN1" s="1" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="BO1" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="BP1" s="1" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="BQ1" s="1" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>765</v>
+        <v>478</v>
       </c>
       <c r="BS1" s="1" t="s">
-        <v>767</v>
+        <v>774</v>
       </c>
       <c r="BT1" s="1" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="BU1" s="1" t="s">
-        <v>771</v>
+        <v>778</v>
       </c>
       <c r="BV1" s="1" t="s">
-        <v>773</v>
+        <v>780</v>
       </c>
       <c r="BW1" s="1" t="s">
-        <v>775</v>
+        <v>782</v>
       </c>
       <c r="BX1" s="1" t="s">
-        <v>777</v>
+        <v>784</v>
       </c>
       <c r="BY1" s="1" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="BZ1" s="1" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
       <c r="CA1" s="1" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="CB1" s="1" t="s">
-        <v>785</v>
+        <v>792</v>
       </c>
       <c r="CC1" s="1" t="s">
-        <v>787</v>
+        <v>794</v>
       </c>
       <c r="CD1" s="1" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
       <c r="CE1" s="1" t="s">
-        <v>791</v>
+        <v>798</v>
       </c>
       <c r="CF1" s="1" t="s">
-        <v>793</v>
+        <v>800</v>
       </c>
       <c r="CG1" s="1" t="s">
-        <v>795</v>
+        <v>802</v>
       </c>
       <c r="CH1" s="1" t="s">
-        <v>797</v>
+        <v>804</v>
       </c>
       <c r="CI1" s="1" t="s">
-        <v>799</v>
+        <v>806</v>
       </c>
       <c r="CJ1" s="1" t="s">
-        <v>801</v>
+        <v>808</v>
       </c>
       <c r="CK1" s="1" t="s">
-        <v>803</v>
+        <v>810</v>
       </c>
       <c r="CL1" s="1" t="s">
-        <v>805</v>
+        <v>812</v>
       </c>
       <c r="CM1" s="1" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="CN1" s="1" t="s">
-        <v>815</v>
+        <v>822</v>
       </c>
       <c r="CO1" s="1" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="CP1" s="1" t="s">
-        <v>825</v>
+        <v>832</v>
       </c>
       <c r="CQ1" s="1" t="s">
-        <v>827</v>
+        <v>834</v>
       </c>
       <c r="CR1" s="1" t="s">
-        <v>829</v>
+        <v>836</v>
       </c>
       <c r="CS1" s="1" t="s">
-        <v>831</v>
+        <v>838</v>
       </c>
       <c r="CT1" s="1" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="CU1" s="1" t="s">
-        <v>840</v>
+        <v>847</v>
       </c>
       <c r="CV1" s="1" t="s">
-        <v>842</v>
+        <v>849</v>
       </c>
       <c r="CW1" s="1" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
       <c r="CX1" s="1" t="s">
-        <v>846</v>
+        <v>853</v>
       </c>
       <c r="CY1" s="1" t="s">
-        <v>848</v>
+        <v>855</v>
       </c>
       <c r="CZ1" s="1" t="s">
-        <v>850</v>
+        <v>857</v>
       </c>
       <c r="DA1" s="1" t="s">
-        <v>852</v>
+        <v>859</v>
       </c>
       <c r="DB1" s="1" t="s">
-        <v>854</v>
+        <v>861</v>
       </c>
       <c r="DC1" s="1" t="s">
-        <v>856</v>
+        <v>863</v>
       </c>
       <c r="DD1" s="1" t="s">
-        <v>858</v>
+        <v>865</v>
       </c>
       <c r="DE1" s="1" t="s">
-        <v>860</v>
+        <v>867</v>
       </c>
       <c r="DF1" s="1" t="s">
-        <v>862</v>
+        <v>869</v>
       </c>
       <c r="DG1" s="1" t="s">
-        <v>864</v>
+        <v>871</v>
       </c>
       <c r="DH1" s="1" t="s">
-        <v>866</v>
+        <v>873</v>
       </c>
       <c r="DI1" s="1" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="DJ1" s="1" t="s">
-        <v>879</v>
+        <v>886</v>
       </c>
       <c r="DK1" s="1" t="s">
-        <v>881</v>
+        <v>888</v>
       </c>
       <c r="DL1" s="1" t="s">
-        <v>883</v>
+        <v>890</v>
       </c>
       <c r="DM1" s="1" t="s">
-        <v>885</v>
+        <v>892</v>
       </c>
       <c r="DN1" s="1" t="s">
-        <v>887</v>
+        <v>894</v>
       </c>
       <c r="DO1" s="1" t="s">
-        <v>889</v>
+        <v>896</v>
       </c>
       <c r="DP1" s="1" t="s">
-        <v>891</v>
+        <v>898</v>
       </c>
       <c r="DQ1" s="1" t="s">
-        <v>893</v>
+        <v>900</v>
       </c>
       <c r="DR1" s="1" t="s">
-        <v>895</v>
+        <v>902</v>
       </c>
       <c r="DS1" s="1" t="s">
-        <v>897</v>
+        <v>904</v>
       </c>
       <c r="DT1" s="1" t="s">
-        <v>899</v>
+        <v>906</v>
       </c>
       <c r="DU1" s="1" t="s">
-        <v>901</v>
+        <v>908</v>
       </c>
       <c r="DV1" s="1" t="s">
-        <v>903</v>
+        <v>910</v>
       </c>
       <c r="DW1" s="1" t="s">
-        <v>905</v>
+        <v>912</v>
       </c>
       <c r="DX1" s="1" t="s">
-        <v>907</v>
+        <v>914</v>
       </c>
       <c r="DY1" s="1" t="s">
-        <v>909</v>
+        <v>916</v>
       </c>
       <c r="DZ1" s="1" t="s">
-        <v>911</v>
+        <v>918</v>
       </c>
       <c r="EA1" s="1" t="s">
-        <v>913</v>
+        <v>920</v>
       </c>
       <c r="EB1" s="1" t="s">
-        <v>915</v>
+        <v>922</v>
       </c>
       <c r="EC1" s="1" t="s">
-        <v>917</v>
+        <v>924</v>
       </c>
       <c r="ED1" s="1" t="s">
-        <v>919</v>
+        <v>926</v>
       </c>
       <c r="EE1" s="1" t="s">
-        <v>921</v>
+        <v>928</v>
       </c>
       <c r="EF1" s="1" t="s">
-        <v>923</v>
+        <v>930</v>
       </c>
       <c r="EG1" s="1" t="s">
-        <v>925</v>
+        <v>932</v>
       </c>
       <c r="EH1" s="1" t="s">
-        <v>927</v>
+        <v>934</v>
       </c>
       <c r="EI1" s="1" t="s">
-        <v>929</v>
+        <v>936</v>
       </c>
       <c r="EJ1" s="1" t="s">
-        <v>931</v>
+        <v>938</v>
       </c>
       <c r="EK1" s="1" t="s">
-        <v>933</v>
+        <v>940</v>
       </c>
       <c r="EL1" s="1" t="s">
-        <v>935</v>
+        <v>942</v>
       </c>
       <c r="EM1" s="1" t="s">
-        <v>937</v>
+        <v>944</v>
       </c>
       <c r="EN1" s="1" t="s">
-        <v>939</v>
+        <v>946</v>
       </c>
       <c r="EO1" s="1" t="s">
-        <v>941</v>
+        <v>948</v>
       </c>
       <c r="EP1" s="1" t="s">
-        <v>943</v>
+        <v>950</v>
       </c>
       <c r="EQ1" s="1" t="s">
-        <v>949</v>
+        <v>952</v>
       </c>
       <c r="ER1" s="1" t="s">
-        <v>951</v>
+        <v>958</v>
       </c>
       <c r="ES1" s="1" t="s">
-        <v>953</v>
+        <v>960</v>
       </c>
       <c r="ET1" s="1" t="s">
-        <v>955</v>
+        <v>962</v>
       </c>
       <c r="EU1" s="1" t="s">
-        <v>957</v>
+        <v>964</v>
       </c>
       <c r="EV1" s="1" t="s">
-        <v>959</v>
+        <v>966</v>
       </c>
       <c r="EW1" s="1" t="s">
-        <v>961</v>
+        <v>968</v>
       </c>
       <c r="EX1" s="1" t="s">
-        <v>963</v>
+        <v>970</v>
       </c>
       <c r="EY1" s="1" t="s">
-        <v>965</v>
+        <v>972</v>
       </c>
       <c r="EZ1" s="1" t="s">
-        <v>967</v>
+        <v>974</v>
       </c>
       <c r="FA1" s="1" t="s">
-        <v>969</v>
+        <v>976</v>
       </c>
       <c r="FB1" s="1" t="s">
-        <v>971</v>
+        <v>978</v>
       </c>
       <c r="FC1" s="1" t="s">
-        <v>973</v>
+        <v>980</v>
       </c>
       <c r="FD1" s="1" t="s">
-        <v>975</v>
+        <v>982</v>
       </c>
       <c r="FE1" s="1" t="s">
-        <v>977</v>
+        <v>984</v>
       </c>
       <c r="FF1" s="1" t="s">
-        <v>979</v>
+        <v>986</v>
       </c>
       <c r="FG1" s="1" t="s">
-        <v>981</v>
+        <v>988</v>
       </c>
       <c r="FH1" s="1" t="s">
-        <v>983</v>
+        <v>990</v>
       </c>
       <c r="FI1" s="1" t="s">
-        <v>985</v>
+        <v>992</v>
       </c>
       <c r="FJ1" s="1" t="s">
-        <v>987</v>
+        <v>994</v>
       </c>
       <c r="FK1" s="1" t="s">
-        <v>989</v>
+        <v>996</v>
       </c>
       <c r="FL1" s="1" t="s">
-        <v>991</v>
+        <v>998</v>
       </c>
       <c r="FM1" s="1" t="s">
-        <v>993</v>
+        <v>1000</v>
       </c>
       <c r="FN1" s="1" t="s">
-        <v>995</v>
+        <v>1002</v>
       </c>
       <c r="FO1" s="1" t="s">
-        <v>997</v>
+        <v>1004</v>
       </c>
       <c r="FP1" s="1" t="s">
-        <v>999</v>
+        <v>1006</v>
       </c>
       <c r="FQ1" s="1" t="s">
-        <v>1001</v>
+        <v>1008</v>
       </c>
       <c r="FR1" s="1" t="s">
-        <v>1003</v>
+        <v>1010</v>
       </c>
       <c r="FS1" s="1" t="s">
-        <v>1005</v>
+        <v>1012</v>
       </c>
       <c r="FT1" s="1" t="s">
-        <v>1007</v>
+        <v>1014</v>
       </c>
       <c r="FU1" s="1" t="s">
-        <v>1009</v>
+        <v>1016</v>
       </c>
       <c r="FV1" s="1" t="s">
-        <v>1011</v>
+        <v>1018</v>
       </c>
       <c r="FW1" s="1" t="s">
-        <v>1013</v>
+        <v>1020</v>
       </c>
       <c r="FX1" s="1" t="s">
-        <v>1015</v>
+        <v>1022</v>
       </c>
       <c r="FY1" s="1" t="s">
-        <v>1017</v>
-      </c>
-    </row>
-    <row r="2" spans="1:181" ht="150" customHeight="1">
+        <v>1024</v>
+      </c>
+      <c r="FZ1" s="1" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:182" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>303</v>
+        <v>275</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>370</v>
+        <v>340</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="Z2" s="2" t="s">
         <v>384</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AP2" s="2" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AQ2" s="2" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AR2" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AS2" s="2" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AU2" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AV2" s="2" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AW2" s="2" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AX2" s="2" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AY2" s="2" t="s">
         <v>439</v>
       </c>
       <c r="AZ2" s="2" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="BA2" s="2" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="BB2" s="2" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="BC2" s="2" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="BD2" s="2" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="BE2" s="2" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="BF2" s="2" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="BG2" s="2" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="BH2" s="2" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="BI2" s="2" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="BJ2" s="2" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="BK2" s="2" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="BL2" s="2" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="BM2" s="2" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="BN2" s="2" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="BO2" s="2" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="BP2" s="2" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="BQ2" s="2" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="BR2" s="2" t="s">
-        <v>766</v>
+        <v>479</v>
       </c>
       <c r="BS2" s="2" t="s">
-        <v>768</v>
+        <v>775</v>
       </c>
       <c r="BT2" s="2" t="s">
-        <v>770</v>
+        <v>777</v>
       </c>
       <c r="BU2" s="2" t="s">
-        <v>772</v>
+        <v>779</v>
       </c>
       <c r="BV2" s="2" t="s">
-        <v>774</v>
+        <v>781</v>
       </c>
       <c r="BW2" s="2" t="s">
-        <v>776</v>
+        <v>783</v>
       </c>
       <c r="BX2" s="2" t="s">
-        <v>778</v>
+        <v>785</v>
       </c>
       <c r="BY2" s="2" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="BZ2" s="2" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="CA2" s="2" t="s">
-        <v>784</v>
+        <v>791</v>
       </c>
       <c r="CB2" s="2" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="CC2" s="2" t="s">
-        <v>788</v>
+        <v>795</v>
       </c>
       <c r="CD2" s="2" t="s">
-        <v>790</v>
+        <v>797</v>
       </c>
       <c r="CE2" s="2" t="s">
-        <v>792</v>
+        <v>799</v>
       </c>
       <c r="CF2" s="2" t="s">
-        <v>794</v>
+        <v>801</v>
       </c>
       <c r="CG2" s="2" t="s">
-        <v>796</v>
+        <v>803</v>
       </c>
       <c r="CH2" s="2" t="s">
-        <v>798</v>
+        <v>805</v>
       </c>
       <c r="CI2" s="2" t="s">
-        <v>800</v>
+        <v>807</v>
       </c>
       <c r="CJ2" s="2" t="s">
-        <v>802</v>
+        <v>809</v>
       </c>
       <c r="CK2" s="2" t="s">
-        <v>804</v>
+        <v>811</v>
       </c>
       <c r="CL2" s="2" t="s">
-        <v>806</v>
+        <v>813</v>
       </c>
       <c r="CM2" s="2" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="CN2" s="2" t="s">
-        <v>816</v>
+        <v>823</v>
       </c>
       <c r="CO2" s="2" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="CP2" s="2" t="s">
-        <v>826</v>
+        <v>833</v>
       </c>
       <c r="CQ2" s="2" t="s">
-        <v>828</v>
+        <v>835</v>
       </c>
       <c r="CR2" s="2" t="s">
-        <v>830</v>
+        <v>837</v>
       </c>
       <c r="CS2" s="2" t="s">
-        <v>832</v>
+        <v>839</v>
       </c>
       <c r="CT2" s="2" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="CU2" s="2" t="s">
-        <v>841</v>
+        <v>848</v>
       </c>
       <c r="CV2" s="2" t="s">
-        <v>843</v>
+        <v>850</v>
       </c>
       <c r="CW2" s="2" t="s">
-        <v>845</v>
+        <v>852</v>
       </c>
       <c r="CX2" s="2" t="s">
-        <v>847</v>
+        <v>854</v>
       </c>
       <c r="CY2" s="2" t="s">
-        <v>849</v>
+        <v>856</v>
       </c>
       <c r="CZ2" s="2" t="s">
-        <v>851</v>
+        <v>858</v>
       </c>
       <c r="DA2" s="2" t="s">
-        <v>853</v>
+        <v>860</v>
       </c>
       <c r="DB2" s="2" t="s">
-        <v>855</v>
+        <v>862</v>
       </c>
       <c r="DC2" s="2" t="s">
-        <v>857</v>
+        <v>864</v>
       </c>
       <c r="DD2" s="2" t="s">
-        <v>859</v>
+        <v>866</v>
       </c>
       <c r="DE2" s="2" t="s">
-        <v>861</v>
+        <v>868</v>
       </c>
       <c r="DF2" s="2" t="s">
-        <v>863</v>
+        <v>870</v>
       </c>
       <c r="DG2" s="2" t="s">
-        <v>865</v>
+        <v>872</v>
       </c>
       <c r="DH2" s="2" t="s">
-        <v>867</v>
+        <v>874</v>
       </c>
       <c r="DI2" s="2" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="DJ2" s="2" t="s">
-        <v>880</v>
+        <v>887</v>
       </c>
       <c r="DK2" s="2" t="s">
-        <v>882</v>
+        <v>889</v>
       </c>
       <c r="DL2" s="2" t="s">
-        <v>884</v>
+        <v>891</v>
       </c>
       <c r="DM2" s="2" t="s">
-        <v>886</v>
+        <v>893</v>
       </c>
       <c r="DN2" s="2" t="s">
-        <v>888</v>
+        <v>895</v>
       </c>
       <c r="DO2" s="2" t="s">
-        <v>890</v>
+        <v>897</v>
       </c>
       <c r="DP2" s="2" t="s">
-        <v>892</v>
+        <v>899</v>
       </c>
       <c r="DQ2" s="2" t="s">
-        <v>894</v>
+        <v>901</v>
       </c>
       <c r="DR2" s="2" t="s">
-        <v>896</v>
+        <v>903</v>
       </c>
       <c r="DS2" s="2" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="DT2" s="2" t="s">
-        <v>900</v>
+        <v>907</v>
       </c>
       <c r="DU2" s="2" t="s">
-        <v>902</v>
+        <v>909</v>
       </c>
       <c r="DV2" s="2" t="s">
-        <v>904</v>
+        <v>911</v>
       </c>
       <c r="DW2" s="2" t="s">
-        <v>906</v>
+        <v>913</v>
       </c>
       <c r="DX2" s="2" t="s">
-        <v>908</v>
+        <v>915</v>
       </c>
       <c r="DY2" s="2" t="s">
-        <v>910</v>
+        <v>917</v>
       </c>
       <c r="DZ2" s="2" t="s">
-        <v>912</v>
+        <v>919</v>
       </c>
       <c r="EA2" s="2" t="s">
-        <v>914</v>
+        <v>921</v>
       </c>
       <c r="EB2" s="2" t="s">
-        <v>916</v>
+        <v>923</v>
       </c>
       <c r="EC2" s="2" t="s">
-        <v>918</v>
+        <v>925</v>
       </c>
       <c r="ED2" s="2" t="s">
-        <v>920</v>
+        <v>927</v>
       </c>
       <c r="EE2" s="2" t="s">
-        <v>922</v>
+        <v>929</v>
       </c>
       <c r="EF2" s="2" t="s">
-        <v>924</v>
+        <v>931</v>
       </c>
       <c r="EG2" s="2" t="s">
-        <v>926</v>
+        <v>933</v>
       </c>
       <c r="EH2" s="2" t="s">
-        <v>928</v>
+        <v>935</v>
       </c>
       <c r="EI2" s="2" t="s">
-        <v>930</v>
+        <v>937</v>
       </c>
       <c r="EJ2" s="2" t="s">
-        <v>932</v>
+        <v>939</v>
       </c>
       <c r="EK2" s="2" t="s">
-        <v>934</v>
+        <v>941</v>
       </c>
       <c r="EL2" s="2" t="s">
-        <v>936</v>
+        <v>943</v>
       </c>
       <c r="EM2" s="2" t="s">
-        <v>938</v>
+        <v>945</v>
       </c>
       <c r="EN2" s="2" t="s">
-        <v>940</v>
+        <v>947</v>
       </c>
       <c r="EO2" s="2" t="s">
-        <v>942</v>
+        <v>949</v>
       </c>
       <c r="EP2" s="2" t="s">
-        <v>944</v>
+        <v>951</v>
       </c>
       <c r="EQ2" s="2" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="ER2" s="2" t="s">
-        <v>952</v>
+        <v>959</v>
       </c>
       <c r="ES2" s="2" t="s">
-        <v>954</v>
+        <v>961</v>
       </c>
       <c r="ET2" s="2" t="s">
-        <v>956</v>
+        <v>963</v>
       </c>
       <c r="EU2" s="2" t="s">
-        <v>958</v>
+        <v>965</v>
       </c>
       <c r="EV2" s="2" t="s">
-        <v>960</v>
+        <v>967</v>
       </c>
       <c r="EW2" s="2" t="s">
-        <v>962</v>
+        <v>969</v>
       </c>
       <c r="EX2" s="2" t="s">
-        <v>964</v>
+        <v>971</v>
       </c>
       <c r="EY2" s="2" t="s">
-        <v>966</v>
+        <v>973</v>
       </c>
       <c r="EZ2" s="2" t="s">
-        <v>968</v>
+        <v>975</v>
       </c>
       <c r="FA2" s="2" t="s">
-        <v>970</v>
+        <v>977</v>
       </c>
       <c r="FB2" s="2" t="s">
-        <v>972</v>
+        <v>979</v>
       </c>
       <c r="FC2" s="2" t="s">
-        <v>974</v>
+        <v>981</v>
       </c>
       <c r="FD2" s="2" t="s">
-        <v>976</v>
+        <v>983</v>
       </c>
       <c r="FE2" s="2" t="s">
-        <v>978</v>
+        <v>985</v>
       </c>
       <c r="FF2" s="2" t="s">
-        <v>980</v>
+        <v>987</v>
       </c>
       <c r="FG2" s="2" t="s">
-        <v>982</v>
+        <v>989</v>
       </c>
       <c r="FH2" s="2" t="s">
-        <v>984</v>
+        <v>991</v>
       </c>
       <c r="FI2" s="2" t="s">
-        <v>986</v>
+        <v>993</v>
       </c>
       <c r="FJ2" s="2" t="s">
-        <v>988</v>
+        <v>995</v>
       </c>
       <c r="FK2" s="2" t="s">
-        <v>990</v>
+        <v>997</v>
       </c>
       <c r="FL2" s="2" t="s">
-        <v>992</v>
+        <v>999</v>
       </c>
       <c r="FM2" s="2" t="s">
-        <v>994</v>
+        <v>1001</v>
       </c>
       <c r="FN2" s="2" t="s">
-        <v>996</v>
+        <v>1003</v>
       </c>
       <c r="FO2" s="2" t="s">
-        <v>998</v>
+        <v>1005</v>
       </c>
       <c r="FP2" s="2" t="s">
-        <v>1000</v>
+        <v>1007</v>
       </c>
       <c r="FQ2" s="2" t="s">
-        <v>1002</v>
+        <v>1009</v>
       </c>
       <c r="FR2" s="2" t="s">
-        <v>1004</v>
+        <v>1011</v>
       </c>
       <c r="FS2" s="2" t="s">
-        <v>1006</v>
+        <v>1013</v>
       </c>
       <c r="FT2" s="2" t="s">
-        <v>1008</v>
+        <v>1015</v>
       </c>
       <c r="FU2" s="2" t="s">
-        <v>1010</v>
+        <v>1017</v>
       </c>
       <c r="FV2" s="2" t="s">
-        <v>1012</v>
+        <v>1019</v>
       </c>
       <c r="FW2" s="2" t="s">
-        <v>1014</v>
+        <v>1021</v>
       </c>
       <c r="FX2" s="2" t="s">
-        <v>1016</v>
+        <v>1023</v>
       </c>
       <c r="FY2" s="2" t="s">
-        <v>1018</v>
+        <v>1025</v>
+      </c>
+      <c r="FZ2" s="2" t="s">
+        <v>1027</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="12">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G101">
       <formula1>trophiclevel</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I3:I101">
       <formula1>relationshiptooxygen</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T3:T101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U3:U101">
       <formula1>soiltype</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z3:Z101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA3:AA101">
       <formula1>oxygenationstatusofsample</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AU3:AU101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AV3:AV101">
       <formula1>sequencequalitycheck</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AY3:AY101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AZ3:AZ101">
       <formula1>16srecovered</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BR3:BR101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BS3:BS101">
       <formula1>geographiclocationcountryandorsea</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CM3:CM101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CN3:CN101">
       <formula1>soilhorizon</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CO3:CO101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CP3:CP101">
       <formula1>drainageclassification</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CT3:CT101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CU3:CU101">
       <formula1>profileposition</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="DI3:DI101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="DJ3:DJ101">
       <formula1>historytillage</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="EQ3:EQ101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="ER3:ER101">
       <formula1>singlecellorviralparticlelysisapproach</formula1>
     </dataValidation>
   </dataValidations>
@@ -5754,1770 +5795,1795 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="F1:EQ289"/>
+  <dimension ref="G1:ER294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="6:147">
-      <c r="F1" t="s">
-        <v>272</v>
-      </c>
-      <c r="H1" t="s">
-        <v>306</v>
-      </c>
-      <c r="T1" t="s">
-        <v>337</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>381</v>
-      </c>
-      <c r="AU1" t="s">
-        <v>425</v>
-      </c>
-      <c r="AY1" t="s">
-        <v>436</v>
-      </c>
-      <c r="BR1" t="s">
-        <v>476</v>
-      </c>
-      <c r="CM1" t="s">
-        <v>807</v>
-      </c>
-      <c r="CO1" t="s">
+    <row r="1" spans="7:148">
+      <c r="G1" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1" t="s">
+        <v>310</v>
+      </c>
+      <c r="U1" t="s">
+        <v>341</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>385</v>
+      </c>
+      <c r="AV1" t="s">
+        <v>429</v>
+      </c>
+      <c r="AZ1" t="s">
+        <v>440</v>
+      </c>
+      <c r="BS1" t="s">
+        <v>480</v>
+      </c>
+      <c r="CN1" t="s">
+        <v>816</v>
+      </c>
+      <c r="CP1" t="s">
+        <v>826</v>
+      </c>
+      <c r="CU1" t="s">
+        <v>842</v>
+      </c>
+      <c r="DJ1" t="s">
+        <v>877</v>
+      </c>
+      <c r="ER1" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="2" spans="7:148">
+      <c r="G2" t="s">
+        <v>277</v>
+      </c>
+      <c r="I2" t="s">
+        <v>311</v>
+      </c>
+      <c r="U2" t="s">
+        <v>342</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>386</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>430</v>
+      </c>
+      <c r="AZ2" t="s">
+        <v>441</v>
+      </c>
+      <c r="BS2" t="s">
+        <v>481</v>
+      </c>
+      <c r="CN2" t="s">
         <v>817</v>
       </c>
-      <c r="CT1" t="s">
-        <v>833</v>
-      </c>
-      <c r="DI1" t="s">
-        <v>868</v>
-      </c>
-      <c r="EQ1" t="s">
-        <v>945</v>
-      </c>
-    </row>
-    <row r="2" spans="6:147">
-      <c r="F2" t="s">
-        <v>273</v>
-      </c>
-      <c r="H2" t="s">
-        <v>307</v>
-      </c>
-      <c r="T2" t="s">
-        <v>338</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>382</v>
-      </c>
-      <c r="AU2" t="s">
-        <v>426</v>
-      </c>
-      <c r="AY2" t="s">
-        <v>437</v>
-      </c>
-      <c r="BR2" t="s">
-        <v>477</v>
-      </c>
-      <c r="CM2" t="s">
-        <v>808</v>
-      </c>
-      <c r="CO2" t="s">
+      <c r="CP2" t="s">
+        <v>827</v>
+      </c>
+      <c r="CU2" t="s">
+        <v>843</v>
+      </c>
+      <c r="DJ2" t="s">
+        <v>878</v>
+      </c>
+      <c r="ER2" t="s">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="3" spans="7:148">
+      <c r="G3" t="s">
+        <v>278</v>
+      </c>
+      <c r="I3" t="s">
+        <v>312</v>
+      </c>
+      <c r="U3" t="s">
+        <v>343</v>
+      </c>
+      <c r="AV3" t="s">
+        <v>431</v>
+      </c>
+      <c r="BS3" t="s">
+        <v>482</v>
+      </c>
+      <c r="CN3" t="s">
         <v>818</v>
       </c>
-      <c r="CT2" t="s">
-        <v>834</v>
-      </c>
-      <c r="DI2" t="s">
-        <v>869</v>
-      </c>
-      <c r="EQ2" t="s">
-        <v>946</v>
-      </c>
-    </row>
-    <row r="3" spans="6:147">
-      <c r="F3" t="s">
-        <v>274</v>
-      </c>
-      <c r="H3" t="s">
-        <v>308</v>
-      </c>
-      <c r="T3" t="s">
-        <v>339</v>
-      </c>
-      <c r="AU3" t="s">
-        <v>427</v>
-      </c>
-      <c r="BR3" t="s">
-        <v>478</v>
-      </c>
-      <c r="CM3" t="s">
-        <v>809</v>
-      </c>
-      <c r="CO3" t="s">
+      <c r="CP3" t="s">
+        <v>828</v>
+      </c>
+      <c r="CU3" t="s">
+        <v>844</v>
+      </c>
+      <c r="DJ3" t="s">
+        <v>879</v>
+      </c>
+      <c r="ER3" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="4" spans="7:148">
+      <c r="G4" t="s">
+        <v>279</v>
+      </c>
+      <c r="I4" t="s">
+        <v>313</v>
+      </c>
+      <c r="U4" t="s">
+        <v>344</v>
+      </c>
+      <c r="BS4" t="s">
+        <v>483</v>
+      </c>
+      <c r="CN4" t="s">
         <v>819</v>
       </c>
-      <c r="CT3" t="s">
-        <v>835</v>
-      </c>
-      <c r="DI3" t="s">
-        <v>870</v>
-      </c>
-      <c r="EQ3" t="s">
-        <v>947</v>
-      </c>
-    </row>
-    <row r="4" spans="6:147">
-      <c r="F4" t="s">
-        <v>275</v>
-      </c>
-      <c r="H4" t="s">
-        <v>309</v>
-      </c>
-      <c r="T4" t="s">
-        <v>340</v>
-      </c>
-      <c r="BR4" t="s">
-        <v>479</v>
-      </c>
-      <c r="CM4" t="s">
-        <v>810</v>
-      </c>
-      <c r="CO4" t="s">
+      <c r="CP4" t="s">
+        <v>829</v>
+      </c>
+      <c r="CU4" t="s">
+        <v>845</v>
+      </c>
+      <c r="DJ4" t="s">
+        <v>880</v>
+      </c>
+      <c r="ER4" t="s">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="5" spans="7:148">
+      <c r="G5" t="s">
+        <v>280</v>
+      </c>
+      <c r="I5" t="s">
+        <v>314</v>
+      </c>
+      <c r="U5" t="s">
+        <v>345</v>
+      </c>
+      <c r="BS5" t="s">
+        <v>484</v>
+      </c>
+      <c r="CN5" t="s">
         <v>820</v>
       </c>
-      <c r="CT4" t="s">
-        <v>836</v>
-      </c>
-      <c r="DI4" t="s">
-        <v>871</v>
-      </c>
-      <c r="EQ4" t="s">
-        <v>948</v>
-      </c>
-    </row>
-    <row r="5" spans="6:147">
-      <c r="F5" t="s">
-        <v>276</v>
-      </c>
-      <c r="H5" t="s">
-        <v>310</v>
-      </c>
-      <c r="T5" t="s">
-        <v>341</v>
-      </c>
-      <c r="BR5" t="s">
-        <v>480</v>
-      </c>
-      <c r="CM5" t="s">
-        <v>811</v>
-      </c>
-      <c r="CO5" t="s">
+      <c r="CP5" t="s">
+        <v>830</v>
+      </c>
+      <c r="CU5" t="s">
+        <v>846</v>
+      </c>
+      <c r="DJ5" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="6" spans="7:148">
+      <c r="G6" t="s">
+        <v>281</v>
+      </c>
+      <c r="I6" t="s">
+        <v>315</v>
+      </c>
+      <c r="U6" t="s">
+        <v>346</v>
+      </c>
+      <c r="BS6" t="s">
+        <v>485</v>
+      </c>
+      <c r="CN6" t="s">
         <v>821</v>
       </c>
-      <c r="CT5" t="s">
-        <v>837</v>
-      </c>
-      <c r="DI5" t="s">
-        <v>872</v>
-      </c>
-    </row>
-    <row r="6" spans="6:147">
-      <c r="F6" t="s">
-        <v>277</v>
-      </c>
-      <c r="H6" t="s">
-        <v>311</v>
-      </c>
-      <c r="T6" t="s">
-        <v>342</v>
-      </c>
-      <c r="BR6" t="s">
-        <v>481</v>
-      </c>
-      <c r="CM6" t="s">
-        <v>812</v>
-      </c>
-      <c r="CO6" t="s">
-        <v>822</v>
-      </c>
-      <c r="DI6" t="s">
-        <v>873</v>
-      </c>
-    </row>
-    <row r="7" spans="6:147">
-      <c r="F7" t="s">
-        <v>278</v>
-      </c>
-      <c r="H7" t="s">
-        <v>312</v>
-      </c>
-      <c r="T7" t="s">
-        <v>343</v>
-      </c>
-      <c r="BR7" t="s">
-        <v>482</v>
-      </c>
-      <c r="DI7" t="s">
-        <v>874</v>
-      </c>
-    </row>
-    <row r="8" spans="6:147">
-      <c r="F8" t="s">
-        <v>279</v>
-      </c>
-      <c r="T8" t="s">
-        <v>344</v>
-      </c>
-      <c r="BR8" t="s">
-        <v>483</v>
-      </c>
-      <c r="DI8" t="s">
-        <v>875</v>
-      </c>
-    </row>
-    <row r="9" spans="6:147">
-      <c r="F9" t="s">
-        <v>280</v>
-      </c>
-      <c r="T9" t="s">
-        <v>345</v>
-      </c>
-      <c r="BR9" t="s">
-        <v>484</v>
-      </c>
-      <c r="DI9" t="s">
-        <v>876</v>
-      </c>
-    </row>
-    <row r="10" spans="6:147">
-      <c r="F10" t="s">
-        <v>281</v>
-      </c>
-      <c r="T10" t="s">
-        <v>346</v>
-      </c>
-      <c r="BR10" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="11" spans="6:147">
-      <c r="F11" t="s">
+      <c r="CP6" t="s">
+        <v>831</v>
+      </c>
+      <c r="DJ6" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="7" spans="7:148">
+      <c r="G7" t="s">
         <v>282</v>
       </c>
-      <c r="T11" t="s">
+      <c r="I7" t="s">
+        <v>316</v>
+      </c>
+      <c r="U7" t="s">
         <v>347</v>
       </c>
-      <c r="BR11" t="s">
+      <c r="BS7" t="s">
         <v>486</v>
       </c>
-    </row>
-    <row r="12" spans="6:147">
-      <c r="F12" t="s">
+      <c r="DJ7" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="8" spans="7:148">
+      <c r="G8" t="s">
         <v>283</v>
       </c>
-      <c r="T12" t="s">
+      <c r="U8" t="s">
         <v>348</v>
       </c>
-      <c r="BR12" t="s">
+      <c r="BS8" t="s">
         <v>487</v>
       </c>
-    </row>
-    <row r="13" spans="6:147">
-      <c r="F13" t="s">
+      <c r="DJ8" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="9" spans="7:148">
+      <c r="G9" t="s">
         <v>284</v>
       </c>
-      <c r="T13" t="s">
+      <c r="U9" t="s">
         <v>349</v>
       </c>
-      <c r="BR13" t="s">
+      <c r="BS9" t="s">
         <v>488</v>
       </c>
-    </row>
-    <row r="14" spans="6:147">
-      <c r="F14" t="s">
+      <c r="DJ9" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="10" spans="7:148">
+      <c r="G10" t="s">
         <v>285</v>
       </c>
-      <c r="T14" t="s">
+      <c r="U10" t="s">
         <v>350</v>
       </c>
-      <c r="BR14" t="s">
+      <c r="BS10" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="15" spans="6:147">
-      <c r="F15" t="s">
+    <row r="11" spans="7:148">
+      <c r="G11" t="s">
         <v>286</v>
       </c>
-      <c r="T15" t="s">
+      <c r="U11" t="s">
         <v>351</v>
       </c>
-      <c r="BR15" t="s">
+      <c r="BS11" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="16" spans="6:147">
-      <c r="F16" t="s">
+    <row r="12" spans="7:148">
+      <c r="G12" t="s">
         <v>287</v>
       </c>
-      <c r="T16" t="s">
+      <c r="U12" t="s">
         <v>352</v>
       </c>
-      <c r="BR16" t="s">
+      <c r="BS12" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="17" spans="6:70">
-      <c r="F17" t="s">
+    <row r="13" spans="7:148">
+      <c r="G13" t="s">
         <v>288</v>
       </c>
-      <c r="T17" t="s">
+      <c r="U13" t="s">
         <v>353</v>
       </c>
-      <c r="BR17" t="s">
+      <c r="BS13" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="18" spans="6:70">
-      <c r="F18" t="s">
+    <row r="14" spans="7:148">
+      <c r="G14" t="s">
         <v>289</v>
       </c>
-      <c r="T18" t="s">
+      <c r="U14" t="s">
         <v>354</v>
       </c>
-      <c r="BR18" t="s">
+      <c r="BS14" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="19" spans="6:70">
-      <c r="F19" t="s">
+    <row r="15" spans="7:148">
+      <c r="G15" t="s">
         <v>290</v>
       </c>
-      <c r="T19" t="s">
+      <c r="U15" t="s">
         <v>355</v>
       </c>
-      <c r="BR19" t="s">
+      <c r="BS15" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="20" spans="6:70">
-      <c r="F20" t="s">
+    <row r="16" spans="7:148">
+      <c r="G16" t="s">
         <v>291</v>
       </c>
-      <c r="T20" t="s">
+      <c r="U16" t="s">
         <v>356</v>
       </c>
-      <c r="BR20" t="s">
+      <c r="BS16" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="21" spans="6:70">
-      <c r="F21" t="s">
+    <row r="17" spans="7:71">
+      <c r="G17" t="s">
         <v>292</v>
       </c>
-      <c r="T21" t="s">
+      <c r="U17" t="s">
         <v>357</v>
       </c>
-      <c r="BR21" t="s">
+      <c r="BS17" t="s">
         <v>496</v>
       </c>
     </row>
-    <row r="22" spans="6:70">
-      <c r="F22" t="s">
+    <row r="18" spans="7:71">
+      <c r="G18" t="s">
         <v>293</v>
       </c>
-      <c r="T22" t="s">
+      <c r="U18" t="s">
         <v>358</v>
       </c>
-      <c r="BR22" t="s">
+      <c r="BS18" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="23" spans="6:70">
-      <c r="F23" t="s">
+    <row r="19" spans="7:71">
+      <c r="G19" t="s">
         <v>294</v>
       </c>
-      <c r="T23" t="s">
+      <c r="U19" t="s">
         <v>359</v>
       </c>
-      <c r="BR23" t="s">
+      <c r="BS19" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="24" spans="6:70">
-      <c r="F24" t="s">
+    <row r="20" spans="7:71">
+      <c r="G20" t="s">
         <v>295</v>
       </c>
-      <c r="T24" t="s">
+      <c r="U20" t="s">
         <v>360</v>
       </c>
-      <c r="BR24" t="s">
+      <c r="BS20" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="25" spans="6:70">
-      <c r="F25" t="s">
+    <row r="21" spans="7:71">
+      <c r="G21" t="s">
         <v>296</v>
       </c>
-      <c r="T25" t="s">
+      <c r="U21" t="s">
         <v>361</v>
       </c>
-      <c r="BR25" t="s">
+      <c r="BS21" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="26" spans="6:70">
-      <c r="F26" t="s">
+    <row r="22" spans="7:71">
+      <c r="G22" t="s">
         <v>297</v>
       </c>
-      <c r="T26" t="s">
+      <c r="U22" t="s">
         <v>362</v>
       </c>
-      <c r="BR26" t="s">
+      <c r="BS22" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="27" spans="6:70">
-      <c r="F27" t="s">
+    <row r="23" spans="7:71">
+      <c r="G23" t="s">
         <v>298</v>
       </c>
-      <c r="T27" t="s">
+      <c r="U23" t="s">
         <v>363</v>
       </c>
-      <c r="BR27" t="s">
+      <c r="BS23" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="28" spans="6:70">
-      <c r="F28" t="s">
+    <row r="24" spans="7:71">
+      <c r="G24" t="s">
         <v>299</v>
       </c>
-      <c r="T28" t="s">
+      <c r="U24" t="s">
         <v>364</v>
       </c>
-      <c r="BR28" t="s">
+      <c r="BS24" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="29" spans="6:70">
-      <c r="F29" t="s">
+    <row r="25" spans="7:71">
+      <c r="G25" t="s">
         <v>300</v>
       </c>
-      <c r="T29" t="s">
+      <c r="U25" t="s">
         <v>365</v>
       </c>
-      <c r="BR29" t="s">
+      <c r="BS25" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="30" spans="6:70">
-      <c r="F30" t="s">
+    <row r="26" spans="7:71">
+      <c r="G26" t="s">
         <v>301</v>
       </c>
-      <c r="T30" t="s">
+      <c r="U26" t="s">
         <v>366</v>
       </c>
-      <c r="BR30" t="s">
+      <c r="BS26" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="31" spans="6:70">
-      <c r="T31" t="s">
+    <row r="27" spans="7:71">
+      <c r="G27" t="s">
+        <v>302</v>
+      </c>
+      <c r="U27" t="s">
         <v>367</v>
       </c>
-      <c r="BR31" t="s">
+      <c r="BS27" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="32" spans="6:70">
-      <c r="T32" t="s">
+    <row r="28" spans="7:71">
+      <c r="G28" t="s">
+        <v>303</v>
+      </c>
+      <c r="U28" t="s">
         <v>368</v>
       </c>
-      <c r="BR32" t="s">
+      <c r="BS28" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="33" spans="70:70">
-      <c r="BR33" t="s">
+    <row r="29" spans="7:71">
+      <c r="G29" t="s">
+        <v>304</v>
+      </c>
+      <c r="U29" t="s">
+        <v>369</v>
+      </c>
+      <c r="BS29" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="34" spans="70:70">
-      <c r="BR34" t="s">
+    <row r="30" spans="7:71">
+      <c r="G30" t="s">
+        <v>305</v>
+      </c>
+      <c r="U30" t="s">
+        <v>370</v>
+      </c>
+      <c r="BS30" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="35" spans="70:70">
-      <c r="BR35" t="s">
+    <row r="31" spans="7:71">
+      <c r="U31" t="s">
+        <v>371</v>
+      </c>
+      <c r="BS31" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="36" spans="70:70">
-      <c r="BR36" t="s">
+    <row r="32" spans="7:71">
+      <c r="U32" t="s">
+        <v>372</v>
+      </c>
+      <c r="BS32" t="s">
         <v>511</v>
       </c>
     </row>
-    <row r="37" spans="70:70">
-      <c r="BR37" t="s">
+    <row r="33" spans="71:71">
+      <c r="BS33" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="38" spans="70:70">
-      <c r="BR38" t="s">
+    <row r="34" spans="71:71">
+      <c r="BS34" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="39" spans="70:70">
-      <c r="BR39" t="s">
+    <row r="35" spans="71:71">
+      <c r="BS35" t="s">
         <v>514</v>
       </c>
     </row>
-    <row r="40" spans="70:70">
-      <c r="BR40" t="s">
+    <row r="36" spans="71:71">
+      <c r="BS36" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="41" spans="70:70">
-      <c r="BR41" t="s">
+    <row r="37" spans="71:71">
+      <c r="BS37" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="42" spans="70:70">
-      <c r="BR42" t="s">
+    <row r="38" spans="71:71">
+      <c r="BS38" t="s">
         <v>517</v>
       </c>
     </row>
-    <row r="43" spans="70:70">
-      <c r="BR43" t="s">
+    <row r="39" spans="71:71">
+      <c r="BS39" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="44" spans="70:70">
-      <c r="BR44" t="s">
+    <row r="40" spans="71:71">
+      <c r="BS40" t="s">
         <v>519</v>
       </c>
     </row>
-    <row r="45" spans="70:70">
-      <c r="BR45" t="s">
+    <row r="41" spans="71:71">
+      <c r="BS41" t="s">
         <v>520</v>
       </c>
     </row>
-    <row r="46" spans="70:70">
-      <c r="BR46" t="s">
+    <row r="42" spans="71:71">
+      <c r="BS42" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="47" spans="70:70">
-      <c r="BR47" t="s">
+    <row r="43" spans="71:71">
+      <c r="BS43" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="48" spans="70:70">
-      <c r="BR48" t="s">
+    <row r="44" spans="71:71">
+      <c r="BS44" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="49" spans="70:70">
-      <c r="BR49" t="s">
+    <row r="45" spans="71:71">
+      <c r="BS45" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="50" spans="70:70">
-      <c r="BR50" t="s">
+    <row r="46" spans="71:71">
+      <c r="BS46" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="51" spans="70:70">
-      <c r="BR51" t="s">
+    <row r="47" spans="71:71">
+      <c r="BS47" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="52" spans="70:70">
-      <c r="BR52" t="s">
+    <row r="48" spans="71:71">
+      <c r="BS48" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="53" spans="70:70">
-      <c r="BR53" t="s">
+    <row r="49" spans="71:71">
+      <c r="BS49" t="s">
         <v>528</v>
       </c>
     </row>
-    <row r="54" spans="70:70">
-      <c r="BR54" t="s">
+    <row r="50" spans="71:71">
+      <c r="BS50" t="s">
         <v>529</v>
       </c>
     </row>
-    <row r="55" spans="70:70">
-      <c r="BR55" t="s">
+    <row r="51" spans="71:71">
+      <c r="BS51" t="s">
         <v>530</v>
       </c>
     </row>
-    <row r="56" spans="70:70">
-      <c r="BR56" t="s">
+    <row r="52" spans="71:71">
+      <c r="BS52" t="s">
         <v>531</v>
       </c>
     </row>
-    <row r="57" spans="70:70">
-      <c r="BR57" t="s">
+    <row r="53" spans="71:71">
+      <c r="BS53" t="s">
         <v>532</v>
       </c>
     </row>
-    <row r="58" spans="70:70">
-      <c r="BR58" t="s">
+    <row r="54" spans="71:71">
+      <c r="BS54" t="s">
         <v>533</v>
       </c>
     </row>
-    <row r="59" spans="70:70">
-      <c r="BR59" t="s">
+    <row r="55" spans="71:71">
+      <c r="BS55" t="s">
         <v>534</v>
       </c>
     </row>
-    <row r="60" spans="70:70">
-      <c r="BR60" t="s">
+    <row r="56" spans="71:71">
+      <c r="BS56" t="s">
         <v>535</v>
       </c>
     </row>
-    <row r="61" spans="70:70">
-      <c r="BR61" t="s">
+    <row r="57" spans="71:71">
+      <c r="BS57" t="s">
         <v>536</v>
       </c>
     </row>
-    <row r="62" spans="70:70">
-      <c r="BR62" t="s">
+    <row r="58" spans="71:71">
+      <c r="BS58" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="63" spans="70:70">
-      <c r="BR63" t="s">
+    <row r="59" spans="71:71">
+      <c r="BS59" t="s">
         <v>538</v>
       </c>
     </row>
-    <row r="64" spans="70:70">
-      <c r="BR64" t="s">
+    <row r="60" spans="71:71">
+      <c r="BS60" t="s">
         <v>539</v>
       </c>
     </row>
-    <row r="65" spans="70:70">
-      <c r="BR65" t="s">
+    <row r="61" spans="71:71">
+      <c r="BS61" t="s">
         <v>540</v>
       </c>
     </row>
-    <row r="66" spans="70:70">
-      <c r="BR66" t="s">
+    <row r="62" spans="71:71">
+      <c r="BS62" t="s">
         <v>541</v>
       </c>
     </row>
-    <row r="67" spans="70:70">
-      <c r="BR67" t="s">
+    <row r="63" spans="71:71">
+      <c r="BS63" t="s">
         <v>542</v>
       </c>
     </row>
-    <row r="68" spans="70:70">
-      <c r="BR68" t="s">
+    <row r="64" spans="71:71">
+      <c r="BS64" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="69" spans="70:70">
-      <c r="BR69" t="s">
+    <row r="65" spans="71:71">
+      <c r="BS65" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="70" spans="70:70">
-      <c r="BR70" t="s">
+    <row r="66" spans="71:71">
+      <c r="BS66" t="s">
         <v>545</v>
       </c>
     </row>
-    <row r="71" spans="70:70">
-      <c r="BR71" t="s">
+    <row r="67" spans="71:71">
+      <c r="BS67" t="s">
         <v>546</v>
       </c>
     </row>
-    <row r="72" spans="70:70">
-      <c r="BR72" t="s">
+    <row r="68" spans="71:71">
+      <c r="BS68" t="s">
         <v>547</v>
       </c>
     </row>
-    <row r="73" spans="70:70">
-      <c r="BR73" t="s">
+    <row r="69" spans="71:71">
+      <c r="BS69" t="s">
         <v>548</v>
       </c>
     </row>
-    <row r="74" spans="70:70">
-      <c r="BR74" t="s">
+    <row r="70" spans="71:71">
+      <c r="BS70" t="s">
         <v>549</v>
       </c>
     </row>
-    <row r="75" spans="70:70">
-      <c r="BR75" t="s">
+    <row r="71" spans="71:71">
+      <c r="BS71" t="s">
         <v>550</v>
       </c>
     </row>
-    <row r="76" spans="70:70">
-      <c r="BR76" t="s">
+    <row r="72" spans="71:71">
+      <c r="BS72" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="77" spans="70:70">
-      <c r="BR77" t="s">
+    <row r="73" spans="71:71">
+      <c r="BS73" t="s">
         <v>552</v>
       </c>
     </row>
-    <row r="78" spans="70:70">
-      <c r="BR78" t="s">
+    <row r="74" spans="71:71">
+      <c r="BS74" t="s">
         <v>553</v>
       </c>
     </row>
-    <row r="79" spans="70:70">
-      <c r="BR79" t="s">
+    <row r="75" spans="71:71">
+      <c r="BS75" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="80" spans="70:70">
-      <c r="BR80" t="s">
+    <row r="76" spans="71:71">
+      <c r="BS76" t="s">
         <v>555</v>
       </c>
     </row>
-    <row r="81" spans="70:70">
-      <c r="BR81" t="s">
+    <row r="77" spans="71:71">
+      <c r="BS77" t="s">
         <v>556</v>
       </c>
     </row>
-    <row r="82" spans="70:70">
-      <c r="BR82" t="s">
+    <row r="78" spans="71:71">
+      <c r="BS78" t="s">
         <v>557</v>
       </c>
     </row>
-    <row r="83" spans="70:70">
-      <c r="BR83" t="s">
+    <row r="79" spans="71:71">
+      <c r="BS79" t="s">
         <v>558</v>
       </c>
     </row>
-    <row r="84" spans="70:70">
-      <c r="BR84" t="s">
+    <row r="80" spans="71:71">
+      <c r="BS80" t="s">
         <v>559</v>
       </c>
     </row>
-    <row r="85" spans="70:70">
-      <c r="BR85" t="s">
+    <row r="81" spans="71:71">
+      <c r="BS81" t="s">
         <v>560</v>
       </c>
     </row>
-    <row r="86" spans="70:70">
-      <c r="BR86" t="s">
+    <row r="82" spans="71:71">
+      <c r="BS82" t="s">
         <v>561</v>
       </c>
     </row>
-    <row r="87" spans="70:70">
-      <c r="BR87" t="s">
+    <row r="83" spans="71:71">
+      <c r="BS83" t="s">
         <v>562</v>
       </c>
     </row>
-    <row r="88" spans="70:70">
-      <c r="BR88" t="s">
+    <row r="84" spans="71:71">
+      <c r="BS84" t="s">
         <v>563</v>
       </c>
     </row>
-    <row r="89" spans="70:70">
-      <c r="BR89" t="s">
+    <row r="85" spans="71:71">
+      <c r="BS85" t="s">
         <v>564</v>
       </c>
     </row>
-    <row r="90" spans="70:70">
-      <c r="BR90" t="s">
+    <row r="86" spans="71:71">
+      <c r="BS86" t="s">
         <v>565</v>
       </c>
     </row>
-    <row r="91" spans="70:70">
-      <c r="BR91" t="s">
+    <row r="87" spans="71:71">
+      <c r="BS87" t="s">
         <v>566</v>
       </c>
     </row>
-    <row r="92" spans="70:70">
-      <c r="BR92" t="s">
+    <row r="88" spans="71:71">
+      <c r="BS88" t="s">
         <v>567</v>
       </c>
     </row>
-    <row r="93" spans="70:70">
-      <c r="BR93" t="s">
+    <row r="89" spans="71:71">
+      <c r="BS89" t="s">
         <v>568</v>
       </c>
     </row>
-    <row r="94" spans="70:70">
-      <c r="BR94" t="s">
+    <row r="90" spans="71:71">
+      <c r="BS90" t="s">
         <v>569</v>
       </c>
     </row>
-    <row r="95" spans="70:70">
-      <c r="BR95" t="s">
+    <row r="91" spans="71:71">
+      <c r="BS91" t="s">
         <v>570</v>
       </c>
     </row>
-    <row r="96" spans="70:70">
-      <c r="BR96" t="s">
+    <row r="92" spans="71:71">
+      <c r="BS92" t="s">
         <v>571</v>
       </c>
     </row>
-    <row r="97" spans="70:70">
-      <c r="BR97" t="s">
+    <row r="93" spans="71:71">
+      <c r="BS93" t="s">
         <v>572</v>
       </c>
     </row>
-    <row r="98" spans="70:70">
-      <c r="BR98" t="s">
+    <row r="94" spans="71:71">
+      <c r="BS94" t="s">
         <v>573</v>
       </c>
     </row>
-    <row r="99" spans="70:70">
-      <c r="BR99" t="s">
+    <row r="95" spans="71:71">
+      <c r="BS95" t="s">
         <v>574</v>
       </c>
     </row>
-    <row r="100" spans="70:70">
-      <c r="BR100" t="s">
+    <row r="96" spans="71:71">
+      <c r="BS96" t="s">
         <v>575</v>
       </c>
     </row>
-    <row r="101" spans="70:70">
-      <c r="BR101" t="s">
+    <row r="97" spans="71:71">
+      <c r="BS97" t="s">
         <v>576</v>
       </c>
     </row>
-    <row r="102" spans="70:70">
-      <c r="BR102" t="s">
+    <row r="98" spans="71:71">
+      <c r="BS98" t="s">
         <v>577</v>
       </c>
     </row>
-    <row r="103" spans="70:70">
-      <c r="BR103" t="s">
+    <row r="99" spans="71:71">
+      <c r="BS99" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="104" spans="70:70">
-      <c r="BR104" t="s">
+    <row r="100" spans="71:71">
+      <c r="BS100" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="105" spans="70:70">
-      <c r="BR105" t="s">
+    <row r="101" spans="71:71">
+      <c r="BS101" t="s">
         <v>580</v>
       </c>
     </row>
-    <row r="106" spans="70:70">
-      <c r="BR106" t="s">
+    <row r="102" spans="71:71">
+      <c r="BS102" t="s">
         <v>581</v>
       </c>
     </row>
-    <row r="107" spans="70:70">
-      <c r="BR107" t="s">
+    <row r="103" spans="71:71">
+      <c r="BS103" t="s">
         <v>582</v>
       </c>
     </row>
-    <row r="108" spans="70:70">
-      <c r="BR108" t="s">
+    <row r="104" spans="71:71">
+      <c r="BS104" t="s">
         <v>583</v>
       </c>
     </row>
-    <row r="109" spans="70:70">
-      <c r="BR109" t="s">
+    <row r="105" spans="71:71">
+      <c r="BS105" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="110" spans="70:70">
-      <c r="BR110" t="s">
+    <row r="106" spans="71:71">
+      <c r="BS106" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="111" spans="70:70">
-      <c r="BR111" t="s">
+    <row r="107" spans="71:71">
+      <c r="BS107" t="s">
         <v>586</v>
       </c>
     </row>
-    <row r="112" spans="70:70">
-      <c r="BR112" t="s">
+    <row r="108" spans="71:71">
+      <c r="BS108" t="s">
         <v>587</v>
       </c>
     </row>
-    <row r="113" spans="70:70">
-      <c r="BR113" t="s">
+    <row r="109" spans="71:71">
+      <c r="BS109" t="s">
         <v>588</v>
       </c>
     </row>
-    <row r="114" spans="70:70">
-      <c r="BR114" t="s">
+    <row r="110" spans="71:71">
+      <c r="BS110" t="s">
         <v>589</v>
       </c>
     </row>
-    <row r="115" spans="70:70">
-      <c r="BR115" t="s">
+    <row r="111" spans="71:71">
+      <c r="BS111" t="s">
         <v>590</v>
       </c>
     </row>
-    <row r="116" spans="70:70">
-      <c r="BR116" t="s">
+    <row r="112" spans="71:71">
+      <c r="BS112" t="s">
         <v>591</v>
       </c>
     </row>
-    <row r="117" spans="70:70">
-      <c r="BR117" t="s">
+    <row r="113" spans="71:71">
+      <c r="BS113" t="s">
         <v>592</v>
       </c>
     </row>
-    <row r="118" spans="70:70">
-      <c r="BR118" t="s">
+    <row r="114" spans="71:71">
+      <c r="BS114" t="s">
         <v>593</v>
       </c>
     </row>
-    <row r="119" spans="70:70">
-      <c r="BR119" t="s">
+    <row r="115" spans="71:71">
+      <c r="BS115" t="s">
         <v>594</v>
       </c>
     </row>
-    <row r="120" spans="70:70">
-      <c r="BR120" t="s">
+    <row r="116" spans="71:71">
+      <c r="BS116" t="s">
         <v>595</v>
       </c>
     </row>
-    <row r="121" spans="70:70">
-      <c r="BR121" t="s">
+    <row r="117" spans="71:71">
+      <c r="BS117" t="s">
         <v>596</v>
       </c>
     </row>
-    <row r="122" spans="70:70">
-      <c r="BR122" t="s">
+    <row r="118" spans="71:71">
+      <c r="BS118" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="123" spans="70:70">
-      <c r="BR123" t="s">
+    <row r="119" spans="71:71">
+      <c r="BS119" t="s">
         <v>598</v>
       </c>
     </row>
-    <row r="124" spans="70:70">
-      <c r="BR124" t="s">
+    <row r="120" spans="71:71">
+      <c r="BS120" t="s">
         <v>599</v>
       </c>
     </row>
-    <row r="125" spans="70:70">
-      <c r="BR125" t="s">
+    <row r="121" spans="71:71">
+      <c r="BS121" t="s">
         <v>600</v>
       </c>
     </row>
-    <row r="126" spans="70:70">
-      <c r="BR126" t="s">
+    <row r="122" spans="71:71">
+      <c r="BS122" t="s">
         <v>601</v>
       </c>
     </row>
-    <row r="127" spans="70:70">
-      <c r="BR127" t="s">
+    <row r="123" spans="71:71">
+      <c r="BS123" t="s">
         <v>602</v>
       </c>
     </row>
-    <row r="128" spans="70:70">
-      <c r="BR128" t="s">
+    <row r="124" spans="71:71">
+      <c r="BS124" t="s">
         <v>603</v>
       </c>
     </row>
-    <row r="129" spans="70:70">
-      <c r="BR129" t="s">
+    <row r="125" spans="71:71">
+      <c r="BS125" t="s">
         <v>604</v>
       </c>
     </row>
-    <row r="130" spans="70:70">
-      <c r="BR130" t="s">
+    <row r="126" spans="71:71">
+      <c r="BS126" t="s">
         <v>605</v>
       </c>
     </row>
-    <row r="131" spans="70:70">
-      <c r="BR131" t="s">
+    <row r="127" spans="71:71">
+      <c r="BS127" t="s">
         <v>606</v>
       </c>
     </row>
-    <row r="132" spans="70:70">
-      <c r="BR132" t="s">
+    <row r="128" spans="71:71">
+      <c r="BS128" t="s">
         <v>607</v>
       </c>
     </row>
-    <row r="133" spans="70:70">
-      <c r="BR133" t="s">
+    <row r="129" spans="71:71">
+      <c r="BS129" t="s">
         <v>608</v>
       </c>
     </row>
-    <row r="134" spans="70:70">
-      <c r="BR134" t="s">
+    <row r="130" spans="71:71">
+      <c r="BS130" t="s">
         <v>609</v>
       </c>
     </row>
-    <row r="135" spans="70:70">
-      <c r="BR135" t="s">
+    <row r="131" spans="71:71">
+      <c r="BS131" t="s">
         <v>610</v>
       </c>
     </row>
-    <row r="136" spans="70:70">
-      <c r="BR136" t="s">
+    <row r="132" spans="71:71">
+      <c r="BS132" t="s">
         <v>611</v>
       </c>
     </row>
-    <row r="137" spans="70:70">
-      <c r="BR137" t="s">
+    <row r="133" spans="71:71">
+      <c r="BS133" t="s">
         <v>612</v>
       </c>
     </row>
-    <row r="138" spans="70:70">
-      <c r="BR138" t="s">
+    <row r="134" spans="71:71">
+      <c r="BS134" t="s">
         <v>613</v>
       </c>
     </row>
-    <row r="139" spans="70:70">
-      <c r="BR139" t="s">
+    <row r="135" spans="71:71">
+      <c r="BS135" t="s">
         <v>614</v>
       </c>
     </row>
-    <row r="140" spans="70:70">
-      <c r="BR140" t="s">
+    <row r="136" spans="71:71">
+      <c r="BS136" t="s">
         <v>615</v>
       </c>
     </row>
-    <row r="141" spans="70:70">
-      <c r="BR141" t="s">
+    <row r="137" spans="71:71">
+      <c r="BS137" t="s">
         <v>616</v>
       </c>
     </row>
-    <row r="142" spans="70:70">
-      <c r="BR142" t="s">
+    <row r="138" spans="71:71">
+      <c r="BS138" t="s">
         <v>617</v>
       </c>
     </row>
-    <row r="143" spans="70:70">
-      <c r="BR143" t="s">
+    <row r="139" spans="71:71">
+      <c r="BS139" t="s">
         <v>618</v>
       </c>
     </row>
-    <row r="144" spans="70:70">
-      <c r="BR144" t="s">
+    <row r="140" spans="71:71">
+      <c r="BS140" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="145" spans="70:70">
-      <c r="BR145" t="s">
+    <row r="141" spans="71:71">
+      <c r="BS141" t="s">
         <v>620</v>
       </c>
     </row>
-    <row r="146" spans="70:70">
-      <c r="BR146" t="s">
+    <row r="142" spans="71:71">
+      <c r="BS142" t="s">
         <v>621</v>
       </c>
     </row>
-    <row r="147" spans="70:70">
-      <c r="BR147" t="s">
+    <row r="143" spans="71:71">
+      <c r="BS143" t="s">
         <v>622</v>
       </c>
     </row>
-    <row r="148" spans="70:70">
-      <c r="BR148" t="s">
+    <row r="144" spans="71:71">
+      <c r="BS144" t="s">
         <v>623</v>
       </c>
     </row>
-    <row r="149" spans="70:70">
-      <c r="BR149" t="s">
+    <row r="145" spans="71:71">
+      <c r="BS145" t="s">
         <v>624</v>
       </c>
     </row>
-    <row r="150" spans="70:70">
-      <c r="BR150" t="s">
+    <row r="146" spans="71:71">
+      <c r="BS146" t="s">
         <v>625</v>
       </c>
     </row>
-    <row r="151" spans="70:70">
-      <c r="BR151" t="s">
+    <row r="147" spans="71:71">
+      <c r="BS147" t="s">
         <v>626</v>
       </c>
     </row>
-    <row r="152" spans="70:70">
-      <c r="BR152" t="s">
+    <row r="148" spans="71:71">
+      <c r="BS148" t="s">
         <v>627</v>
       </c>
     </row>
-    <row r="153" spans="70:70">
-      <c r="BR153" t="s">
+    <row r="149" spans="71:71">
+      <c r="BS149" t="s">
         <v>628</v>
       </c>
     </row>
-    <row r="154" spans="70:70">
-      <c r="BR154" t="s">
+    <row r="150" spans="71:71">
+      <c r="BS150" t="s">
         <v>629</v>
       </c>
     </row>
-    <row r="155" spans="70:70">
-      <c r="BR155" t="s">
+    <row r="151" spans="71:71">
+      <c r="BS151" t="s">
         <v>630</v>
       </c>
     </row>
-    <row r="156" spans="70:70">
-      <c r="BR156" t="s">
+    <row r="152" spans="71:71">
+      <c r="BS152" t="s">
         <v>631</v>
       </c>
     </row>
-    <row r="157" spans="70:70">
-      <c r="BR157" t="s">
+    <row r="153" spans="71:71">
+      <c r="BS153" t="s">
         <v>632</v>
       </c>
     </row>
-    <row r="158" spans="70:70">
-      <c r="BR158" t="s">
+    <row r="154" spans="71:71">
+      <c r="BS154" t="s">
         <v>633</v>
       </c>
     </row>
-    <row r="159" spans="70:70">
-      <c r="BR159" t="s">
+    <row r="155" spans="71:71">
+      <c r="BS155" t="s">
         <v>634</v>
       </c>
     </row>
-    <row r="160" spans="70:70">
-      <c r="BR160" t="s">
+    <row r="156" spans="71:71">
+      <c r="BS156" t="s">
         <v>635</v>
       </c>
     </row>
-    <row r="161" spans="70:70">
-      <c r="BR161" t="s">
+    <row r="157" spans="71:71">
+      <c r="BS157" t="s">
         <v>636</v>
       </c>
     </row>
-    <row r="162" spans="70:70">
-      <c r="BR162" t="s">
+    <row r="158" spans="71:71">
+      <c r="BS158" t="s">
         <v>637</v>
       </c>
     </row>
-    <row r="163" spans="70:70">
-      <c r="BR163" t="s">
+    <row r="159" spans="71:71">
+      <c r="BS159" t="s">
         <v>638</v>
       </c>
     </row>
-    <row r="164" spans="70:70">
-      <c r="BR164" t="s">
+    <row r="160" spans="71:71">
+      <c r="BS160" t="s">
         <v>639</v>
       </c>
     </row>
-    <row r="165" spans="70:70">
-      <c r="BR165" t="s">
+    <row r="161" spans="71:71">
+      <c r="BS161" t="s">
         <v>640</v>
       </c>
     </row>
-    <row r="166" spans="70:70">
-      <c r="BR166" t="s">
+    <row r="162" spans="71:71">
+      <c r="BS162" t="s">
         <v>641</v>
       </c>
     </row>
-    <row r="167" spans="70:70">
-      <c r="BR167" t="s">
+    <row r="163" spans="71:71">
+      <c r="BS163" t="s">
         <v>642</v>
       </c>
     </row>
-    <row r="168" spans="70:70">
-      <c r="BR168" t="s">
+    <row r="164" spans="71:71">
+      <c r="BS164" t="s">
         <v>643</v>
       </c>
     </row>
-    <row r="169" spans="70:70">
-      <c r="BR169" t="s">
+    <row r="165" spans="71:71">
+      <c r="BS165" t="s">
         <v>644</v>
       </c>
     </row>
-    <row r="170" spans="70:70">
-      <c r="BR170" t="s">
+    <row r="166" spans="71:71">
+      <c r="BS166" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="171" spans="70:70">
-      <c r="BR171" t="s">
+    <row r="167" spans="71:71">
+      <c r="BS167" t="s">
         <v>646</v>
       </c>
     </row>
-    <row r="172" spans="70:70">
-      <c r="BR172" t="s">
+    <row r="168" spans="71:71">
+      <c r="BS168" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="173" spans="70:70">
-      <c r="BR173" t="s">
+    <row r="169" spans="71:71">
+      <c r="BS169" t="s">
         <v>648</v>
       </c>
     </row>
-    <row r="174" spans="70:70">
-      <c r="BR174" t="s">
+    <row r="170" spans="71:71">
+      <c r="BS170" t="s">
         <v>649</v>
       </c>
     </row>
-    <row r="175" spans="70:70">
-      <c r="BR175" t="s">
+    <row r="171" spans="71:71">
+      <c r="BS171" t="s">
         <v>650</v>
       </c>
     </row>
-    <row r="176" spans="70:70">
-      <c r="BR176" t="s">
+    <row r="172" spans="71:71">
+      <c r="BS172" t="s">
         <v>651</v>
       </c>
     </row>
-    <row r="177" spans="70:70">
-      <c r="BR177" t="s">
+    <row r="173" spans="71:71">
+      <c r="BS173" t="s">
         <v>652</v>
       </c>
     </row>
-    <row r="178" spans="70:70">
-      <c r="BR178" t="s">
+    <row r="174" spans="71:71">
+      <c r="BS174" t="s">
         <v>653</v>
       </c>
     </row>
-    <row r="179" spans="70:70">
-      <c r="BR179" t="s">
+    <row r="175" spans="71:71">
+      <c r="BS175" t="s">
         <v>654</v>
       </c>
     </row>
-    <row r="180" spans="70:70">
-      <c r="BR180" t="s">
+    <row r="176" spans="71:71">
+      <c r="BS176" t="s">
         <v>655</v>
       </c>
     </row>
-    <row r="181" spans="70:70">
-      <c r="BR181" t="s">
+    <row r="177" spans="71:71">
+      <c r="BS177" t="s">
         <v>656</v>
       </c>
     </row>
-    <row r="182" spans="70:70">
-      <c r="BR182" t="s">
+    <row r="178" spans="71:71">
+      <c r="BS178" t="s">
         <v>657</v>
       </c>
     </row>
-    <row r="183" spans="70:70">
-      <c r="BR183" t="s">
+    <row r="179" spans="71:71">
+      <c r="BS179" t="s">
         <v>658</v>
       </c>
     </row>
-    <row r="184" spans="70:70">
-      <c r="BR184" t="s">
+    <row r="180" spans="71:71">
+      <c r="BS180" t="s">
         <v>659</v>
       </c>
     </row>
-    <row r="185" spans="70:70">
-      <c r="BR185" t="s">
+    <row r="181" spans="71:71">
+      <c r="BS181" t="s">
         <v>660</v>
       </c>
     </row>
-    <row r="186" spans="70:70">
-      <c r="BR186" t="s">
+    <row r="182" spans="71:71">
+      <c r="BS182" t="s">
         <v>661</v>
       </c>
     </row>
-    <row r="187" spans="70:70">
-      <c r="BR187" t="s">
+    <row r="183" spans="71:71">
+      <c r="BS183" t="s">
         <v>662</v>
       </c>
     </row>
-    <row r="188" spans="70:70">
-      <c r="BR188" t="s">
+    <row r="184" spans="71:71">
+      <c r="BS184" t="s">
         <v>663</v>
       </c>
     </row>
-    <row r="189" spans="70:70">
-      <c r="BR189" t="s">
+    <row r="185" spans="71:71">
+      <c r="BS185" t="s">
         <v>664</v>
       </c>
     </row>
-    <row r="190" spans="70:70">
-      <c r="BR190" t="s">
+    <row r="186" spans="71:71">
+      <c r="BS186" t="s">
         <v>665</v>
       </c>
     </row>
-    <row r="191" spans="70:70">
-      <c r="BR191" t="s">
+    <row r="187" spans="71:71">
+      <c r="BS187" t="s">
         <v>666</v>
       </c>
     </row>
-    <row r="192" spans="70:70">
-      <c r="BR192" t="s">
+    <row r="188" spans="71:71">
+      <c r="BS188" t="s">
         <v>667</v>
       </c>
     </row>
-    <row r="193" spans="70:70">
-      <c r="BR193" t="s">
+    <row r="189" spans="71:71">
+      <c r="BS189" t="s">
         <v>668</v>
       </c>
     </row>
-    <row r="194" spans="70:70">
-      <c r="BR194" t="s">
+    <row r="190" spans="71:71">
+      <c r="BS190" t="s">
         <v>669</v>
       </c>
     </row>
-    <row r="195" spans="70:70">
-      <c r="BR195" t="s">
+    <row r="191" spans="71:71">
+      <c r="BS191" t="s">
         <v>670</v>
       </c>
     </row>
-    <row r="196" spans="70:70">
-      <c r="BR196" t="s">
+    <row r="192" spans="71:71">
+      <c r="BS192" t="s">
         <v>671</v>
       </c>
     </row>
-    <row r="197" spans="70:70">
-      <c r="BR197" t="s">
+    <row r="193" spans="71:71">
+      <c r="BS193" t="s">
         <v>672</v>
       </c>
     </row>
-    <row r="198" spans="70:70">
-      <c r="BR198" t="s">
+    <row r="194" spans="71:71">
+      <c r="BS194" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="199" spans="70:70">
-      <c r="BR199" t="s">
+    <row r="195" spans="71:71">
+      <c r="BS195" t="s">
         <v>674</v>
       </c>
     </row>
-    <row r="200" spans="70:70">
-      <c r="BR200" t="s">
+    <row r="196" spans="71:71">
+      <c r="BS196" t="s">
         <v>675</v>
       </c>
     </row>
-    <row r="201" spans="70:70">
-      <c r="BR201" t="s">
+    <row r="197" spans="71:71">
+      <c r="BS197" t="s">
         <v>676</v>
       </c>
     </row>
-    <row r="202" spans="70:70">
-      <c r="BR202" t="s">
+    <row r="198" spans="71:71">
+      <c r="BS198" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="203" spans="70:70">
-      <c r="BR203" t="s">
+    <row r="199" spans="71:71">
+      <c r="BS199" t="s">
         <v>678</v>
       </c>
     </row>
-    <row r="204" spans="70:70">
-      <c r="BR204" t="s">
+    <row r="200" spans="71:71">
+      <c r="BS200" t="s">
         <v>679</v>
       </c>
     </row>
-    <row r="205" spans="70:70">
-      <c r="BR205" t="s">
+    <row r="201" spans="71:71">
+      <c r="BS201" t="s">
         <v>680</v>
       </c>
     </row>
-    <row r="206" spans="70:70">
-      <c r="BR206" t="s">
+    <row r="202" spans="71:71">
+      <c r="BS202" t="s">
         <v>681</v>
       </c>
     </row>
-    <row r="207" spans="70:70">
-      <c r="BR207" t="s">
+    <row r="203" spans="71:71">
+      <c r="BS203" t="s">
         <v>682</v>
       </c>
     </row>
-    <row r="208" spans="70:70">
-      <c r="BR208" t="s">
+    <row r="204" spans="71:71">
+      <c r="BS204" t="s">
         <v>683</v>
       </c>
     </row>
-    <row r="209" spans="70:70">
-      <c r="BR209" t="s">
+    <row r="205" spans="71:71">
+      <c r="BS205" t="s">
         <v>684</v>
       </c>
     </row>
-    <row r="210" spans="70:70">
-      <c r="BR210" t="s">
+    <row r="206" spans="71:71">
+      <c r="BS206" t="s">
         <v>685</v>
       </c>
     </row>
-    <row r="211" spans="70:70">
-      <c r="BR211" t="s">
+    <row r="207" spans="71:71">
+      <c r="BS207" t="s">
         <v>686</v>
       </c>
     </row>
-    <row r="212" spans="70:70">
-      <c r="BR212" t="s">
+    <row r="208" spans="71:71">
+      <c r="BS208" t="s">
         <v>687</v>
       </c>
     </row>
-    <row r="213" spans="70:70">
-      <c r="BR213" t="s">
+    <row r="209" spans="71:71">
+      <c r="BS209" t="s">
         <v>688</v>
       </c>
     </row>
-    <row r="214" spans="70:70">
-      <c r="BR214" t="s">
+    <row r="210" spans="71:71">
+      <c r="BS210" t="s">
         <v>689</v>
       </c>
     </row>
-    <row r="215" spans="70:70">
-      <c r="BR215" t="s">
+    <row r="211" spans="71:71">
+      <c r="BS211" t="s">
         <v>690</v>
       </c>
     </row>
-    <row r="216" spans="70:70">
-      <c r="BR216" t="s">
+    <row r="212" spans="71:71">
+      <c r="BS212" t="s">
         <v>691</v>
       </c>
     </row>
-    <row r="217" spans="70:70">
-      <c r="BR217" t="s">
+    <row r="213" spans="71:71">
+      <c r="BS213" t="s">
         <v>692</v>
       </c>
     </row>
-    <row r="218" spans="70:70">
-      <c r="BR218" t="s">
+    <row r="214" spans="71:71">
+      <c r="BS214" t="s">
         <v>693</v>
       </c>
     </row>
-    <row r="219" spans="70:70">
-      <c r="BR219" t="s">
+    <row r="215" spans="71:71">
+      <c r="BS215" t="s">
         <v>694</v>
       </c>
     </row>
-    <row r="220" spans="70:70">
-      <c r="BR220" t="s">
+    <row r="216" spans="71:71">
+      <c r="BS216" t="s">
         <v>695</v>
       </c>
     </row>
-    <row r="221" spans="70:70">
-      <c r="BR221" t="s">
+    <row r="217" spans="71:71">
+      <c r="BS217" t="s">
         <v>696</v>
       </c>
     </row>
-    <row r="222" spans="70:70">
-      <c r="BR222" t="s">
+    <row r="218" spans="71:71">
+      <c r="BS218" t="s">
         <v>697</v>
       </c>
     </row>
-    <row r="223" spans="70:70">
-      <c r="BR223" t="s">
+    <row r="219" spans="71:71">
+      <c r="BS219" t="s">
         <v>698</v>
       </c>
     </row>
-    <row r="224" spans="70:70">
-      <c r="BR224" t="s">
+    <row r="220" spans="71:71">
+      <c r="BS220" t="s">
         <v>699</v>
       </c>
     </row>
-    <row r="225" spans="70:70">
-      <c r="BR225" t="s">
+    <row r="221" spans="71:71">
+      <c r="BS221" t="s">
         <v>700</v>
       </c>
     </row>
-    <row r="226" spans="70:70">
-      <c r="BR226" t="s">
+    <row r="222" spans="71:71">
+      <c r="BS222" t="s">
         <v>701</v>
       </c>
     </row>
-    <row r="227" spans="70:70">
-      <c r="BR227" t="s">
+    <row r="223" spans="71:71">
+      <c r="BS223" t="s">
         <v>702</v>
       </c>
     </row>
-    <row r="228" spans="70:70">
-      <c r="BR228" t="s">
+    <row r="224" spans="71:71">
+      <c r="BS224" t="s">
         <v>703</v>
       </c>
     </row>
-    <row r="229" spans="70:70">
-      <c r="BR229" t="s">
+    <row r="225" spans="71:71">
+      <c r="BS225" t="s">
         <v>704</v>
       </c>
     </row>
-    <row r="230" spans="70:70">
-      <c r="BR230" t="s">
+    <row r="226" spans="71:71">
+      <c r="BS226" t="s">
         <v>705</v>
       </c>
     </row>
-    <row r="231" spans="70:70">
-      <c r="BR231" t="s">
+    <row r="227" spans="71:71">
+      <c r="BS227" t="s">
         <v>706</v>
       </c>
     </row>
-    <row r="232" spans="70:70">
-      <c r="BR232" t="s">
+    <row r="228" spans="71:71">
+      <c r="BS228" t="s">
         <v>707</v>
       </c>
     </row>
-    <row r="233" spans="70:70">
-      <c r="BR233" t="s">
+    <row r="229" spans="71:71">
+      <c r="BS229" t="s">
         <v>708</v>
       </c>
     </row>
-    <row r="234" spans="70:70">
-      <c r="BR234" t="s">
+    <row r="230" spans="71:71">
+      <c r="BS230" t="s">
         <v>709</v>
       </c>
     </row>
-    <row r="235" spans="70:70">
-      <c r="BR235" t="s">
+    <row r="231" spans="71:71">
+      <c r="BS231" t="s">
         <v>710</v>
       </c>
     </row>
-    <row r="236" spans="70:70">
-      <c r="BR236" t="s">
+    <row r="232" spans="71:71">
+      <c r="BS232" t="s">
         <v>711</v>
       </c>
     </row>
-    <row r="237" spans="70:70">
-      <c r="BR237" t="s">
+    <row r="233" spans="71:71">
+      <c r="BS233" t="s">
         <v>712</v>
       </c>
     </row>
-    <row r="238" spans="70:70">
-      <c r="BR238" t="s">
+    <row r="234" spans="71:71">
+      <c r="BS234" t="s">
         <v>713</v>
       </c>
     </row>
-    <row r="239" spans="70:70">
-      <c r="BR239" t="s">
+    <row r="235" spans="71:71">
+      <c r="BS235" t="s">
         <v>714</v>
       </c>
     </row>
-    <row r="240" spans="70:70">
-      <c r="BR240" t="s">
+    <row r="236" spans="71:71">
+      <c r="BS236" t="s">
         <v>715</v>
       </c>
     </row>
-    <row r="241" spans="70:70">
-      <c r="BR241" t="s">
+    <row r="237" spans="71:71">
+      <c r="BS237" t="s">
         <v>716</v>
       </c>
     </row>
-    <row r="242" spans="70:70">
-      <c r="BR242" t="s">
+    <row r="238" spans="71:71">
+      <c r="BS238" t="s">
         <v>717</v>
       </c>
     </row>
-    <row r="243" spans="70:70">
-      <c r="BR243" t="s">
+    <row r="239" spans="71:71">
+      <c r="BS239" t="s">
         <v>718</v>
       </c>
     </row>
-    <row r="244" spans="70:70">
-      <c r="BR244" t="s">
+    <row r="240" spans="71:71">
+      <c r="BS240" t="s">
         <v>719</v>
       </c>
     </row>
-    <row r="245" spans="70:70">
-      <c r="BR245" t="s">
+    <row r="241" spans="71:71">
+      <c r="BS241" t="s">
         <v>720</v>
       </c>
     </row>
-    <row r="246" spans="70:70">
-      <c r="BR246" t="s">
+    <row r="242" spans="71:71">
+      <c r="BS242" t="s">
         <v>721</v>
       </c>
     </row>
-    <row r="247" spans="70:70">
-      <c r="BR247" t="s">
+    <row r="243" spans="71:71">
+      <c r="BS243" t="s">
         <v>722</v>
       </c>
     </row>
-    <row r="248" spans="70:70">
-      <c r="BR248" t="s">
+    <row r="244" spans="71:71">
+      <c r="BS244" t="s">
         <v>723</v>
       </c>
     </row>
-    <row r="249" spans="70:70">
-      <c r="BR249" t="s">
+    <row r="245" spans="71:71">
+      <c r="BS245" t="s">
         <v>724</v>
       </c>
     </row>
-    <row r="250" spans="70:70">
-      <c r="BR250" t="s">
+    <row r="246" spans="71:71">
+      <c r="BS246" t="s">
         <v>725</v>
       </c>
     </row>
-    <row r="251" spans="70:70">
-      <c r="BR251" t="s">
+    <row r="247" spans="71:71">
+      <c r="BS247" t="s">
         <v>726</v>
       </c>
     </row>
-    <row r="252" spans="70:70">
-      <c r="BR252" t="s">
+    <row r="248" spans="71:71">
+      <c r="BS248" t="s">
         <v>727</v>
       </c>
     </row>
-    <row r="253" spans="70:70">
-      <c r="BR253" t="s">
+    <row r="249" spans="71:71">
+      <c r="BS249" t="s">
         <v>728</v>
       </c>
     </row>
-    <row r="254" spans="70:70">
-      <c r="BR254" t="s">
+    <row r="250" spans="71:71">
+      <c r="BS250" t="s">
         <v>729</v>
       </c>
     </row>
-    <row r="255" spans="70:70">
-      <c r="BR255" t="s">
+    <row r="251" spans="71:71">
+      <c r="BS251" t="s">
         <v>730</v>
       </c>
     </row>
-    <row r="256" spans="70:70">
-      <c r="BR256" t="s">
+    <row r="252" spans="71:71">
+      <c r="BS252" t="s">
         <v>731</v>
       </c>
     </row>
-    <row r="257" spans="70:70">
-      <c r="BR257" t="s">
+    <row r="253" spans="71:71">
+      <c r="BS253" t="s">
         <v>732</v>
       </c>
     </row>
-    <row r="258" spans="70:70">
-      <c r="BR258" t="s">
+    <row r="254" spans="71:71">
+      <c r="BS254" t="s">
         <v>733</v>
       </c>
     </row>
-    <row r="259" spans="70:70">
-      <c r="BR259" t="s">
+    <row r="255" spans="71:71">
+      <c r="BS255" t="s">
         <v>734</v>
       </c>
     </row>
-    <row r="260" spans="70:70">
-      <c r="BR260" t="s">
+    <row r="256" spans="71:71">
+      <c r="BS256" t="s">
         <v>735</v>
       </c>
     </row>
-    <row r="261" spans="70:70">
-      <c r="BR261" t="s">
+    <row r="257" spans="71:71">
+      <c r="BS257" t="s">
         <v>736</v>
       </c>
     </row>
-    <row r="262" spans="70:70">
-      <c r="BR262" t="s">
+    <row r="258" spans="71:71">
+      <c r="BS258" t="s">
         <v>737</v>
       </c>
     </row>
-    <row r="263" spans="70:70">
-      <c r="BR263" t="s">
+    <row r="259" spans="71:71">
+      <c r="BS259" t="s">
         <v>738</v>
       </c>
     </row>
-    <row r="264" spans="70:70">
-      <c r="BR264" t="s">
+    <row r="260" spans="71:71">
+      <c r="BS260" t="s">
         <v>739</v>
       </c>
     </row>
-    <row r="265" spans="70:70">
-      <c r="BR265" t="s">
+    <row r="261" spans="71:71">
+      <c r="BS261" t="s">
         <v>740</v>
       </c>
     </row>
-    <row r="266" spans="70:70">
-      <c r="BR266" t="s">
+    <row r="262" spans="71:71">
+      <c r="BS262" t="s">
         <v>741</v>
       </c>
     </row>
-    <row r="267" spans="70:70">
-      <c r="BR267" t="s">
+    <row r="263" spans="71:71">
+      <c r="BS263" t="s">
         <v>742</v>
       </c>
     </row>
-    <row r="268" spans="70:70">
-      <c r="BR268" t="s">
+    <row r="264" spans="71:71">
+      <c r="BS264" t="s">
         <v>743</v>
       </c>
     </row>
-    <row r="269" spans="70:70">
-      <c r="BR269" t="s">
+    <row r="265" spans="71:71">
+      <c r="BS265" t="s">
         <v>744</v>
       </c>
     </row>
-    <row r="270" spans="70:70">
-      <c r="BR270" t="s">
+    <row r="266" spans="71:71">
+      <c r="BS266" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="271" spans="70:70">
-      <c r="BR271" t="s">
+    <row r="267" spans="71:71">
+      <c r="BS267" t="s">
         <v>746</v>
       </c>
     </row>
-    <row r="272" spans="70:70">
-      <c r="BR272" t="s">
+    <row r="268" spans="71:71">
+      <c r="BS268" t="s">
         <v>747</v>
       </c>
     </row>
-    <row r="273" spans="70:70">
-      <c r="BR273" t="s">
+    <row r="269" spans="71:71">
+      <c r="BS269" t="s">
         <v>748</v>
       </c>
     </row>
-    <row r="274" spans="70:70">
-      <c r="BR274" t="s">
+    <row r="270" spans="71:71">
+      <c r="BS270" t="s">
         <v>749</v>
       </c>
     </row>
-    <row r="275" spans="70:70">
-      <c r="BR275" t="s">
+    <row r="271" spans="71:71">
+      <c r="BS271" t="s">
         <v>750</v>
       </c>
     </row>
-    <row r="276" spans="70:70">
-      <c r="BR276" t="s">
+    <row r="272" spans="71:71">
+      <c r="BS272" t="s">
         <v>751</v>
       </c>
     </row>
-    <row r="277" spans="70:70">
-      <c r="BR277" t="s">
+    <row r="273" spans="71:71">
+      <c r="BS273" t="s">
         <v>752</v>
       </c>
     </row>
-    <row r="278" spans="70:70">
-      <c r="BR278" t="s">
+    <row r="274" spans="71:71">
+      <c r="BS274" t="s">
         <v>753</v>
       </c>
     </row>
-    <row r="279" spans="70:70">
-      <c r="BR279" t="s">
+    <row r="275" spans="71:71">
+      <c r="BS275" t="s">
         <v>754</v>
       </c>
     </row>
-    <row r="280" spans="70:70">
-      <c r="BR280" t="s">
+    <row r="276" spans="71:71">
+      <c r="BS276" t="s">
         <v>755</v>
       </c>
     </row>
-    <row r="281" spans="70:70">
-      <c r="BR281" t="s">
+    <row r="277" spans="71:71">
+      <c r="BS277" t="s">
         <v>756</v>
       </c>
     </row>
-    <row r="282" spans="70:70">
-      <c r="BR282" t="s">
+    <row r="278" spans="71:71">
+      <c r="BS278" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="283" spans="70:70">
-      <c r="BR283" t="s">
+    <row r="279" spans="71:71">
+      <c r="BS279" t="s">
         <v>758</v>
       </c>
     </row>
-    <row r="284" spans="70:70">
-      <c r="BR284" t="s">
+    <row r="280" spans="71:71">
+      <c r="BS280" t="s">
         <v>759</v>
       </c>
     </row>
-    <row r="285" spans="70:70">
-      <c r="BR285" t="s">
+    <row r="281" spans="71:71">
+      <c r="BS281" t="s">
         <v>760</v>
       </c>
     </row>
-    <row r="286" spans="70:70">
-      <c r="BR286" t="s">
+    <row r="282" spans="71:71">
+      <c r="BS282" t="s">
         <v>761</v>
       </c>
     </row>
-    <row r="287" spans="70:70">
-      <c r="BR287" t="s">
+    <row r="283" spans="71:71">
+      <c r="BS283" t="s">
         <v>762</v>
       </c>
     </row>
-    <row r="288" spans="70:70">
-      <c r="BR288" t="s">
+    <row r="284" spans="71:71">
+      <c r="BS284" t="s">
         <v>763</v>
       </c>
     </row>
-    <row r="289" spans="70:70">
-      <c r="BR289" t="s">
+    <row r="285" spans="71:71">
+      <c r="BS285" t="s">
         <v>764</v>
+      </c>
+    </row>
+    <row r="286" spans="71:71">
+      <c r="BS286" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="287" spans="71:71">
+      <c r="BS287" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="288" spans="71:71">
+      <c r="BS288" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="289" spans="71:71">
+      <c r="BS289" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="290" spans="71:71">
+      <c r="BS290" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="291" spans="71:71">
+      <c r="BS291" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="292" spans="71:71">
+      <c r="BS292" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="293" spans="71:71">
+      <c r="BS293" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="294" spans="71:71">
+      <c r="BS294" t="s">
+        <v>773</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000055/metadata_template_ERC000055.xlsx
+++ b/templates/ERC000055/metadata_template_ERC000055.xlsx
@@ -17,31 +17,31 @@
     <sheet name="cv_sample" sheetId="8" state="hidden" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="drainageclassification">'cv_sample'!$CP$1:$CP$6</definedName>
+    <definedName name="drainageclassification">'cv_sample'!$CQ$1:$CQ$6</definedName>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$BS$1:$BS$294</definedName>
-    <definedName name="historytillage">'cv_sample'!$DJ$1:$DJ$9</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$BT$1:$BT$294</definedName>
+    <definedName name="historytillage">'cv_sample'!$DK$1:$DK$9</definedName>
     <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
-    <definedName name="oxygenationstatusofsample">'cv_sample'!$AA$1:$AA$2</definedName>
+    <definedName name="oxygenationstatusofsample">'cv_sample'!$AB$1:$AB$2</definedName>
     <definedName name="platform">'cv_experiment'!$M$1:$M$18</definedName>
-    <definedName name="profileposition">'cv_sample'!$CU$1:$CU$5</definedName>
-    <definedName name="relationshiptooxygen">'cv_sample'!$I$1:$I$7</definedName>
-    <definedName name="sequencequalitycheck">'cv_sample'!$AV$1:$AV$3</definedName>
-    <definedName name="singlecellorviralparticlelysisapproach">'cv_sample'!$ER$1:$ER$4</definedName>
-    <definedName name="soilhorizon">'cv_sample'!$CN$1:$CN$6</definedName>
-    <definedName name="soiltype">'cv_sample'!$U$1:$U$32</definedName>
+    <definedName name="profileposition">'cv_sample'!$CV$1:$CV$5</definedName>
+    <definedName name="relationshiptooxygen">'cv_sample'!$J$1:$J$7</definedName>
+    <definedName name="sequencequalitycheck">'cv_sample'!$AW$1:$AW$3</definedName>
+    <definedName name="singlecellorviralparticlelysisapproach">'cv_sample'!$ES$1:$ES$4</definedName>
+    <definedName name="soilhorizon">'cv_sample'!$CO$1:$CO$6</definedName>
+    <definedName name="soiltype">'cv_sample'!$V$1:$V$32</definedName>
     <definedName name="studytype">'cv_study'!$C$1:$C$15</definedName>
-    <definedName name="trophiclevel">'cv_sample'!$G$1:$G$30</definedName>
+    <definedName name="trophiclevel">'cv_sample'!$H$1:$H$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1036" uniqueCount="1028">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1038" uniqueCount="1030">
   <si>
     <t>alias</t>
   </si>
@@ -857,6 +857,12 @@
   </si>
   <si>
     <t>(Optional) Scientific name of sample that distinguishes its taxonomy.  please use a name or synonym that is tracked in the insdc taxonomy database. also, this field can be used to confirm the taxon_id setting.</t>
+  </si>
+  <si>
+    <t>common_name</t>
+  </si>
+  <si>
+    <t>(Optional) Genbank common name of the organism.  examples: human, mouse.</t>
   </si>
   <si>
     <t>sample_description</t>
@@ -4648,13 +4654,13 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:FZ2"/>
+  <dimension ref="A1:GA2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="301" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:182">
+    <row r="1" spans="1:183">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4674,13 +4680,13 @@
         <v>274</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>306</v>
+        <v>276</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>308</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>319</v>
@@ -4716,7 +4722,7 @@
         <v>339</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>373</v>
+        <v>341</v>
       </c>
       <c r="V1" s="1" t="s">
         <v>375</v>
@@ -4734,7 +4740,7 @@
         <v>383</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="AB1" s="1" t="s">
         <v>389</v>
@@ -4797,7 +4803,7 @@
         <v>427</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="AW1" s="1" t="s">
         <v>434</v>
@@ -4809,7 +4815,7 @@
         <v>438</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="BA1" s="1" t="s">
         <v>444</v>
@@ -4866,7 +4872,7 @@
         <v>478</v>
       </c>
       <c r="BS1" s="1" t="s">
-        <v>774</v>
+        <v>480</v>
       </c>
       <c r="BT1" s="1" t="s">
         <v>776</v>
@@ -4929,13 +4935,13 @@
         <v>814</v>
       </c>
       <c r="CN1" s="1" t="s">
-        <v>822</v>
+        <v>816</v>
       </c>
       <c r="CO1" s="1" t="s">
         <v>824</v>
       </c>
       <c r="CP1" s="1" t="s">
-        <v>832</v>
+        <v>826</v>
       </c>
       <c r="CQ1" s="1" t="s">
         <v>834</v>
@@ -4950,7 +4956,7 @@
         <v>840</v>
       </c>
       <c r="CU1" s="1" t="s">
-        <v>847</v>
+        <v>842</v>
       </c>
       <c r="CV1" s="1" t="s">
         <v>849</v>
@@ -4995,7 +5001,7 @@
         <v>875</v>
       </c>
       <c r="DJ1" s="1" t="s">
-        <v>886</v>
+        <v>877</v>
       </c>
       <c r="DK1" s="1" t="s">
         <v>888</v>
@@ -5097,7 +5103,7 @@
         <v>952</v>
       </c>
       <c r="ER1" s="1" t="s">
-        <v>958</v>
+        <v>954</v>
       </c>
       <c r="ES1" s="1" t="s">
         <v>960</v>
@@ -5201,8 +5207,11 @@
       <c r="FZ1" s="1" t="s">
         <v>1026</v>
       </c>
-    </row>
-    <row r="2" spans="1:182" ht="150" customHeight="1">
+      <c r="GA1" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="2" spans="1:183" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>266</v>
       </c>
@@ -5222,13 +5231,13 @@
         <v>275</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>307</v>
+        <v>277</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>309</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>320</v>
@@ -5264,7 +5273,7 @@
         <v>340</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>374</v>
+        <v>342</v>
       </c>
       <c r="V2" s="2" t="s">
         <v>376</v>
@@ -5282,7 +5291,7 @@
         <v>384</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="AB2" s="2" t="s">
         <v>390</v>
@@ -5345,7 +5354,7 @@
         <v>428</v>
       </c>
       <c r="AV2" s="2" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="AW2" s="2" t="s">
         <v>435</v>
@@ -5357,7 +5366,7 @@
         <v>439</v>
       </c>
       <c r="AZ2" s="2" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="BA2" s="2" t="s">
         <v>445</v>
@@ -5414,7 +5423,7 @@
         <v>479</v>
       </c>
       <c r="BS2" s="2" t="s">
-        <v>775</v>
+        <v>481</v>
       </c>
       <c r="BT2" s="2" t="s">
         <v>777</v>
@@ -5477,13 +5486,13 @@
         <v>815</v>
       </c>
       <c r="CN2" s="2" t="s">
-        <v>823</v>
+        <v>817</v>
       </c>
       <c r="CO2" s="2" t="s">
         <v>825</v>
       </c>
       <c r="CP2" s="2" t="s">
-        <v>833</v>
+        <v>827</v>
       </c>
       <c r="CQ2" s="2" t="s">
         <v>835</v>
@@ -5498,7 +5507,7 @@
         <v>841</v>
       </c>
       <c r="CU2" s="2" t="s">
-        <v>848</v>
+        <v>843</v>
       </c>
       <c r="CV2" s="2" t="s">
         <v>850</v>
@@ -5543,7 +5552,7 @@
         <v>876</v>
       </c>
       <c r="DJ2" s="2" t="s">
-        <v>887</v>
+        <v>878</v>
       </c>
       <c r="DK2" s="2" t="s">
         <v>889</v>
@@ -5645,7 +5654,7 @@
         <v>953</v>
       </c>
       <c r="ER2" s="2" t="s">
-        <v>959</v>
+        <v>955</v>
       </c>
       <c r="ES2" s="2" t="s">
         <v>961</v>
@@ -5749,43 +5758,46 @@
       <c r="FZ2" s="2" t="s">
         <v>1027</v>
       </c>
+      <c r="GA2" s="2" t="s">
+        <v>1029</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="12">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H101">
       <formula1>trophiclevel</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I3:I101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J3:J101">
       <formula1>relationshiptooxygen</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U3:U101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V3:V101">
       <formula1>soiltype</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA3:AA101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB3:AB101">
       <formula1>oxygenationstatusofsample</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AV3:AV101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AW3:AW101">
       <formula1>sequencequalitycheck</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AZ3:AZ101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BA3:BA101">
       <formula1>16srecovered</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BS3:BS101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BT3:BT101">
       <formula1>geographiclocationcountryandorsea</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CN3:CN101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CO3:CO101">
       <formula1>soilhorizon</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CP3:CP101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CQ3:CQ101">
       <formula1>drainageclassification</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CU3:CU101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CV3:CV101">
       <formula1>profileposition</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="DJ3:DJ101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="DK3:DK101">
       <formula1>historytillage</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="ER3:ER101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="ES3:ES101">
       <formula1>singlecellorviralparticlelysisapproach</formula1>
     </dataValidation>
   </dataValidations>
@@ -5795,1795 +5807,1795 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:ER294"/>
+  <dimension ref="H1:ES294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="7:148">
-      <c r="G1" t="s">
-        <v>276</v>
-      </c>
-      <c r="I1" t="s">
-        <v>310</v>
-      </c>
-      <c r="U1" t="s">
-        <v>341</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>385</v>
-      </c>
-      <c r="AV1" t="s">
-        <v>429</v>
-      </c>
-      <c r="AZ1" t="s">
-        <v>440</v>
-      </c>
-      <c r="BS1" t="s">
-        <v>480</v>
-      </c>
-      <c r="CN1" t="s">
-        <v>816</v>
-      </c>
-      <c r="CP1" t="s">
-        <v>826</v>
-      </c>
-      <c r="CU1" t="s">
-        <v>842</v>
-      </c>
-      <c r="DJ1" t="s">
-        <v>877</v>
-      </c>
-      <c r="ER1" t="s">
-        <v>954</v>
-      </c>
-    </row>
-    <row r="2" spans="7:148">
-      <c r="G2" t="s">
-        <v>277</v>
-      </c>
-      <c r="I2" t="s">
-        <v>311</v>
-      </c>
-      <c r="U2" t="s">
-        <v>342</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>386</v>
-      </c>
-      <c r="AV2" t="s">
-        <v>430</v>
-      </c>
-      <c r="AZ2" t="s">
-        <v>441</v>
-      </c>
-      <c r="BS2" t="s">
-        <v>481</v>
-      </c>
-      <c r="CN2" t="s">
-        <v>817</v>
-      </c>
-      <c r="CP2" t="s">
-        <v>827</v>
-      </c>
-      <c r="CU2" t="s">
-        <v>843</v>
-      </c>
-      <c r="DJ2" t="s">
-        <v>878</v>
-      </c>
-      <c r="ER2" t="s">
-        <v>955</v>
-      </c>
-    </row>
-    <row r="3" spans="7:148">
-      <c r="G3" t="s">
+    <row r="1" spans="8:149">
+      <c r="H1" t="s">
         <v>278</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J1" t="s">
         <v>312</v>
       </c>
-      <c r="U3" t="s">
+      <c r="V1" t="s">
         <v>343</v>
       </c>
-      <c r="AV3" t="s">
+      <c r="AB1" t="s">
+        <v>387</v>
+      </c>
+      <c r="AW1" t="s">
         <v>431</v>
       </c>
-      <c r="BS3" t="s">
+      <c r="BA1" t="s">
+        <v>442</v>
+      </c>
+      <c r="BT1" t="s">
         <v>482</v>
       </c>
-      <c r="CN3" t="s">
+      <c r="CO1" t="s">
         <v>818</v>
       </c>
-      <c r="CP3" t="s">
+      <c r="CQ1" t="s">
         <v>828</v>
       </c>
-      <c r="CU3" t="s">
+      <c r="CV1" t="s">
         <v>844</v>
       </c>
-      <c r="DJ3" t="s">
+      <c r="DK1" t="s">
         <v>879</v>
       </c>
-      <c r="ER3" t="s">
+      <c r="ES1" t="s">
         <v>956</v>
       </c>
     </row>
-    <row r="4" spans="7:148">
-      <c r="G4" t="s">
+    <row r="2" spans="8:149">
+      <c r="H2" t="s">
         <v>279</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J2" t="s">
         <v>313</v>
       </c>
-      <c r="U4" t="s">
+      <c r="V2" t="s">
         <v>344</v>
       </c>
-      <c r="BS4" t="s">
+      <c r="AB2" t="s">
+        <v>388</v>
+      </c>
+      <c r="AW2" t="s">
+        <v>432</v>
+      </c>
+      <c r="BA2" t="s">
+        <v>443</v>
+      </c>
+      <c r="BT2" t="s">
         <v>483</v>
       </c>
-      <c r="CN4" t="s">
+      <c r="CO2" t="s">
         <v>819</v>
       </c>
-      <c r="CP4" t="s">
+      <c r="CQ2" t="s">
         <v>829</v>
       </c>
-      <c r="CU4" t="s">
+      <c r="CV2" t="s">
         <v>845</v>
       </c>
-      <c r="DJ4" t="s">
+      <c r="DK2" t="s">
         <v>880</v>
       </c>
-      <c r="ER4" t="s">
+      <c r="ES2" t="s">
         <v>957</v>
       </c>
     </row>
-    <row r="5" spans="7:148">
-      <c r="G5" t="s">
+    <row r="3" spans="8:149">
+      <c r="H3" t="s">
         <v>280</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J3" t="s">
         <v>314</v>
       </c>
-      <c r="U5" t="s">
+      <c r="V3" t="s">
         <v>345</v>
       </c>
-      <c r="BS5" t="s">
+      <c r="AW3" t="s">
+        <v>433</v>
+      </c>
+      <c r="BT3" t="s">
         <v>484</v>
       </c>
-      <c r="CN5" t="s">
+      <c r="CO3" t="s">
         <v>820</v>
       </c>
-      <c r="CP5" t="s">
+      <c r="CQ3" t="s">
         <v>830</v>
       </c>
-      <c r="CU5" t="s">
+      <c r="CV3" t="s">
         <v>846</v>
       </c>
-      <c r="DJ5" t="s">
+      <c r="DK3" t="s">
         <v>881</v>
       </c>
-    </row>
-    <row r="6" spans="7:148">
-      <c r="G6" t="s">
+      <c r="ES3" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="4" spans="8:149">
+      <c r="H4" t="s">
         <v>281</v>
       </c>
-      <c r="I6" t="s">
+      <c r="J4" t="s">
         <v>315</v>
       </c>
-      <c r="U6" t="s">
+      <c r="V4" t="s">
         <v>346</v>
       </c>
-      <c r="BS6" t="s">
+      <c r="BT4" t="s">
         <v>485</v>
       </c>
-      <c r="CN6" t="s">
+      <c r="CO4" t="s">
         <v>821</v>
       </c>
-      <c r="CP6" t="s">
+      <c r="CQ4" t="s">
         <v>831</v>
       </c>
-      <c r="DJ6" t="s">
+      <c r="CV4" t="s">
+        <v>847</v>
+      </c>
+      <c r="DK4" t="s">
         <v>882</v>
       </c>
-    </row>
-    <row r="7" spans="7:148">
-      <c r="G7" t="s">
+      <c r="ES4" t="s">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="5" spans="8:149">
+      <c r="H5" t="s">
         <v>282</v>
       </c>
-      <c r="I7" t="s">
+      <c r="J5" t="s">
         <v>316</v>
       </c>
-      <c r="U7" t="s">
+      <c r="V5" t="s">
         <v>347</v>
       </c>
-      <c r="BS7" t="s">
+      <c r="BT5" t="s">
         <v>486</v>
       </c>
-      <c r="DJ7" t="s">
+      <c r="CO5" t="s">
+        <v>822</v>
+      </c>
+      <c r="CQ5" t="s">
+        <v>832</v>
+      </c>
+      <c r="CV5" t="s">
+        <v>848</v>
+      </c>
+      <c r="DK5" t="s">
         <v>883</v>
       </c>
     </row>
-    <row r="8" spans="7:148">
-      <c r="G8" t="s">
+    <row r="6" spans="8:149">
+      <c r="H6" t="s">
         <v>283</v>
       </c>
-      <c r="U8" t="s">
+      <c r="J6" t="s">
+        <v>317</v>
+      </c>
+      <c r="V6" t="s">
         <v>348</v>
       </c>
-      <c r="BS8" t="s">
+      <c r="BT6" t="s">
         <v>487</v>
       </c>
-      <c r="DJ8" t="s">
+      <c r="CO6" t="s">
+        <v>823</v>
+      </c>
+      <c r="CQ6" t="s">
+        <v>833</v>
+      </c>
+      <c r="DK6" t="s">
         <v>884</v>
       </c>
     </row>
-    <row r="9" spans="7:148">
-      <c r="G9" t="s">
+    <row r="7" spans="8:149">
+      <c r="H7" t="s">
         <v>284</v>
       </c>
-      <c r="U9" t="s">
+      <c r="J7" t="s">
+        <v>318</v>
+      </c>
+      <c r="V7" t="s">
         <v>349</v>
       </c>
-      <c r="BS9" t="s">
+      <c r="BT7" t="s">
         <v>488</v>
       </c>
-      <c r="DJ9" t="s">
+      <c r="DK7" t="s">
         <v>885</v>
       </c>
     </row>
-    <row r="10" spans="7:148">
-      <c r="G10" t="s">
+    <row r="8" spans="8:149">
+      <c r="H8" t="s">
         <v>285</v>
       </c>
-      <c r="U10" t="s">
+      <c r="V8" t="s">
         <v>350</v>
       </c>
-      <c r="BS10" t="s">
+      <c r="BT8" t="s">
         <v>489</v>
       </c>
-    </row>
-    <row r="11" spans="7:148">
-      <c r="G11" t="s">
+      <c r="DK8" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="9" spans="8:149">
+      <c r="H9" t="s">
         <v>286</v>
       </c>
-      <c r="U11" t="s">
+      <c r="V9" t="s">
         <v>351</v>
       </c>
-      <c r="BS11" t="s">
+      <c r="BT9" t="s">
         <v>490</v>
       </c>
-    </row>
-    <row r="12" spans="7:148">
-      <c r="G12" t="s">
+      <c r="DK9" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="10" spans="8:149">
+      <c r="H10" t="s">
         <v>287</v>
       </c>
-      <c r="U12" t="s">
+      <c r="V10" t="s">
         <v>352</v>
       </c>
-      <c r="BS12" t="s">
+      <c r="BT10" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="13" spans="7:148">
-      <c r="G13" t="s">
+    <row r="11" spans="8:149">
+      <c r="H11" t="s">
         <v>288</v>
       </c>
-      <c r="U13" t="s">
+      <c r="V11" t="s">
         <v>353</v>
       </c>
-      <c r="BS13" t="s">
+      <c r="BT11" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="14" spans="7:148">
-      <c r="G14" t="s">
+    <row r="12" spans="8:149">
+      <c r="H12" t="s">
         <v>289</v>
       </c>
-      <c r="U14" t="s">
+      <c r="V12" t="s">
         <v>354</v>
       </c>
-      <c r="BS14" t="s">
+      <c r="BT12" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="15" spans="7:148">
-      <c r="G15" t="s">
+    <row r="13" spans="8:149">
+      <c r="H13" t="s">
         <v>290</v>
       </c>
-      <c r="U15" t="s">
+      <c r="V13" t="s">
         <v>355</v>
       </c>
-      <c r="BS15" t="s">
+      <c r="BT13" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="16" spans="7:148">
-      <c r="G16" t="s">
+    <row r="14" spans="8:149">
+      <c r="H14" t="s">
         <v>291</v>
       </c>
-      <c r="U16" t="s">
+      <c r="V14" t="s">
         <v>356</v>
       </c>
-      <c r="BS16" t="s">
+      <c r="BT14" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="17" spans="7:71">
-      <c r="G17" t="s">
+    <row r="15" spans="8:149">
+      <c r="H15" t="s">
         <v>292</v>
       </c>
-      <c r="U17" t="s">
+      <c r="V15" t="s">
         <v>357</v>
       </c>
-      <c r="BS17" t="s">
+      <c r="BT15" t="s">
         <v>496</v>
       </c>
     </row>
-    <row r="18" spans="7:71">
-      <c r="G18" t="s">
+    <row r="16" spans="8:149">
+      <c r="H16" t="s">
         <v>293</v>
       </c>
-      <c r="U18" t="s">
+      <c r="V16" t="s">
         <v>358</v>
       </c>
-      <c r="BS18" t="s">
+      <c r="BT16" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="19" spans="7:71">
-      <c r="G19" t="s">
+    <row r="17" spans="8:72">
+      <c r="H17" t="s">
         <v>294</v>
       </c>
-      <c r="U19" t="s">
+      <c r="V17" t="s">
         <v>359</v>
       </c>
-      <c r="BS19" t="s">
+      <c r="BT17" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="20" spans="7:71">
-      <c r="G20" t="s">
+    <row r="18" spans="8:72">
+      <c r="H18" t="s">
         <v>295</v>
       </c>
-      <c r="U20" t="s">
+      <c r="V18" t="s">
         <v>360</v>
       </c>
-      <c r="BS20" t="s">
+      <c r="BT18" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="21" spans="7:71">
-      <c r="G21" t="s">
+    <row r="19" spans="8:72">
+      <c r="H19" t="s">
         <v>296</v>
       </c>
-      <c r="U21" t="s">
+      <c r="V19" t="s">
         <v>361</v>
       </c>
-      <c r="BS21" t="s">
+      <c r="BT19" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="22" spans="7:71">
-      <c r="G22" t="s">
+    <row r="20" spans="8:72">
+      <c r="H20" t="s">
         <v>297</v>
       </c>
-      <c r="U22" t="s">
+      <c r="V20" t="s">
         <v>362</v>
       </c>
-      <c r="BS22" t="s">
+      <c r="BT20" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="23" spans="7:71">
-      <c r="G23" t="s">
+    <row r="21" spans="8:72">
+      <c r="H21" t="s">
         <v>298</v>
       </c>
-      <c r="U23" t="s">
+      <c r="V21" t="s">
         <v>363</v>
       </c>
-      <c r="BS23" t="s">
+      <c r="BT21" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="24" spans="7:71">
-      <c r="G24" t="s">
+    <row r="22" spans="8:72">
+      <c r="H22" t="s">
         <v>299</v>
       </c>
-      <c r="U24" t="s">
+      <c r="V22" t="s">
         <v>364</v>
       </c>
-      <c r="BS24" t="s">
+      <c r="BT22" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="25" spans="7:71">
-      <c r="G25" t="s">
+    <row r="23" spans="8:72">
+      <c r="H23" t="s">
         <v>300</v>
       </c>
-      <c r="U25" t="s">
+      <c r="V23" t="s">
         <v>365</v>
       </c>
-      <c r="BS25" t="s">
+      <c r="BT23" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="26" spans="7:71">
-      <c r="G26" t="s">
+    <row r="24" spans="8:72">
+      <c r="H24" t="s">
         <v>301</v>
       </c>
-      <c r="U26" t="s">
+      <c r="V24" t="s">
         <v>366</v>
       </c>
-      <c r="BS26" t="s">
+      <c r="BT24" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="27" spans="7:71">
-      <c r="G27" t="s">
+    <row r="25" spans="8:72">
+      <c r="H25" t="s">
         <v>302</v>
       </c>
-      <c r="U27" t="s">
+      <c r="V25" t="s">
         <v>367</v>
       </c>
-      <c r="BS27" t="s">
+      <c r="BT25" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="28" spans="7:71">
-      <c r="G28" t="s">
+    <row r="26" spans="8:72">
+      <c r="H26" t="s">
         <v>303</v>
       </c>
-      <c r="U28" t="s">
+      <c r="V26" t="s">
         <v>368</v>
       </c>
-      <c r="BS28" t="s">
+      <c r="BT26" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="29" spans="7:71">
-      <c r="G29" t="s">
+    <row r="27" spans="8:72">
+      <c r="H27" t="s">
         <v>304</v>
       </c>
-      <c r="U29" t="s">
+      <c r="V27" t="s">
         <v>369</v>
       </c>
-      <c r="BS29" t="s">
+      <c r="BT27" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="30" spans="7:71">
-      <c r="G30" t="s">
+    <row r="28" spans="8:72">
+      <c r="H28" t="s">
         <v>305</v>
       </c>
-      <c r="U30" t="s">
+      <c r="V28" t="s">
         <v>370</v>
       </c>
-      <c r="BS30" t="s">
+      <c r="BT28" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="31" spans="7:71">
-      <c r="U31" t="s">
+    <row r="29" spans="8:72">
+      <c r="H29" t="s">
+        <v>306</v>
+      </c>
+      <c r="V29" t="s">
         <v>371</v>
       </c>
-      <c r="BS31" t="s">
+      <c r="BT29" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="32" spans="7:71">
-      <c r="U32" t="s">
+    <row r="30" spans="8:72">
+      <c r="H30" t="s">
+        <v>307</v>
+      </c>
+      <c r="V30" t="s">
         <v>372</v>
       </c>
-      <c r="BS32" t="s">
+      <c r="BT30" t="s">
         <v>511</v>
       </c>
     </row>
-    <row r="33" spans="71:71">
-      <c r="BS33" t="s">
+    <row r="31" spans="8:72">
+      <c r="V31" t="s">
+        <v>373</v>
+      </c>
+      <c r="BT31" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="34" spans="71:71">
-      <c r="BS34" t="s">
+    <row r="32" spans="8:72">
+      <c r="V32" t="s">
+        <v>374</v>
+      </c>
+      <c r="BT32" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="35" spans="71:71">
-      <c r="BS35" t="s">
+    <row r="33" spans="72:72">
+      <c r="BT33" t="s">
         <v>514</v>
       </c>
     </row>
-    <row r="36" spans="71:71">
-      <c r="BS36" t="s">
+    <row r="34" spans="72:72">
+      <c r="BT34" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="37" spans="71:71">
-      <c r="BS37" t="s">
+    <row r="35" spans="72:72">
+      <c r="BT35" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="38" spans="71:71">
-      <c r="BS38" t="s">
+    <row r="36" spans="72:72">
+      <c r="BT36" t="s">
         <v>517</v>
       </c>
     </row>
-    <row r="39" spans="71:71">
-      <c r="BS39" t="s">
+    <row r="37" spans="72:72">
+      <c r="BT37" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="40" spans="71:71">
-      <c r="BS40" t="s">
+    <row r="38" spans="72:72">
+      <c r="BT38" t="s">
         <v>519</v>
       </c>
     </row>
-    <row r="41" spans="71:71">
-      <c r="BS41" t="s">
+    <row r="39" spans="72:72">
+      <c r="BT39" t="s">
         <v>520</v>
       </c>
     </row>
-    <row r="42" spans="71:71">
-      <c r="BS42" t="s">
+    <row r="40" spans="72:72">
+      <c r="BT40" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="43" spans="71:71">
-      <c r="BS43" t="s">
+    <row r="41" spans="72:72">
+      <c r="BT41" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="44" spans="71:71">
-      <c r="BS44" t="s">
+    <row r="42" spans="72:72">
+      <c r="BT42" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="45" spans="71:71">
-      <c r="BS45" t="s">
+    <row r="43" spans="72:72">
+      <c r="BT43" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="46" spans="71:71">
-      <c r="BS46" t="s">
+    <row r="44" spans="72:72">
+      <c r="BT44" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="47" spans="71:71">
-      <c r="BS47" t="s">
+    <row r="45" spans="72:72">
+      <c r="BT45" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="48" spans="71:71">
-      <c r="BS48" t="s">
+    <row r="46" spans="72:72">
+      <c r="BT46" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="49" spans="71:71">
-      <c r="BS49" t="s">
+    <row r="47" spans="72:72">
+      <c r="BT47" t="s">
         <v>528</v>
       </c>
     </row>
-    <row r="50" spans="71:71">
-      <c r="BS50" t="s">
+    <row r="48" spans="72:72">
+      <c r="BT48" t="s">
         <v>529</v>
       </c>
     </row>
-    <row r="51" spans="71:71">
-      <c r="BS51" t="s">
+    <row r="49" spans="72:72">
+      <c r="BT49" t="s">
         <v>530</v>
       </c>
     </row>
-    <row r="52" spans="71:71">
-      <c r="BS52" t="s">
+    <row r="50" spans="72:72">
+      <c r="BT50" t="s">
         <v>531</v>
       </c>
     </row>
-    <row r="53" spans="71:71">
-      <c r="BS53" t="s">
+    <row r="51" spans="72:72">
+      <c r="BT51" t="s">
         <v>532</v>
       </c>
     </row>
-    <row r="54" spans="71:71">
-      <c r="BS54" t="s">
+    <row r="52" spans="72:72">
+      <c r="BT52" t="s">
         <v>533</v>
       </c>
     </row>
-    <row r="55" spans="71:71">
-      <c r="BS55" t="s">
+    <row r="53" spans="72:72">
+      <c r="BT53" t="s">
         <v>534</v>
       </c>
     </row>
-    <row r="56" spans="71:71">
-      <c r="BS56" t="s">
+    <row r="54" spans="72:72">
+      <c r="BT54" t="s">
         <v>535</v>
       </c>
     </row>
-    <row r="57" spans="71:71">
-      <c r="BS57" t="s">
+    <row r="55" spans="72:72">
+      <c r="BT55" t="s">
         <v>536</v>
       </c>
     </row>
-    <row r="58" spans="71:71">
-      <c r="BS58" t="s">
+    <row r="56" spans="72:72">
+      <c r="BT56" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="59" spans="71:71">
-      <c r="BS59" t="s">
+    <row r="57" spans="72:72">
+      <c r="BT57" t="s">
         <v>538</v>
       </c>
     </row>
-    <row r="60" spans="71:71">
-      <c r="BS60" t="s">
+    <row r="58" spans="72:72">
+      <c r="BT58" t="s">
         <v>539</v>
       </c>
     </row>
-    <row r="61" spans="71:71">
-      <c r="BS61" t="s">
+    <row r="59" spans="72:72">
+      <c r="BT59" t="s">
         <v>540</v>
       </c>
     </row>
-    <row r="62" spans="71:71">
-      <c r="BS62" t="s">
+    <row r="60" spans="72:72">
+      <c r="BT60" t="s">
         <v>541</v>
       </c>
     </row>
-    <row r="63" spans="71:71">
-      <c r="BS63" t="s">
+    <row r="61" spans="72:72">
+      <c r="BT61" t="s">
         <v>542</v>
       </c>
     </row>
-    <row r="64" spans="71:71">
-      <c r="BS64" t="s">
+    <row r="62" spans="72:72">
+      <c r="BT62" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="65" spans="71:71">
-      <c r="BS65" t="s">
+    <row r="63" spans="72:72">
+      <c r="BT63" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="66" spans="71:71">
-      <c r="BS66" t="s">
+    <row r="64" spans="72:72">
+      <c r="BT64" t="s">
         <v>545</v>
       </c>
     </row>
-    <row r="67" spans="71:71">
-      <c r="BS67" t="s">
+    <row r="65" spans="72:72">
+      <c r="BT65" t="s">
         <v>546</v>
       </c>
     </row>
-    <row r="68" spans="71:71">
-      <c r="BS68" t="s">
+    <row r="66" spans="72:72">
+      <c r="BT66" t="s">
         <v>547</v>
       </c>
     </row>
-    <row r="69" spans="71:71">
-      <c r="BS69" t="s">
+    <row r="67" spans="72:72">
+      <c r="BT67" t="s">
         <v>548</v>
       </c>
     </row>
-    <row r="70" spans="71:71">
-      <c r="BS70" t="s">
+    <row r="68" spans="72:72">
+      <c r="BT68" t="s">
         <v>549</v>
       </c>
     </row>
-    <row r="71" spans="71:71">
-      <c r="BS71" t="s">
+    <row r="69" spans="72:72">
+      <c r="BT69" t="s">
         <v>550</v>
       </c>
     </row>
-    <row r="72" spans="71:71">
-      <c r="BS72" t="s">
+    <row r="70" spans="72:72">
+      <c r="BT70" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="73" spans="71:71">
-      <c r="BS73" t="s">
+    <row r="71" spans="72:72">
+      <c r="BT71" t="s">
         <v>552</v>
       </c>
     </row>
-    <row r="74" spans="71:71">
-      <c r="BS74" t="s">
+    <row r="72" spans="72:72">
+      <c r="BT72" t="s">
         <v>553</v>
       </c>
     </row>
-    <row r="75" spans="71:71">
-      <c r="BS75" t="s">
+    <row r="73" spans="72:72">
+      <c r="BT73" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="76" spans="71:71">
-      <c r="BS76" t="s">
+    <row r="74" spans="72:72">
+      <c r="BT74" t="s">
         <v>555</v>
       </c>
     </row>
-    <row r="77" spans="71:71">
-      <c r="BS77" t="s">
+    <row r="75" spans="72:72">
+      <c r="BT75" t="s">
         <v>556</v>
       </c>
     </row>
-    <row r="78" spans="71:71">
-      <c r="BS78" t="s">
+    <row r="76" spans="72:72">
+      <c r="BT76" t="s">
         <v>557</v>
       </c>
     </row>
-    <row r="79" spans="71:71">
-      <c r="BS79" t="s">
+    <row r="77" spans="72:72">
+      <c r="BT77" t="s">
         <v>558</v>
       </c>
     </row>
-    <row r="80" spans="71:71">
-      <c r="BS80" t="s">
+    <row r="78" spans="72:72">
+      <c r="BT78" t="s">
         <v>559</v>
       </c>
     </row>
-    <row r="81" spans="71:71">
-      <c r="BS81" t="s">
+    <row r="79" spans="72:72">
+      <c r="BT79" t="s">
         <v>560</v>
       </c>
     </row>
-    <row r="82" spans="71:71">
-      <c r="BS82" t="s">
+    <row r="80" spans="72:72">
+      <c r="BT80" t="s">
         <v>561</v>
       </c>
     </row>
-    <row r="83" spans="71:71">
-      <c r="BS83" t="s">
+    <row r="81" spans="72:72">
+      <c r="BT81" t="s">
         <v>562</v>
       </c>
     </row>
-    <row r="84" spans="71:71">
-      <c r="BS84" t="s">
+    <row r="82" spans="72:72">
+      <c r="BT82" t="s">
         <v>563</v>
       </c>
     </row>
-    <row r="85" spans="71:71">
-      <c r="BS85" t="s">
+    <row r="83" spans="72:72">
+      <c r="BT83" t="s">
         <v>564</v>
       </c>
     </row>
-    <row r="86" spans="71:71">
-      <c r="BS86" t="s">
+    <row r="84" spans="72:72">
+      <c r="BT84" t="s">
         <v>565</v>
       </c>
     </row>
-    <row r="87" spans="71:71">
-      <c r="BS87" t="s">
+    <row r="85" spans="72:72">
+      <c r="BT85" t="s">
         <v>566</v>
       </c>
     </row>
-    <row r="88" spans="71:71">
-      <c r="BS88" t="s">
+    <row r="86" spans="72:72">
+      <c r="BT86" t="s">
         <v>567</v>
       </c>
     </row>
-    <row r="89" spans="71:71">
-      <c r="BS89" t="s">
+    <row r="87" spans="72:72">
+      <c r="BT87" t="s">
         <v>568</v>
       </c>
     </row>
-    <row r="90" spans="71:71">
-      <c r="BS90" t="s">
+    <row r="88" spans="72:72">
+      <c r="BT88" t="s">
         <v>569</v>
       </c>
     </row>
-    <row r="91" spans="71:71">
-      <c r="BS91" t="s">
+    <row r="89" spans="72:72">
+      <c r="BT89" t="s">
         <v>570</v>
       </c>
     </row>
-    <row r="92" spans="71:71">
-      <c r="BS92" t="s">
+    <row r="90" spans="72:72">
+      <c r="BT90" t="s">
         <v>571</v>
       </c>
     </row>
-    <row r="93" spans="71:71">
-      <c r="BS93" t="s">
+    <row r="91" spans="72:72">
+      <c r="BT91" t="s">
         <v>572</v>
       </c>
     </row>
-    <row r="94" spans="71:71">
-      <c r="BS94" t="s">
+    <row r="92" spans="72:72">
+      <c r="BT92" t="s">
         <v>573</v>
       </c>
     </row>
-    <row r="95" spans="71:71">
-      <c r="BS95" t="s">
+    <row r="93" spans="72:72">
+      <c r="BT93" t="s">
         <v>574</v>
       </c>
     </row>
-    <row r="96" spans="71:71">
-      <c r="BS96" t="s">
+    <row r="94" spans="72:72">
+      <c r="BT94" t="s">
         <v>575</v>
       </c>
     </row>
-    <row r="97" spans="71:71">
-      <c r="BS97" t="s">
+    <row r="95" spans="72:72">
+      <c r="BT95" t="s">
         <v>576</v>
       </c>
     </row>
-    <row r="98" spans="71:71">
-      <c r="BS98" t="s">
+    <row r="96" spans="72:72">
+      <c r="BT96" t="s">
         <v>577</v>
       </c>
     </row>
-    <row r="99" spans="71:71">
-      <c r="BS99" t="s">
+    <row r="97" spans="72:72">
+      <c r="BT97" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="100" spans="71:71">
-      <c r="BS100" t="s">
+    <row r="98" spans="72:72">
+      <c r="BT98" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="101" spans="71:71">
-      <c r="BS101" t="s">
+    <row r="99" spans="72:72">
+      <c r="BT99" t="s">
         <v>580</v>
       </c>
     </row>
-    <row r="102" spans="71:71">
-      <c r="BS102" t="s">
+    <row r="100" spans="72:72">
+      <c r="BT100" t="s">
         <v>581</v>
       </c>
     </row>
-    <row r="103" spans="71:71">
-      <c r="BS103" t="s">
+    <row r="101" spans="72:72">
+      <c r="BT101" t="s">
         <v>582</v>
       </c>
     </row>
-    <row r="104" spans="71:71">
-      <c r="BS104" t="s">
+    <row r="102" spans="72:72">
+      <c r="BT102" t="s">
         <v>583</v>
       </c>
     </row>
-    <row r="105" spans="71:71">
-      <c r="BS105" t="s">
+    <row r="103" spans="72:72">
+      <c r="BT103" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="106" spans="71:71">
-      <c r="BS106" t="s">
+    <row r="104" spans="72:72">
+      <c r="BT104" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="107" spans="71:71">
-      <c r="BS107" t="s">
+    <row r="105" spans="72:72">
+      <c r="BT105" t="s">
         <v>586</v>
       </c>
     </row>
-    <row r="108" spans="71:71">
-      <c r="BS108" t="s">
+    <row r="106" spans="72:72">
+      <c r="BT106" t="s">
         <v>587</v>
       </c>
     </row>
-    <row r="109" spans="71:71">
-      <c r="BS109" t="s">
+    <row r="107" spans="72:72">
+      <c r="BT107" t="s">
         <v>588</v>
       </c>
     </row>
-    <row r="110" spans="71:71">
-      <c r="BS110" t="s">
+    <row r="108" spans="72:72">
+      <c r="BT108" t="s">
         <v>589</v>
       </c>
     </row>
-    <row r="111" spans="71:71">
-      <c r="BS111" t="s">
+    <row r="109" spans="72:72">
+      <c r="BT109" t="s">
         <v>590</v>
       </c>
     </row>
-    <row r="112" spans="71:71">
-      <c r="BS112" t="s">
+    <row r="110" spans="72:72">
+      <c r="BT110" t="s">
         <v>591</v>
       </c>
     </row>
-    <row r="113" spans="71:71">
-      <c r="BS113" t="s">
+    <row r="111" spans="72:72">
+      <c r="BT111" t="s">
         <v>592</v>
       </c>
     </row>
-    <row r="114" spans="71:71">
-      <c r="BS114" t="s">
+    <row r="112" spans="72:72">
+      <c r="BT112" t="s">
         <v>593</v>
       </c>
     </row>
-    <row r="115" spans="71:71">
-      <c r="BS115" t="s">
+    <row r="113" spans="72:72">
+      <c r="BT113" t="s">
         <v>594</v>
       </c>
     </row>
-    <row r="116" spans="71:71">
-      <c r="BS116" t="s">
+    <row r="114" spans="72:72">
+      <c r="BT114" t="s">
         <v>595</v>
       </c>
     </row>
-    <row r="117" spans="71:71">
-      <c r="BS117" t="s">
+    <row r="115" spans="72:72">
+      <c r="BT115" t="s">
         <v>596</v>
       </c>
     </row>
-    <row r="118" spans="71:71">
-      <c r="BS118" t="s">
+    <row r="116" spans="72:72">
+      <c r="BT116" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="119" spans="71:71">
-      <c r="BS119" t="s">
+    <row r="117" spans="72:72">
+      <c r="BT117" t="s">
         <v>598</v>
       </c>
     </row>
-    <row r="120" spans="71:71">
-      <c r="BS120" t="s">
+    <row r="118" spans="72:72">
+      <c r="BT118" t="s">
         <v>599</v>
       </c>
     </row>
-    <row r="121" spans="71:71">
-      <c r="BS121" t="s">
+    <row r="119" spans="72:72">
+      <c r="BT119" t="s">
         <v>600</v>
       </c>
     </row>
-    <row r="122" spans="71:71">
-      <c r="BS122" t="s">
+    <row r="120" spans="72:72">
+      <c r="BT120" t="s">
         <v>601</v>
       </c>
     </row>
-    <row r="123" spans="71:71">
-      <c r="BS123" t="s">
+    <row r="121" spans="72:72">
+      <c r="BT121" t="s">
         <v>602</v>
       </c>
     </row>
-    <row r="124" spans="71:71">
-      <c r="BS124" t="s">
+    <row r="122" spans="72:72">
+      <c r="BT122" t="s">
         <v>603</v>
       </c>
     </row>
-    <row r="125" spans="71:71">
-      <c r="BS125" t="s">
+    <row r="123" spans="72:72">
+      <c r="BT123" t="s">
         <v>604</v>
       </c>
     </row>
-    <row r="126" spans="71:71">
-      <c r="BS126" t="s">
+    <row r="124" spans="72:72">
+      <c r="BT124" t="s">
         <v>605</v>
       </c>
     </row>
-    <row r="127" spans="71:71">
-      <c r="BS127" t="s">
+    <row r="125" spans="72:72">
+      <c r="BT125" t="s">
         <v>606</v>
       </c>
     </row>
-    <row r="128" spans="71:71">
-      <c r="BS128" t="s">
+    <row r="126" spans="72:72">
+      <c r="BT126" t="s">
         <v>607</v>
       </c>
     </row>
-    <row r="129" spans="71:71">
-      <c r="BS129" t="s">
+    <row r="127" spans="72:72">
+      <c r="BT127" t="s">
         <v>608</v>
       </c>
     </row>
-    <row r="130" spans="71:71">
-      <c r="BS130" t="s">
+    <row r="128" spans="72:72">
+      <c r="BT128" t="s">
         <v>609</v>
       </c>
     </row>
-    <row r="131" spans="71:71">
-      <c r="BS131" t="s">
+    <row r="129" spans="72:72">
+      <c r="BT129" t="s">
         <v>610</v>
       </c>
     </row>
-    <row r="132" spans="71:71">
-      <c r="BS132" t="s">
+    <row r="130" spans="72:72">
+      <c r="BT130" t="s">
         <v>611</v>
       </c>
     </row>
-    <row r="133" spans="71:71">
-      <c r="BS133" t="s">
+    <row r="131" spans="72:72">
+      <c r="BT131" t="s">
         <v>612</v>
       </c>
     </row>
-    <row r="134" spans="71:71">
-      <c r="BS134" t="s">
+    <row r="132" spans="72:72">
+      <c r="BT132" t="s">
         <v>613</v>
       </c>
     </row>
-    <row r="135" spans="71:71">
-      <c r="BS135" t="s">
+    <row r="133" spans="72:72">
+      <c r="BT133" t="s">
         <v>614</v>
       </c>
     </row>
-    <row r="136" spans="71:71">
-      <c r="BS136" t="s">
+    <row r="134" spans="72:72">
+      <c r="BT134" t="s">
         <v>615</v>
       </c>
     </row>
-    <row r="137" spans="71:71">
-      <c r="BS137" t="s">
+    <row r="135" spans="72:72">
+      <c r="BT135" t="s">
         <v>616</v>
       </c>
     </row>
-    <row r="138" spans="71:71">
-      <c r="BS138" t="s">
+    <row r="136" spans="72:72">
+      <c r="BT136" t="s">
         <v>617</v>
       </c>
     </row>
-    <row r="139" spans="71:71">
-      <c r="BS139" t="s">
+    <row r="137" spans="72:72">
+      <c r="BT137" t="s">
         <v>618</v>
       </c>
     </row>
-    <row r="140" spans="71:71">
-      <c r="BS140" t="s">
+    <row r="138" spans="72:72">
+      <c r="BT138" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="141" spans="71:71">
-      <c r="BS141" t="s">
+    <row r="139" spans="72:72">
+      <c r="BT139" t="s">
         <v>620</v>
       </c>
     </row>
-    <row r="142" spans="71:71">
-      <c r="BS142" t="s">
+    <row r="140" spans="72:72">
+      <c r="BT140" t="s">
         <v>621</v>
       </c>
     </row>
-    <row r="143" spans="71:71">
-      <c r="BS143" t="s">
+    <row r="141" spans="72:72">
+      <c r="BT141" t="s">
         <v>622</v>
       </c>
     </row>
-    <row r="144" spans="71:71">
-      <c r="BS144" t="s">
+    <row r="142" spans="72:72">
+      <c r="BT142" t="s">
         <v>623</v>
       </c>
     </row>
-    <row r="145" spans="71:71">
-      <c r="BS145" t="s">
+    <row r="143" spans="72:72">
+      <c r="BT143" t="s">
         <v>624</v>
       </c>
     </row>
-    <row r="146" spans="71:71">
-      <c r="BS146" t="s">
+    <row r="144" spans="72:72">
+      <c r="BT144" t="s">
         <v>625</v>
       </c>
     </row>
-    <row r="147" spans="71:71">
-      <c r="BS147" t="s">
+    <row r="145" spans="72:72">
+      <c r="BT145" t="s">
         <v>626</v>
       </c>
     </row>
-    <row r="148" spans="71:71">
-      <c r="BS148" t="s">
+    <row r="146" spans="72:72">
+      <c r="BT146" t="s">
         <v>627</v>
       </c>
     </row>
-    <row r="149" spans="71:71">
-      <c r="BS149" t="s">
+    <row r="147" spans="72:72">
+      <c r="BT147" t="s">
         <v>628</v>
       </c>
     </row>
-    <row r="150" spans="71:71">
-      <c r="BS150" t="s">
+    <row r="148" spans="72:72">
+      <c r="BT148" t="s">
         <v>629</v>
       </c>
     </row>
-    <row r="151" spans="71:71">
-      <c r="BS151" t="s">
+    <row r="149" spans="72:72">
+      <c r="BT149" t="s">
         <v>630</v>
       </c>
     </row>
-    <row r="152" spans="71:71">
-      <c r="BS152" t="s">
+    <row r="150" spans="72:72">
+      <c r="BT150" t="s">
         <v>631</v>
       </c>
     </row>
-    <row r="153" spans="71:71">
-      <c r="BS153" t="s">
+    <row r="151" spans="72:72">
+      <c r="BT151" t="s">
         <v>632</v>
       </c>
     </row>
-    <row r="154" spans="71:71">
-      <c r="BS154" t="s">
+    <row r="152" spans="72:72">
+      <c r="BT152" t="s">
         <v>633</v>
       </c>
     </row>
-    <row r="155" spans="71:71">
-      <c r="BS155" t="s">
+    <row r="153" spans="72:72">
+      <c r="BT153" t="s">
         <v>634</v>
       </c>
     </row>
-    <row r="156" spans="71:71">
-      <c r="BS156" t="s">
+    <row r="154" spans="72:72">
+      <c r="BT154" t="s">
         <v>635</v>
       </c>
     </row>
-    <row r="157" spans="71:71">
-      <c r="BS157" t="s">
+    <row r="155" spans="72:72">
+      <c r="BT155" t="s">
         <v>636</v>
       </c>
     </row>
-    <row r="158" spans="71:71">
-      <c r="BS158" t="s">
+    <row r="156" spans="72:72">
+      <c r="BT156" t="s">
         <v>637</v>
       </c>
     </row>
-    <row r="159" spans="71:71">
-      <c r="BS159" t="s">
+    <row r="157" spans="72:72">
+      <c r="BT157" t="s">
         <v>638</v>
       </c>
     </row>
-    <row r="160" spans="71:71">
-      <c r="BS160" t="s">
+    <row r="158" spans="72:72">
+      <c r="BT158" t="s">
         <v>639</v>
       </c>
     </row>
-    <row r="161" spans="71:71">
-      <c r="BS161" t="s">
+    <row r="159" spans="72:72">
+      <c r="BT159" t="s">
         <v>640</v>
       </c>
     </row>
-    <row r="162" spans="71:71">
-      <c r="BS162" t="s">
+    <row r="160" spans="72:72">
+      <c r="BT160" t="s">
         <v>641</v>
       </c>
     </row>
-    <row r="163" spans="71:71">
-      <c r="BS163" t="s">
+    <row r="161" spans="72:72">
+      <c r="BT161" t="s">
         <v>642</v>
       </c>
     </row>
-    <row r="164" spans="71:71">
-      <c r="BS164" t="s">
+    <row r="162" spans="72:72">
+      <c r="BT162" t="s">
         <v>643</v>
       </c>
     </row>
-    <row r="165" spans="71:71">
-      <c r="BS165" t="s">
+    <row r="163" spans="72:72">
+      <c r="BT163" t="s">
         <v>644</v>
       </c>
     </row>
-    <row r="166" spans="71:71">
-      <c r="BS166" t="s">
+    <row r="164" spans="72:72">
+      <c r="BT164" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="167" spans="71:71">
-      <c r="BS167" t="s">
+    <row r="165" spans="72:72">
+      <c r="BT165" t="s">
         <v>646</v>
       </c>
     </row>
-    <row r="168" spans="71:71">
-      <c r="BS168" t="s">
+    <row r="166" spans="72:72">
+      <c r="BT166" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="169" spans="71:71">
-      <c r="BS169" t="s">
+    <row r="167" spans="72:72">
+      <c r="BT167" t="s">
         <v>648</v>
       </c>
     </row>
-    <row r="170" spans="71:71">
-      <c r="BS170" t="s">
+    <row r="168" spans="72:72">
+      <c r="BT168" t="s">
         <v>649</v>
       </c>
     </row>
-    <row r="171" spans="71:71">
-      <c r="BS171" t="s">
+    <row r="169" spans="72:72">
+      <c r="BT169" t="s">
         <v>650</v>
       </c>
     </row>
-    <row r="172" spans="71:71">
-      <c r="BS172" t="s">
+    <row r="170" spans="72:72">
+      <c r="BT170" t="s">
         <v>651</v>
       </c>
     </row>
-    <row r="173" spans="71:71">
-      <c r="BS173" t="s">
+    <row r="171" spans="72:72">
+      <c r="BT171" t="s">
         <v>652</v>
       </c>
     </row>
-    <row r="174" spans="71:71">
-      <c r="BS174" t="s">
+    <row r="172" spans="72:72">
+      <c r="BT172" t="s">
         <v>653</v>
       </c>
     </row>
-    <row r="175" spans="71:71">
-      <c r="BS175" t="s">
+    <row r="173" spans="72:72">
+      <c r="BT173" t="s">
         <v>654</v>
       </c>
     </row>
-    <row r="176" spans="71:71">
-      <c r="BS176" t="s">
+    <row r="174" spans="72:72">
+      <c r="BT174" t="s">
         <v>655</v>
       </c>
     </row>
-    <row r="177" spans="71:71">
-      <c r="BS177" t="s">
+    <row r="175" spans="72:72">
+      <c r="BT175" t="s">
         <v>656</v>
       </c>
     </row>
-    <row r="178" spans="71:71">
-      <c r="BS178" t="s">
+    <row r="176" spans="72:72">
+      <c r="BT176" t="s">
         <v>657</v>
       </c>
     </row>
-    <row r="179" spans="71:71">
-      <c r="BS179" t="s">
+    <row r="177" spans="72:72">
+      <c r="BT177" t="s">
         <v>658</v>
       </c>
     </row>
-    <row r="180" spans="71:71">
-      <c r="BS180" t="s">
+    <row r="178" spans="72:72">
+      <c r="BT178" t="s">
         <v>659</v>
       </c>
     </row>
-    <row r="181" spans="71:71">
-      <c r="BS181" t="s">
+    <row r="179" spans="72:72">
+      <c r="BT179" t="s">
         <v>660</v>
       </c>
     </row>
-    <row r="182" spans="71:71">
-      <c r="BS182" t="s">
+    <row r="180" spans="72:72">
+      <c r="BT180" t="s">
         <v>661</v>
       </c>
     </row>
-    <row r="183" spans="71:71">
-      <c r="BS183" t="s">
+    <row r="181" spans="72:72">
+      <c r="BT181" t="s">
         <v>662</v>
       </c>
     </row>
-    <row r="184" spans="71:71">
-      <c r="BS184" t="s">
+    <row r="182" spans="72:72">
+      <c r="BT182" t="s">
         <v>663</v>
       </c>
     </row>
-    <row r="185" spans="71:71">
-      <c r="BS185" t="s">
+    <row r="183" spans="72:72">
+      <c r="BT183" t="s">
         <v>664</v>
       </c>
     </row>
-    <row r="186" spans="71:71">
-      <c r="BS186" t="s">
+    <row r="184" spans="72:72">
+      <c r="BT184" t="s">
         <v>665</v>
       </c>
     </row>
-    <row r="187" spans="71:71">
-      <c r="BS187" t="s">
+    <row r="185" spans="72:72">
+      <c r="BT185" t="s">
         <v>666</v>
       </c>
     </row>
-    <row r="188" spans="71:71">
-      <c r="BS188" t="s">
+    <row r="186" spans="72:72">
+      <c r="BT186" t="s">
         <v>667</v>
       </c>
     </row>
-    <row r="189" spans="71:71">
-      <c r="BS189" t="s">
+    <row r="187" spans="72:72">
+      <c r="BT187" t="s">
         <v>668</v>
       </c>
     </row>
-    <row r="190" spans="71:71">
-      <c r="BS190" t="s">
+    <row r="188" spans="72:72">
+      <c r="BT188" t="s">
         <v>669</v>
       </c>
     </row>
-    <row r="191" spans="71:71">
-      <c r="BS191" t="s">
+    <row r="189" spans="72:72">
+      <c r="BT189" t="s">
         <v>670</v>
       </c>
     </row>
-    <row r="192" spans="71:71">
-      <c r="BS192" t="s">
+    <row r="190" spans="72:72">
+      <c r="BT190" t="s">
         <v>671</v>
       </c>
     </row>
-    <row r="193" spans="71:71">
-      <c r="BS193" t="s">
+    <row r="191" spans="72:72">
+      <c r="BT191" t="s">
         <v>672</v>
       </c>
     </row>
-    <row r="194" spans="71:71">
-      <c r="BS194" t="s">
+    <row r="192" spans="72:72">
+      <c r="BT192" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="195" spans="71:71">
-      <c r="BS195" t="s">
+    <row r="193" spans="72:72">
+      <c r="BT193" t="s">
         <v>674</v>
       </c>
     </row>
-    <row r="196" spans="71:71">
-      <c r="BS196" t="s">
+    <row r="194" spans="72:72">
+      <c r="BT194" t="s">
         <v>675</v>
       </c>
     </row>
-    <row r="197" spans="71:71">
-      <c r="BS197" t="s">
+    <row r="195" spans="72:72">
+      <c r="BT195" t="s">
         <v>676</v>
       </c>
     </row>
-    <row r="198" spans="71:71">
-      <c r="BS198" t="s">
+    <row r="196" spans="72:72">
+      <c r="BT196" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="199" spans="71:71">
-      <c r="BS199" t="s">
+    <row r="197" spans="72:72">
+      <c r="BT197" t="s">
         <v>678</v>
       </c>
     </row>
-    <row r="200" spans="71:71">
-      <c r="BS200" t="s">
+    <row r="198" spans="72:72">
+      <c r="BT198" t="s">
         <v>679</v>
       </c>
     </row>
-    <row r="201" spans="71:71">
-      <c r="BS201" t="s">
+    <row r="199" spans="72:72">
+      <c r="BT199" t="s">
         <v>680</v>
       </c>
     </row>
-    <row r="202" spans="71:71">
-      <c r="BS202" t="s">
+    <row r="200" spans="72:72">
+      <c r="BT200" t="s">
         <v>681</v>
       </c>
     </row>
-    <row r="203" spans="71:71">
-      <c r="BS203" t="s">
+    <row r="201" spans="72:72">
+      <c r="BT201" t="s">
         <v>682</v>
       </c>
     </row>
-    <row r="204" spans="71:71">
-      <c r="BS204" t="s">
+    <row r="202" spans="72:72">
+      <c r="BT202" t="s">
         <v>683</v>
       </c>
     </row>
-    <row r="205" spans="71:71">
-      <c r="BS205" t="s">
+    <row r="203" spans="72:72">
+      <c r="BT203" t="s">
         <v>684</v>
       </c>
     </row>
-    <row r="206" spans="71:71">
-      <c r="BS206" t="s">
+    <row r="204" spans="72:72">
+      <c r="BT204" t="s">
         <v>685</v>
       </c>
     </row>
-    <row r="207" spans="71:71">
-      <c r="BS207" t="s">
+    <row r="205" spans="72:72">
+      <c r="BT205" t="s">
         <v>686</v>
       </c>
     </row>
-    <row r="208" spans="71:71">
-      <c r="BS208" t="s">
+    <row r="206" spans="72:72">
+      <c r="BT206" t="s">
         <v>687</v>
       </c>
     </row>
-    <row r="209" spans="71:71">
-      <c r="BS209" t="s">
+    <row r="207" spans="72:72">
+      <c r="BT207" t="s">
         <v>688</v>
       </c>
     </row>
-    <row r="210" spans="71:71">
-      <c r="BS210" t="s">
+    <row r="208" spans="72:72">
+      <c r="BT208" t="s">
         <v>689</v>
       </c>
     </row>
-    <row r="211" spans="71:71">
-      <c r="BS211" t="s">
+    <row r="209" spans="72:72">
+      <c r="BT209" t="s">
         <v>690</v>
       </c>
     </row>
-    <row r="212" spans="71:71">
-      <c r="BS212" t="s">
+    <row r="210" spans="72:72">
+      <c r="BT210" t="s">
         <v>691</v>
       </c>
     </row>
-    <row r="213" spans="71:71">
-      <c r="BS213" t="s">
+    <row r="211" spans="72:72">
+      <c r="BT211" t="s">
         <v>692</v>
       </c>
     </row>
-    <row r="214" spans="71:71">
-      <c r="BS214" t="s">
+    <row r="212" spans="72:72">
+      <c r="BT212" t="s">
         <v>693</v>
       </c>
     </row>
-    <row r="215" spans="71:71">
-      <c r="BS215" t="s">
+    <row r="213" spans="72:72">
+      <c r="BT213" t="s">
         <v>694</v>
       </c>
     </row>
-    <row r="216" spans="71:71">
-      <c r="BS216" t="s">
+    <row r="214" spans="72:72">
+      <c r="BT214" t="s">
         <v>695</v>
       </c>
     </row>
-    <row r="217" spans="71:71">
-      <c r="BS217" t="s">
+    <row r="215" spans="72:72">
+      <c r="BT215" t="s">
         <v>696</v>
       </c>
     </row>
-    <row r="218" spans="71:71">
-      <c r="BS218" t="s">
+    <row r="216" spans="72:72">
+      <c r="BT216" t="s">
         <v>697</v>
       </c>
     </row>
-    <row r="219" spans="71:71">
-      <c r="BS219" t="s">
+    <row r="217" spans="72:72">
+      <c r="BT217" t="s">
         <v>698</v>
       </c>
     </row>
-    <row r="220" spans="71:71">
-      <c r="BS220" t="s">
+    <row r="218" spans="72:72">
+      <c r="BT218" t="s">
         <v>699</v>
       </c>
     </row>
-    <row r="221" spans="71:71">
-      <c r="BS221" t="s">
+    <row r="219" spans="72:72">
+      <c r="BT219" t="s">
         <v>700</v>
       </c>
     </row>
-    <row r="222" spans="71:71">
-      <c r="BS222" t="s">
+    <row r="220" spans="72:72">
+      <c r="BT220" t="s">
         <v>701</v>
       </c>
     </row>
-    <row r="223" spans="71:71">
-      <c r="BS223" t="s">
+    <row r="221" spans="72:72">
+      <c r="BT221" t="s">
         <v>702</v>
       </c>
     </row>
-    <row r="224" spans="71:71">
-      <c r="BS224" t="s">
+    <row r="222" spans="72:72">
+      <c r="BT222" t="s">
         <v>703</v>
       </c>
     </row>
-    <row r="225" spans="71:71">
-      <c r="BS225" t="s">
+    <row r="223" spans="72:72">
+      <c r="BT223" t="s">
         <v>704</v>
       </c>
     </row>
-    <row r="226" spans="71:71">
-      <c r="BS226" t="s">
+    <row r="224" spans="72:72">
+      <c r="BT224" t="s">
         <v>705</v>
       </c>
     </row>
-    <row r="227" spans="71:71">
-      <c r="BS227" t="s">
+    <row r="225" spans="72:72">
+      <c r="BT225" t="s">
         <v>706</v>
       </c>
     </row>
-    <row r="228" spans="71:71">
-      <c r="BS228" t="s">
+    <row r="226" spans="72:72">
+      <c r="BT226" t="s">
         <v>707</v>
       </c>
     </row>
-    <row r="229" spans="71:71">
-      <c r="BS229" t="s">
+    <row r="227" spans="72:72">
+      <c r="BT227" t="s">
         <v>708</v>
       </c>
     </row>
-    <row r="230" spans="71:71">
-      <c r="BS230" t="s">
+    <row r="228" spans="72:72">
+      <c r="BT228" t="s">
         <v>709</v>
       </c>
     </row>
-    <row r="231" spans="71:71">
-      <c r="BS231" t="s">
+    <row r="229" spans="72:72">
+      <c r="BT229" t="s">
         <v>710</v>
       </c>
     </row>
-    <row r="232" spans="71:71">
-      <c r="BS232" t="s">
+    <row r="230" spans="72:72">
+      <c r="BT230" t="s">
         <v>711</v>
       </c>
     </row>
-    <row r="233" spans="71:71">
-      <c r="BS233" t="s">
+    <row r="231" spans="72:72">
+      <c r="BT231" t="s">
         <v>712</v>
       </c>
     </row>
-    <row r="234" spans="71:71">
-      <c r="BS234" t="s">
+    <row r="232" spans="72:72">
+      <c r="BT232" t="s">
         <v>713</v>
       </c>
     </row>
-    <row r="235" spans="71:71">
-      <c r="BS235" t="s">
+    <row r="233" spans="72:72">
+      <c r="BT233" t="s">
         <v>714</v>
       </c>
     </row>
-    <row r="236" spans="71:71">
-      <c r="BS236" t="s">
+    <row r="234" spans="72:72">
+      <c r="BT234" t="s">
         <v>715</v>
       </c>
     </row>
-    <row r="237" spans="71:71">
-      <c r="BS237" t="s">
+    <row r="235" spans="72:72">
+      <c r="BT235" t="s">
         <v>716</v>
       </c>
     </row>
-    <row r="238" spans="71:71">
-      <c r="BS238" t="s">
+    <row r="236" spans="72:72">
+      <c r="BT236" t="s">
         <v>717</v>
       </c>
     </row>
-    <row r="239" spans="71:71">
-      <c r="BS239" t="s">
+    <row r="237" spans="72:72">
+      <c r="BT237" t="s">
         <v>718</v>
       </c>
     </row>
-    <row r="240" spans="71:71">
-      <c r="BS240" t="s">
+    <row r="238" spans="72:72">
+      <c r="BT238" t="s">
         <v>719</v>
       </c>
     </row>
-    <row r="241" spans="71:71">
-      <c r="BS241" t="s">
+    <row r="239" spans="72:72">
+      <c r="BT239" t="s">
         <v>720</v>
       </c>
     </row>
-    <row r="242" spans="71:71">
-      <c r="BS242" t="s">
+    <row r="240" spans="72:72">
+      <c r="BT240" t="s">
         <v>721</v>
       </c>
     </row>
-    <row r="243" spans="71:71">
-      <c r="BS243" t="s">
+    <row r="241" spans="72:72">
+      <c r="BT241" t="s">
         <v>722</v>
       </c>
     </row>
-    <row r="244" spans="71:71">
-      <c r="BS244" t="s">
+    <row r="242" spans="72:72">
+      <c r="BT242" t="s">
         <v>723</v>
       </c>
     </row>
-    <row r="245" spans="71:71">
-      <c r="BS245" t="s">
+    <row r="243" spans="72:72">
+      <c r="BT243" t="s">
         <v>724</v>
       </c>
     </row>
-    <row r="246" spans="71:71">
-      <c r="BS246" t="s">
+    <row r="244" spans="72:72">
+      <c r="BT244" t="s">
         <v>725</v>
       </c>
     </row>
-    <row r="247" spans="71:71">
-      <c r="BS247" t="s">
+    <row r="245" spans="72:72">
+      <c r="BT245" t="s">
         <v>726</v>
       </c>
     </row>
-    <row r="248" spans="71:71">
-      <c r="BS248" t="s">
+    <row r="246" spans="72:72">
+      <c r="BT246" t="s">
         <v>727</v>
       </c>
     </row>
-    <row r="249" spans="71:71">
-      <c r="BS249" t="s">
+    <row r="247" spans="72:72">
+      <c r="BT247" t="s">
         <v>728</v>
       </c>
     </row>
-    <row r="250" spans="71:71">
-      <c r="BS250" t="s">
+    <row r="248" spans="72:72">
+      <c r="BT248" t="s">
         <v>729</v>
       </c>
     </row>
-    <row r="251" spans="71:71">
-      <c r="BS251" t="s">
+    <row r="249" spans="72:72">
+      <c r="BT249" t="s">
         <v>730</v>
       </c>
     </row>
-    <row r="252" spans="71:71">
-      <c r="BS252" t="s">
+    <row r="250" spans="72:72">
+      <c r="BT250" t="s">
         <v>731</v>
       </c>
     </row>
-    <row r="253" spans="71:71">
-      <c r="BS253" t="s">
+    <row r="251" spans="72:72">
+      <c r="BT251" t="s">
         <v>732</v>
       </c>
     </row>
-    <row r="254" spans="71:71">
-      <c r="BS254" t="s">
+    <row r="252" spans="72:72">
+      <c r="BT252" t="s">
         <v>733</v>
       </c>
     </row>
-    <row r="255" spans="71:71">
-      <c r="BS255" t="s">
+    <row r="253" spans="72:72">
+      <c r="BT253" t="s">
         <v>734</v>
       </c>
     </row>
-    <row r="256" spans="71:71">
-      <c r="BS256" t="s">
+    <row r="254" spans="72:72">
+      <c r="BT254" t="s">
         <v>735</v>
       </c>
     </row>
-    <row r="257" spans="71:71">
-      <c r="BS257" t="s">
+    <row r="255" spans="72:72">
+      <c r="BT255" t="s">
         <v>736</v>
       </c>
     </row>
-    <row r="258" spans="71:71">
-      <c r="BS258" t="s">
+    <row r="256" spans="72:72">
+      <c r="BT256" t="s">
         <v>737</v>
       </c>
     </row>
-    <row r="259" spans="71:71">
-      <c r="BS259" t="s">
+    <row r="257" spans="72:72">
+      <c r="BT257" t="s">
         <v>738</v>
       </c>
     </row>
-    <row r="260" spans="71:71">
-      <c r="BS260" t="s">
+    <row r="258" spans="72:72">
+      <c r="BT258" t="s">
         <v>739</v>
       </c>
     </row>
-    <row r="261" spans="71:71">
-      <c r="BS261" t="s">
+    <row r="259" spans="72:72">
+      <c r="BT259" t="s">
         <v>740</v>
       </c>
     </row>
-    <row r="262" spans="71:71">
-      <c r="BS262" t="s">
+    <row r="260" spans="72:72">
+      <c r="BT260" t="s">
         <v>741</v>
       </c>
     </row>
-    <row r="263" spans="71:71">
-      <c r="BS263" t="s">
+    <row r="261" spans="72:72">
+      <c r="BT261" t="s">
         <v>742</v>
       </c>
     </row>
-    <row r="264" spans="71:71">
-      <c r="BS264" t="s">
+    <row r="262" spans="72:72">
+      <c r="BT262" t="s">
         <v>743</v>
       </c>
     </row>
-    <row r="265" spans="71:71">
-      <c r="BS265" t="s">
+    <row r="263" spans="72:72">
+      <c r="BT263" t="s">
         <v>744</v>
       </c>
     </row>
-    <row r="266" spans="71:71">
-      <c r="BS266" t="s">
+    <row r="264" spans="72:72">
+      <c r="BT264" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="267" spans="71:71">
-      <c r="BS267" t="s">
+    <row r="265" spans="72:72">
+      <c r="BT265" t="s">
         <v>746</v>
       </c>
     </row>
-    <row r="268" spans="71:71">
-      <c r="BS268" t="s">
+    <row r="266" spans="72:72">
+      <c r="BT266" t="s">
         <v>747</v>
       </c>
     </row>
-    <row r="269" spans="71:71">
-      <c r="BS269" t="s">
+    <row r="267" spans="72:72">
+      <c r="BT267" t="s">
         <v>748</v>
       </c>
     </row>
-    <row r="270" spans="71:71">
-      <c r="BS270" t="s">
+    <row r="268" spans="72:72">
+      <c r="BT268" t="s">
         <v>749</v>
       </c>
     </row>
-    <row r="271" spans="71:71">
-      <c r="BS271" t="s">
+    <row r="269" spans="72:72">
+      <c r="BT269" t="s">
         <v>750</v>
       </c>
     </row>
-    <row r="272" spans="71:71">
-      <c r="BS272" t="s">
+    <row r="270" spans="72:72">
+      <c r="BT270" t="s">
         <v>751</v>
       </c>
     </row>
-    <row r="273" spans="71:71">
-      <c r="BS273" t="s">
+    <row r="271" spans="72:72">
+      <c r="BT271" t="s">
         <v>752</v>
       </c>
     </row>
-    <row r="274" spans="71:71">
-      <c r="BS274" t="s">
+    <row r="272" spans="72:72">
+      <c r="BT272" t="s">
         <v>753</v>
       </c>
     </row>
-    <row r="275" spans="71:71">
-      <c r="BS275" t="s">
+    <row r="273" spans="72:72">
+      <c r="BT273" t="s">
         <v>754</v>
       </c>
     </row>
-    <row r="276" spans="71:71">
-      <c r="BS276" t="s">
+    <row r="274" spans="72:72">
+      <c r="BT274" t="s">
         <v>755</v>
       </c>
     </row>
-    <row r="277" spans="71:71">
-      <c r="BS277" t="s">
+    <row r="275" spans="72:72">
+      <c r="BT275" t="s">
         <v>756</v>
       </c>
     </row>
-    <row r="278" spans="71:71">
-      <c r="BS278" t="s">
+    <row r="276" spans="72:72">
+      <c r="BT276" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="279" spans="71:71">
-      <c r="BS279" t="s">
+    <row r="277" spans="72:72">
+      <c r="BT277" t="s">
         <v>758</v>
       </c>
     </row>
-    <row r="280" spans="71:71">
-      <c r="BS280" t="s">
+    <row r="278" spans="72:72">
+      <c r="BT278" t="s">
         <v>759</v>
       </c>
     </row>
-    <row r="281" spans="71:71">
-      <c r="BS281" t="s">
+    <row r="279" spans="72:72">
+      <c r="BT279" t="s">
         <v>760</v>
       </c>
     </row>
-    <row r="282" spans="71:71">
-      <c r="BS282" t="s">
+    <row r="280" spans="72:72">
+      <c r="BT280" t="s">
         <v>761</v>
       </c>
     </row>
-    <row r="283" spans="71:71">
-      <c r="BS283" t="s">
+    <row r="281" spans="72:72">
+      <c r="BT281" t="s">
         <v>762</v>
       </c>
     </row>
-    <row r="284" spans="71:71">
-      <c r="BS284" t="s">
+    <row r="282" spans="72:72">
+      <c r="BT282" t="s">
         <v>763</v>
       </c>
     </row>
-    <row r="285" spans="71:71">
-      <c r="BS285" t="s">
+    <row r="283" spans="72:72">
+      <c r="BT283" t="s">
         <v>764</v>
       </c>
     </row>
-    <row r="286" spans="71:71">
-      <c r="BS286" t="s">
+    <row r="284" spans="72:72">
+      <c r="BT284" t="s">
         <v>765</v>
       </c>
     </row>
-    <row r="287" spans="71:71">
-      <c r="BS287" t="s">
+    <row r="285" spans="72:72">
+      <c r="BT285" t="s">
         <v>766</v>
       </c>
     </row>
-    <row r="288" spans="71:71">
-      <c r="BS288" t="s">
+    <row r="286" spans="72:72">
+      <c r="BT286" t="s">
         <v>767</v>
       </c>
     </row>
-    <row r="289" spans="71:71">
-      <c r="BS289" t="s">
+    <row r="287" spans="72:72">
+      <c r="BT287" t="s">
         <v>768</v>
       </c>
     </row>
-    <row r="290" spans="71:71">
-      <c r="BS290" t="s">
+    <row r="288" spans="72:72">
+      <c r="BT288" t="s">
         <v>769</v>
       </c>
     </row>
-    <row r="291" spans="71:71">
-      <c r="BS291" t="s">
+    <row r="289" spans="72:72">
+      <c r="BT289" t="s">
         <v>770</v>
       </c>
     </row>
-    <row r="292" spans="71:71">
-      <c r="BS292" t="s">
+    <row r="290" spans="72:72">
+      <c r="BT290" t="s">
         <v>771</v>
       </c>
     </row>
-    <row r="293" spans="71:71">
-      <c r="BS293" t="s">
+    <row r="291" spans="72:72">
+      <c r="BT291" t="s">
         <v>772</v>
       </c>
     </row>
-    <row r="294" spans="71:71">
-      <c r="BS294" t="s">
+    <row r="292" spans="72:72">
+      <c r="BT292" t="s">
         <v>773</v>
+      </c>
+    </row>
+    <row r="293" spans="72:72">
+      <c r="BT293" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="294" spans="72:72">
+      <c r="BT294" t="s">
+        <v>775</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000055/metadata_template_ERC000055.xlsx
+++ b/templates/ERC000055/metadata_template_ERC000055.xlsx
@@ -19,14 +19,14 @@
   <definedNames>
     <definedName name="drainageclassification">'cv_sample'!$CQ$1:$CQ$6</definedName>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$BT$1:$BT$289</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$BT$1:$BT$294</definedName>
     <definedName name="historytillage">'cv_sample'!$DK$1:$DK$9</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$87</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
     <definedName name="oxygenationstatusofsample">'cv_sample'!$AB$1:$AB$2</definedName>
-    <definedName name="platform">'cv_experiment'!$M$1:$M$17</definedName>
+    <definedName name="platform">'cv_experiment'!$M$1:$M$18</definedName>
     <definedName name="profileposition">'cv_sample'!$CV$1:$CV$5</definedName>
     <definedName name="relationshiptooxygen">'cv_sample'!$J$1:$J$7</definedName>
     <definedName name="sequencequalitycheck">'cv_sample'!$AW$1:$AW$3</definedName>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1031" uniqueCount="1023">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1038" uniqueCount="1030">
   <si>
     <t>alias</t>
   </si>
@@ -457,6 +457,9 @@
     <t>ELEMENT</t>
   </si>
   <si>
+    <t>AVITI</t>
+  </si>
+  <si>
     <t>ULTIMA</t>
   </si>
   <si>
@@ -547,6 +550,9 @@
     <t>AB SOLiD System 3.0</t>
   </si>
   <si>
+    <t>AVITI 24</t>
+  </si>
+  <si>
     <t>BGISEQ-50</t>
   </si>
   <si>
@@ -1696,9 +1702,6 @@
     <t>Dominican Republic</t>
   </si>
   <si>
-    <t>East Timor</t>
-  </si>
-  <si>
     <t>Ecuador</t>
   </si>
   <si>
@@ -1717,6 +1720,9 @@
     <t>Estonia</t>
   </si>
   <si>
+    <t>Eswatini</t>
+  </si>
+  <si>
     <t>Ethiopia</t>
   </si>
   <si>
@@ -1918,6 +1924,9 @@
     <t>Liechtenstein</t>
   </si>
   <si>
+    <t>Line Islands</t>
+  </si>
+  <si>
     <t>Lithuania</t>
   </si>
   <si>
@@ -1927,9 +1936,6 @@
     <t>Macau</t>
   </si>
   <si>
-    <t>Macedonia</t>
-  </si>
-  <si>
     <t>Madagascar</t>
   </si>
   <si>
@@ -1969,7 +1975,7 @@
     <t>Mexico</t>
   </si>
   <si>
-    <t>Micronesia</t>
+    <t>Micronesia, Federated States of</t>
   </si>
   <si>
     <t>Midway Islands</t>
@@ -2038,6 +2044,9 @@
     <t>North Korea</t>
   </si>
   <si>
+    <t>North Macedonia</t>
+  </si>
+  <si>
     <t>North Sea</t>
   </si>
   <si>
@@ -2113,6 +2122,9 @@
     <t>Rwanda</t>
   </si>
   <si>
+    <t>Saint Barthelemy</t>
+  </si>
+  <si>
     <t>Saint Helena</t>
   </si>
   <si>
@@ -2134,6 +2146,9 @@
     <t>San Marino</t>
   </si>
   <si>
+    <t>Saint Martin</t>
+  </si>
+  <si>
     <t>Sao Tome and Principe</t>
   </si>
   <si>
@@ -2179,6 +2194,9 @@
     <t>South Korea</t>
   </si>
   <si>
+    <t>South Sudan</t>
+  </si>
+  <si>
     <t>Southern Ocean</t>
   </si>
   <si>
@@ -2191,6 +2209,9 @@
     <t>Sri Lanka</t>
   </si>
   <si>
+    <t>State of Palestine</t>
+  </si>
+  <si>
     <t>Sudan</t>
   </si>
   <si>
@@ -2200,9 +2221,6 @@
     <t>Svalbard</t>
   </si>
   <si>
-    <t>Swaziland</t>
-  </si>
-  <si>
     <t>Sweden</t>
   </si>
   <si>
@@ -2227,6 +2245,9 @@
     <t>Thailand</t>
   </si>
   <si>
+    <t>Timor-Leste</t>
+  </si>
+  <si>
     <t>Togo</t>
   </si>
   <si>
@@ -2287,10 +2308,10 @@
     <t>Viet Nam</t>
   </si>
   <si>
+    <t>Wake Island</t>
+  </si>
+  <si>
     <t>Virgin Islands</t>
-  </si>
-  <si>
-    <t>Wake Island</t>
   </si>
   <si>
     <t>Wallis and Futuna</t>
@@ -3636,10 +3657,10 @@
         <v>124</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -3680,10 +3701,10 @@
         <v>125</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -3710,7 +3731,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N87"/>
+  <dimension ref="G1:N88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -3727,7 +3748,7 @@
         <v>126</v>
       </c>
       <c r="N1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="7:14">
@@ -3744,7 +3765,7 @@
         <v>127</v>
       </c>
       <c r="N2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="7:14">
@@ -3761,7 +3782,7 @@
         <v>128</v>
       </c>
       <c r="N3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="7:14">
@@ -3778,7 +3799,7 @@
         <v>129</v>
       </c>
       <c r="N4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="7:14">
@@ -3795,7 +3816,7 @@
         <v>130</v>
       </c>
       <c r="N5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="7:14">
@@ -3812,7 +3833,7 @@
         <v>131</v>
       </c>
       <c r="N6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="7:14">
@@ -3829,7 +3850,7 @@
         <v>132</v>
       </c>
       <c r="N7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="7:14">
@@ -3846,7 +3867,7 @@
         <v>133</v>
       </c>
       <c r="N8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="7:14">
@@ -3863,7 +3884,7 @@
         <v>134</v>
       </c>
       <c r="N9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="7:14">
@@ -3877,7 +3898,7 @@
         <v>135</v>
       </c>
       <c r="N10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="7:14">
@@ -3891,7 +3912,7 @@
         <v>136</v>
       </c>
       <c r="N11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="7:14">
@@ -3905,7 +3926,7 @@
         <v>137</v>
       </c>
       <c r="N12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="7:14">
@@ -3919,7 +3940,7 @@
         <v>138</v>
       </c>
       <c r="N13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="7:14">
@@ -3933,7 +3954,7 @@
         <v>139</v>
       </c>
       <c r="N14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="7:14">
@@ -3947,7 +3968,7 @@
         <v>140</v>
       </c>
       <c r="N15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" spans="7:14">
@@ -3961,7 +3982,7 @@
         <v>141</v>
       </c>
       <c r="N16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" spans="7:14">
@@ -3975,7 +3996,7 @@
         <v>142</v>
       </c>
       <c r="N17" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" spans="7:14">
@@ -3985,8 +4006,11 @@
       <c r="I18" t="s">
         <v>54</v>
       </c>
+      <c r="M18" t="s">
+        <v>143</v>
+      </c>
       <c r="N18" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19" spans="7:14">
@@ -3997,7 +4021,7 @@
         <v>105</v>
       </c>
       <c r="N19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="7:14">
@@ -4008,7 +4032,7 @@
         <v>106</v>
       </c>
       <c r="N20" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21" spans="7:14">
@@ -4019,7 +4043,7 @@
         <v>107</v>
       </c>
       <c r="N21" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22" spans="7:14">
@@ -4030,7 +4054,7 @@
         <v>108</v>
       </c>
       <c r="N22" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="7:14">
@@ -4041,7 +4065,7 @@
         <v>109</v>
       </c>
       <c r="N23" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24" spans="7:14">
@@ -4052,7 +4076,7 @@
         <v>110</v>
       </c>
       <c r="N24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="7:14">
@@ -4063,7 +4087,7 @@
         <v>111</v>
       </c>
       <c r="N25" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26" spans="7:14">
@@ -4074,7 +4098,7 @@
         <v>112</v>
       </c>
       <c r="N26" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="7:14">
@@ -4085,7 +4109,7 @@
         <v>113</v>
       </c>
       <c r="N27" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="7:14">
@@ -4096,7 +4120,7 @@
         <v>114</v>
       </c>
       <c r="N28" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="7:14">
@@ -4107,7 +4131,7 @@
         <v>115</v>
       </c>
       <c r="N29" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="7:14">
@@ -4118,7 +4142,7 @@
         <v>116</v>
       </c>
       <c r="N30" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="7:14">
@@ -4129,7 +4153,7 @@
         <v>117</v>
       </c>
       <c r="N31" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="7:14">
@@ -4137,7 +4161,7 @@
         <v>66</v>
       </c>
       <c r="N32" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" spans="7:14">
@@ -4145,7 +4169,7 @@
         <v>67</v>
       </c>
       <c r="N33" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34" spans="7:14">
@@ -4153,7 +4177,7 @@
         <v>68</v>
       </c>
       <c r="N34" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35" spans="7:14">
@@ -4161,7 +4185,7 @@
         <v>69</v>
       </c>
       <c r="N35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="7:14">
@@ -4169,7 +4193,7 @@
         <v>70</v>
       </c>
       <c r="N36" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37" spans="7:14">
@@ -4177,7 +4201,7 @@
         <v>71</v>
       </c>
       <c r="N37" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="38" spans="7:14">
@@ -4185,7 +4209,7 @@
         <v>72</v>
       </c>
       <c r="N38" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="39" spans="7:14">
@@ -4193,7 +4217,7 @@
         <v>73</v>
       </c>
       <c r="N39" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="40" spans="7:14">
@@ -4201,7 +4225,7 @@
         <v>74</v>
       </c>
       <c r="N40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="41" spans="7:14">
@@ -4209,236 +4233,241 @@
         <v>75</v>
       </c>
       <c r="N41" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42" spans="7:14">
       <c r="N42" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="43" spans="7:14">
       <c r="N43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" spans="7:14">
       <c r="N44" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="45" spans="7:14">
       <c r="N45" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="46" spans="7:14">
       <c r="N46" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="47" spans="7:14">
       <c r="N47" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="48" spans="7:14">
       <c r="N48" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="49" spans="14:14">
       <c r="N49" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="50" spans="14:14">
       <c r="N50" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="51" spans="14:14">
       <c r="N51" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="52" spans="14:14">
       <c r="N52" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="53" spans="14:14">
       <c r="N53" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="54" spans="14:14">
       <c r="N54" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="55" spans="14:14">
       <c r="N55" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="56" spans="14:14">
       <c r="N56" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="57" spans="14:14">
       <c r="N57" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="58" spans="14:14">
       <c r="N58" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="59" spans="14:14">
       <c r="N59" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="60" spans="14:14">
       <c r="N60" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="61" spans="14:14">
       <c r="N61" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="62" spans="14:14">
       <c r="N62" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="63" spans="14:14">
       <c r="N63" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="64" spans="14:14">
       <c r="N64" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="65" spans="14:14">
       <c r="N65" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="66" spans="14:14">
       <c r="N66" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="67" spans="14:14">
       <c r="N67" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="68" spans="14:14">
       <c r="N68" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="69" spans="14:14">
       <c r="N69" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="70" spans="14:14">
       <c r="N70" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="71" spans="14:14">
       <c r="N71" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="72" spans="14:14">
       <c r="N72" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="73" spans="14:14">
       <c r="N73" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="74" spans="14:14">
       <c r="N74" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="75" spans="14:14">
       <c r="N75" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="76" spans="14:14">
       <c r="N76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="77" spans="14:14">
       <c r="N77" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="78" spans="14:14">
       <c r="N78" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="79" spans="14:14">
       <c r="N79" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="80" spans="14:14">
       <c r="N80" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="81" spans="14:14">
       <c r="N81" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="82" spans="14:14">
       <c r="N82" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="83" spans="14:14">
       <c r="N83" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="84" spans="14:14">
       <c r="N84" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="85" spans="14:14">
       <c r="N85" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="86" spans="14:14">
       <c r="N86" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="87" spans="14:14">
       <c r="N87" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="88" spans="14:14">
+      <c r="N88" t="s">
         <v>117</v>
       </c>
     </row>
@@ -4460,27 +4489,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -4500,122 +4529,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -4639,1098 +4668,1098 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="BK1" s="1" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="BM1" s="1" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="BN1" s="1" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="BO1" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="BP1" s="1" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="BQ1" s="1" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="BS1" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="BT1" s="1" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="BU1" s="1" t="s">
-        <v>771</v>
+        <v>778</v>
       </c>
       <c r="BV1" s="1" t="s">
-        <v>773</v>
+        <v>780</v>
       </c>
       <c r="BW1" s="1" t="s">
-        <v>775</v>
+        <v>782</v>
       </c>
       <c r="BX1" s="1" t="s">
-        <v>777</v>
+        <v>784</v>
       </c>
       <c r="BY1" s="1" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="BZ1" s="1" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
       <c r="CA1" s="1" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="CB1" s="1" t="s">
-        <v>785</v>
+        <v>792</v>
       </c>
       <c r="CC1" s="1" t="s">
-        <v>787</v>
+        <v>794</v>
       </c>
       <c r="CD1" s="1" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
       <c r="CE1" s="1" t="s">
-        <v>791</v>
+        <v>798</v>
       </c>
       <c r="CF1" s="1" t="s">
-        <v>793</v>
+        <v>800</v>
       </c>
       <c r="CG1" s="1" t="s">
-        <v>795</v>
+        <v>802</v>
       </c>
       <c r="CH1" s="1" t="s">
-        <v>797</v>
+        <v>804</v>
       </c>
       <c r="CI1" s="1" t="s">
-        <v>799</v>
+        <v>806</v>
       </c>
       <c r="CJ1" s="1" t="s">
-        <v>801</v>
+        <v>808</v>
       </c>
       <c r="CK1" s="1" t="s">
-        <v>803</v>
+        <v>810</v>
       </c>
       <c r="CL1" s="1" t="s">
-        <v>805</v>
+        <v>812</v>
       </c>
       <c r="CM1" s="1" t="s">
-        <v>807</v>
+        <v>814</v>
       </c>
       <c r="CN1" s="1" t="s">
-        <v>809</v>
+        <v>816</v>
       </c>
       <c r="CO1" s="1" t="s">
-        <v>817</v>
+        <v>824</v>
       </c>
       <c r="CP1" s="1" t="s">
-        <v>819</v>
+        <v>826</v>
       </c>
       <c r="CQ1" s="1" t="s">
-        <v>827</v>
+        <v>834</v>
       </c>
       <c r="CR1" s="1" t="s">
-        <v>829</v>
+        <v>836</v>
       </c>
       <c r="CS1" s="1" t="s">
-        <v>831</v>
+        <v>838</v>
       </c>
       <c r="CT1" s="1" t="s">
-        <v>833</v>
+        <v>840</v>
       </c>
       <c r="CU1" s="1" t="s">
-        <v>835</v>
+        <v>842</v>
       </c>
       <c r="CV1" s="1" t="s">
-        <v>842</v>
+        <v>849</v>
       </c>
       <c r="CW1" s="1" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
       <c r="CX1" s="1" t="s">
-        <v>846</v>
+        <v>853</v>
       </c>
       <c r="CY1" s="1" t="s">
-        <v>848</v>
+        <v>855</v>
       </c>
       <c r="CZ1" s="1" t="s">
-        <v>850</v>
+        <v>857</v>
       </c>
       <c r="DA1" s="1" t="s">
-        <v>852</v>
+        <v>859</v>
       </c>
       <c r="DB1" s="1" t="s">
-        <v>854</v>
+        <v>861</v>
       </c>
       <c r="DC1" s="1" t="s">
-        <v>856</v>
+        <v>863</v>
       </c>
       <c r="DD1" s="1" t="s">
-        <v>858</v>
+        <v>865</v>
       </c>
       <c r="DE1" s="1" t="s">
-        <v>860</v>
+        <v>867</v>
       </c>
       <c r="DF1" s="1" t="s">
-        <v>862</v>
+        <v>869</v>
       </c>
       <c r="DG1" s="1" t="s">
-        <v>864</v>
+        <v>871</v>
       </c>
       <c r="DH1" s="1" t="s">
-        <v>866</v>
+        <v>873</v>
       </c>
       <c r="DI1" s="1" t="s">
-        <v>868</v>
+        <v>875</v>
       </c>
       <c r="DJ1" s="1" t="s">
-        <v>870</v>
+        <v>877</v>
       </c>
       <c r="DK1" s="1" t="s">
-        <v>881</v>
+        <v>888</v>
       </c>
       <c r="DL1" s="1" t="s">
-        <v>883</v>
+        <v>890</v>
       </c>
       <c r="DM1" s="1" t="s">
-        <v>885</v>
+        <v>892</v>
       </c>
       <c r="DN1" s="1" t="s">
-        <v>887</v>
+        <v>894</v>
       </c>
       <c r="DO1" s="1" t="s">
-        <v>889</v>
+        <v>896</v>
       </c>
       <c r="DP1" s="1" t="s">
-        <v>891</v>
+        <v>898</v>
       </c>
       <c r="DQ1" s="1" t="s">
-        <v>893</v>
+        <v>900</v>
       </c>
       <c r="DR1" s="1" t="s">
-        <v>895</v>
+        <v>902</v>
       </c>
       <c r="DS1" s="1" t="s">
-        <v>897</v>
+        <v>904</v>
       </c>
       <c r="DT1" s="1" t="s">
-        <v>899</v>
+        <v>906</v>
       </c>
       <c r="DU1" s="1" t="s">
-        <v>901</v>
+        <v>908</v>
       </c>
       <c r="DV1" s="1" t="s">
-        <v>903</v>
+        <v>910</v>
       </c>
       <c r="DW1" s="1" t="s">
-        <v>905</v>
+        <v>912</v>
       </c>
       <c r="DX1" s="1" t="s">
-        <v>907</v>
+        <v>914</v>
       </c>
       <c r="DY1" s="1" t="s">
-        <v>909</v>
+        <v>916</v>
       </c>
       <c r="DZ1" s="1" t="s">
-        <v>911</v>
+        <v>918</v>
       </c>
       <c r="EA1" s="1" t="s">
-        <v>913</v>
+        <v>920</v>
       </c>
       <c r="EB1" s="1" t="s">
-        <v>915</v>
+        <v>922</v>
       </c>
       <c r="EC1" s="1" t="s">
-        <v>917</v>
+        <v>924</v>
       </c>
       <c r="ED1" s="1" t="s">
-        <v>919</v>
+        <v>926</v>
       </c>
       <c r="EE1" s="1" t="s">
-        <v>921</v>
+        <v>928</v>
       </c>
       <c r="EF1" s="1" t="s">
-        <v>923</v>
+        <v>930</v>
       </c>
       <c r="EG1" s="1" t="s">
-        <v>925</v>
+        <v>932</v>
       </c>
       <c r="EH1" s="1" t="s">
-        <v>927</v>
+        <v>934</v>
       </c>
       <c r="EI1" s="1" t="s">
-        <v>929</v>
+        <v>936</v>
       </c>
       <c r="EJ1" s="1" t="s">
-        <v>931</v>
+        <v>938</v>
       </c>
       <c r="EK1" s="1" t="s">
-        <v>933</v>
+        <v>940</v>
       </c>
       <c r="EL1" s="1" t="s">
-        <v>935</v>
+        <v>942</v>
       </c>
       <c r="EM1" s="1" t="s">
-        <v>937</v>
+        <v>944</v>
       </c>
       <c r="EN1" s="1" t="s">
-        <v>939</v>
+        <v>946</v>
       </c>
       <c r="EO1" s="1" t="s">
-        <v>941</v>
+        <v>948</v>
       </c>
       <c r="EP1" s="1" t="s">
-        <v>943</v>
+        <v>950</v>
       </c>
       <c r="EQ1" s="1" t="s">
-        <v>945</v>
+        <v>952</v>
       </c>
       <c r="ER1" s="1" t="s">
-        <v>947</v>
+        <v>954</v>
       </c>
       <c r="ES1" s="1" t="s">
-        <v>953</v>
+        <v>960</v>
       </c>
       <c r="ET1" s="1" t="s">
-        <v>955</v>
+        <v>962</v>
       </c>
       <c r="EU1" s="1" t="s">
-        <v>957</v>
+        <v>964</v>
       </c>
       <c r="EV1" s="1" t="s">
-        <v>959</v>
+        <v>966</v>
       </c>
       <c r="EW1" s="1" t="s">
-        <v>961</v>
+        <v>968</v>
       </c>
       <c r="EX1" s="1" t="s">
-        <v>963</v>
+        <v>970</v>
       </c>
       <c r="EY1" s="1" t="s">
-        <v>965</v>
+        <v>972</v>
       </c>
       <c r="EZ1" s="1" t="s">
-        <v>967</v>
+        <v>974</v>
       </c>
       <c r="FA1" s="1" t="s">
-        <v>969</v>
+        <v>976</v>
       </c>
       <c r="FB1" s="1" t="s">
-        <v>971</v>
+        <v>978</v>
       </c>
       <c r="FC1" s="1" t="s">
-        <v>973</v>
+        <v>980</v>
       </c>
       <c r="FD1" s="1" t="s">
-        <v>975</v>
+        <v>982</v>
       </c>
       <c r="FE1" s="1" t="s">
-        <v>977</v>
+        <v>984</v>
       </c>
       <c r="FF1" s="1" t="s">
-        <v>979</v>
+        <v>986</v>
       </c>
       <c r="FG1" s="1" t="s">
-        <v>981</v>
+        <v>988</v>
       </c>
       <c r="FH1" s="1" t="s">
-        <v>983</v>
+        <v>990</v>
       </c>
       <c r="FI1" s="1" t="s">
-        <v>985</v>
+        <v>992</v>
       </c>
       <c r="FJ1" s="1" t="s">
-        <v>987</v>
+        <v>994</v>
       </c>
       <c r="FK1" s="1" t="s">
-        <v>989</v>
+        <v>996</v>
       </c>
       <c r="FL1" s="1" t="s">
-        <v>991</v>
+        <v>998</v>
       </c>
       <c r="FM1" s="1" t="s">
-        <v>993</v>
+        <v>1000</v>
       </c>
       <c r="FN1" s="1" t="s">
-        <v>995</v>
+        <v>1002</v>
       </c>
       <c r="FO1" s="1" t="s">
-        <v>997</v>
+        <v>1004</v>
       </c>
       <c r="FP1" s="1" t="s">
-        <v>999</v>
+        <v>1006</v>
       </c>
       <c r="FQ1" s="1" t="s">
-        <v>1001</v>
+        <v>1008</v>
       </c>
       <c r="FR1" s="1" t="s">
-        <v>1003</v>
+        <v>1010</v>
       </c>
       <c r="FS1" s="1" t="s">
-        <v>1005</v>
+        <v>1012</v>
       </c>
       <c r="FT1" s="1" t="s">
-        <v>1007</v>
+        <v>1014</v>
       </c>
       <c r="FU1" s="1" t="s">
-        <v>1009</v>
+        <v>1016</v>
       </c>
       <c r="FV1" s="1" t="s">
-        <v>1011</v>
+        <v>1018</v>
       </c>
       <c r="FW1" s="1" t="s">
-        <v>1013</v>
+        <v>1020</v>
       </c>
       <c r="FX1" s="1" t="s">
-        <v>1015</v>
+        <v>1022</v>
       </c>
       <c r="FY1" s="1" t="s">
-        <v>1017</v>
+        <v>1024</v>
       </c>
       <c r="FZ1" s="1" t="s">
-        <v>1019</v>
+        <v>1026</v>
       </c>
       <c r="GA1" s="1" t="s">
-        <v>1021</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="2" spans="1:183" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AP2" s="2" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AQ2" s="2" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AR2" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AS2" s="2" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AU2" s="2" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AV2" s="2" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AW2" s="2" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AX2" s="2" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AY2" s="2" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AZ2" s="2" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="BA2" s="2" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="BB2" s="2" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="BC2" s="2" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="BD2" s="2" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="BE2" s="2" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="BF2" s="2" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="BG2" s="2" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="BH2" s="2" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="BI2" s="2" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="BJ2" s="2" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="BK2" s="2" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="BL2" s="2" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="BM2" s="2" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="BN2" s="2" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="BO2" s="2" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="BP2" s="2" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="BQ2" s="2" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="BR2" s="2" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="BS2" s="2" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="BT2" s="2" t="s">
-        <v>770</v>
+        <v>777</v>
       </c>
       <c r="BU2" s="2" t="s">
-        <v>772</v>
+        <v>779</v>
       </c>
       <c r="BV2" s="2" t="s">
-        <v>774</v>
+        <v>781</v>
       </c>
       <c r="BW2" s="2" t="s">
-        <v>776</v>
+        <v>783</v>
       </c>
       <c r="BX2" s="2" t="s">
-        <v>778</v>
+        <v>785</v>
       </c>
       <c r="BY2" s="2" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="BZ2" s="2" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="CA2" s="2" t="s">
-        <v>784</v>
+        <v>791</v>
       </c>
       <c r="CB2" s="2" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="CC2" s="2" t="s">
-        <v>788</v>
+        <v>795</v>
       </c>
       <c r="CD2" s="2" t="s">
-        <v>790</v>
+        <v>797</v>
       </c>
       <c r="CE2" s="2" t="s">
-        <v>792</v>
+        <v>799</v>
       </c>
       <c r="CF2" s="2" t="s">
-        <v>794</v>
+        <v>801</v>
       </c>
       <c r="CG2" s="2" t="s">
-        <v>796</v>
+        <v>803</v>
       </c>
       <c r="CH2" s="2" t="s">
-        <v>798</v>
+        <v>805</v>
       </c>
       <c r="CI2" s="2" t="s">
-        <v>800</v>
+        <v>807</v>
       </c>
       <c r="CJ2" s="2" t="s">
-        <v>802</v>
+        <v>809</v>
       </c>
       <c r="CK2" s="2" t="s">
-        <v>804</v>
+        <v>811</v>
       </c>
       <c r="CL2" s="2" t="s">
-        <v>806</v>
+        <v>813</v>
       </c>
       <c r="CM2" s="2" t="s">
-        <v>808</v>
+        <v>815</v>
       </c>
       <c r="CN2" s="2" t="s">
-        <v>810</v>
+        <v>817</v>
       </c>
       <c r="CO2" s="2" t="s">
-        <v>818</v>
+        <v>825</v>
       </c>
       <c r="CP2" s="2" t="s">
-        <v>820</v>
+        <v>827</v>
       </c>
       <c r="CQ2" s="2" t="s">
-        <v>828</v>
+        <v>835</v>
       </c>
       <c r="CR2" s="2" t="s">
-        <v>830</v>
+        <v>837</v>
       </c>
       <c r="CS2" s="2" t="s">
-        <v>832</v>
+        <v>839</v>
       </c>
       <c r="CT2" s="2" t="s">
-        <v>834</v>
+        <v>841</v>
       </c>
       <c r="CU2" s="2" t="s">
-        <v>836</v>
+        <v>843</v>
       </c>
       <c r="CV2" s="2" t="s">
-        <v>843</v>
+        <v>850</v>
       </c>
       <c r="CW2" s="2" t="s">
-        <v>845</v>
+        <v>852</v>
       </c>
       <c r="CX2" s="2" t="s">
-        <v>847</v>
+        <v>854</v>
       </c>
       <c r="CY2" s="2" t="s">
-        <v>849</v>
+        <v>856</v>
       </c>
       <c r="CZ2" s="2" t="s">
-        <v>851</v>
+        <v>858</v>
       </c>
       <c r="DA2" s="2" t="s">
-        <v>853</v>
+        <v>860</v>
       </c>
       <c r="DB2" s="2" t="s">
-        <v>855</v>
+        <v>862</v>
       </c>
       <c r="DC2" s="2" t="s">
-        <v>857</v>
+        <v>864</v>
       </c>
       <c r="DD2" s="2" t="s">
-        <v>859</v>
+        <v>866</v>
       </c>
       <c r="DE2" s="2" t="s">
-        <v>861</v>
+        <v>868</v>
       </c>
       <c r="DF2" s="2" t="s">
-        <v>863</v>
+        <v>870</v>
       </c>
       <c r="DG2" s="2" t="s">
-        <v>865</v>
+        <v>872</v>
       </c>
       <c r="DH2" s="2" t="s">
-        <v>867</v>
+        <v>874</v>
       </c>
       <c r="DI2" s="2" t="s">
-        <v>869</v>
+        <v>876</v>
       </c>
       <c r="DJ2" s="2" t="s">
-        <v>871</v>
+        <v>878</v>
       </c>
       <c r="DK2" s="2" t="s">
-        <v>882</v>
+        <v>889</v>
       </c>
       <c r="DL2" s="2" t="s">
-        <v>884</v>
+        <v>891</v>
       </c>
       <c r="DM2" s="2" t="s">
-        <v>886</v>
+        <v>893</v>
       </c>
       <c r="DN2" s="2" t="s">
-        <v>888</v>
+        <v>895</v>
       </c>
       <c r="DO2" s="2" t="s">
-        <v>890</v>
+        <v>897</v>
       </c>
       <c r="DP2" s="2" t="s">
-        <v>892</v>
+        <v>899</v>
       </c>
       <c r="DQ2" s="2" t="s">
-        <v>894</v>
+        <v>901</v>
       </c>
       <c r="DR2" s="2" t="s">
-        <v>896</v>
+        <v>903</v>
       </c>
       <c r="DS2" s="2" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="DT2" s="2" t="s">
-        <v>900</v>
+        <v>907</v>
       </c>
       <c r="DU2" s="2" t="s">
-        <v>902</v>
+        <v>909</v>
       </c>
       <c r="DV2" s="2" t="s">
-        <v>904</v>
+        <v>911</v>
       </c>
       <c r="DW2" s="2" t="s">
-        <v>906</v>
+        <v>913</v>
       </c>
       <c r="DX2" s="2" t="s">
-        <v>908</v>
+        <v>915</v>
       </c>
       <c r="DY2" s="2" t="s">
-        <v>910</v>
+        <v>917</v>
       </c>
       <c r="DZ2" s="2" t="s">
-        <v>912</v>
+        <v>919</v>
       </c>
       <c r="EA2" s="2" t="s">
-        <v>914</v>
+        <v>921</v>
       </c>
       <c r="EB2" s="2" t="s">
-        <v>916</v>
+        <v>923</v>
       </c>
       <c r="EC2" s="2" t="s">
-        <v>918</v>
+        <v>925</v>
       </c>
       <c r="ED2" s="2" t="s">
-        <v>920</v>
+        <v>927</v>
       </c>
       <c r="EE2" s="2" t="s">
-        <v>922</v>
+        <v>929</v>
       </c>
       <c r="EF2" s="2" t="s">
-        <v>924</v>
+        <v>931</v>
       </c>
       <c r="EG2" s="2" t="s">
-        <v>926</v>
+        <v>933</v>
       </c>
       <c r="EH2" s="2" t="s">
-        <v>928</v>
+        <v>935</v>
       </c>
       <c r="EI2" s="2" t="s">
-        <v>930</v>
+        <v>937</v>
       </c>
       <c r="EJ2" s="2" t="s">
-        <v>932</v>
+        <v>939</v>
       </c>
       <c r="EK2" s="2" t="s">
-        <v>934</v>
+        <v>941</v>
       </c>
       <c r="EL2" s="2" t="s">
-        <v>936</v>
+        <v>943</v>
       </c>
       <c r="EM2" s="2" t="s">
-        <v>938</v>
+        <v>945</v>
       </c>
       <c r="EN2" s="2" t="s">
-        <v>940</v>
+        <v>947</v>
       </c>
       <c r="EO2" s="2" t="s">
-        <v>942</v>
+        <v>949</v>
       </c>
       <c r="EP2" s="2" t="s">
-        <v>944</v>
+        <v>951</v>
       </c>
       <c r="EQ2" s="2" t="s">
-        <v>946</v>
+        <v>953</v>
       </c>
       <c r="ER2" s="2" t="s">
-        <v>948</v>
+        <v>955</v>
       </c>
       <c r="ES2" s="2" t="s">
-        <v>954</v>
+        <v>961</v>
       </c>
       <c r="ET2" s="2" t="s">
-        <v>956</v>
+        <v>963</v>
       </c>
       <c r="EU2" s="2" t="s">
-        <v>958</v>
+        <v>965</v>
       </c>
       <c r="EV2" s="2" t="s">
-        <v>960</v>
+        <v>967</v>
       </c>
       <c r="EW2" s="2" t="s">
-        <v>962</v>
+        <v>969</v>
       </c>
       <c r="EX2" s="2" t="s">
-        <v>964</v>
+        <v>971</v>
       </c>
       <c r="EY2" s="2" t="s">
-        <v>966</v>
+        <v>973</v>
       </c>
       <c r="EZ2" s="2" t="s">
-        <v>968</v>
+        <v>975</v>
       </c>
       <c r="FA2" s="2" t="s">
-        <v>970</v>
+        <v>977</v>
       </c>
       <c r="FB2" s="2" t="s">
-        <v>972</v>
+        <v>979</v>
       </c>
       <c r="FC2" s="2" t="s">
-        <v>974</v>
+        <v>981</v>
       </c>
       <c r="FD2" s="2" t="s">
-        <v>976</v>
+        <v>983</v>
       </c>
       <c r="FE2" s="2" t="s">
-        <v>978</v>
+        <v>985</v>
       </c>
       <c r="FF2" s="2" t="s">
-        <v>980</v>
+        <v>987</v>
       </c>
       <c r="FG2" s="2" t="s">
-        <v>982</v>
+        <v>989</v>
       </c>
       <c r="FH2" s="2" t="s">
-        <v>984</v>
+        <v>991</v>
       </c>
       <c r="FI2" s="2" t="s">
-        <v>986</v>
+        <v>993</v>
       </c>
       <c r="FJ2" s="2" t="s">
-        <v>988</v>
+        <v>995</v>
       </c>
       <c r="FK2" s="2" t="s">
-        <v>990</v>
+        <v>997</v>
       </c>
       <c r="FL2" s="2" t="s">
-        <v>992</v>
+        <v>999</v>
       </c>
       <c r="FM2" s="2" t="s">
-        <v>994</v>
+        <v>1001</v>
       </c>
       <c r="FN2" s="2" t="s">
-        <v>996</v>
+        <v>1003</v>
       </c>
       <c r="FO2" s="2" t="s">
-        <v>998</v>
+        <v>1005</v>
       </c>
       <c r="FP2" s="2" t="s">
-        <v>1000</v>
+        <v>1007</v>
       </c>
       <c r="FQ2" s="2" t="s">
-        <v>1002</v>
+        <v>1009</v>
       </c>
       <c r="FR2" s="2" t="s">
-        <v>1004</v>
+        <v>1011</v>
       </c>
       <c r="FS2" s="2" t="s">
-        <v>1006</v>
+        <v>1013</v>
       </c>
       <c r="FT2" s="2" t="s">
-        <v>1008</v>
+        <v>1015</v>
       </c>
       <c r="FU2" s="2" t="s">
-        <v>1010</v>
+        <v>1017</v>
       </c>
       <c r="FV2" s="2" t="s">
-        <v>1012</v>
+        <v>1019</v>
       </c>
       <c r="FW2" s="2" t="s">
-        <v>1014</v>
+        <v>1021</v>
       </c>
       <c r="FX2" s="2" t="s">
-        <v>1016</v>
+        <v>1023</v>
       </c>
       <c r="FY2" s="2" t="s">
-        <v>1018</v>
+        <v>1025</v>
       </c>
       <c r="FZ2" s="2" t="s">
-        <v>1020</v>
+        <v>1027</v>
       </c>
       <c r="GA2" s="2" t="s">
-        <v>1022</v>
+        <v>1029</v>
       </c>
     </row>
   </sheetData>
@@ -5778,1770 +5807,1795 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="H1:ES289"/>
+  <dimension ref="H1:ES294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="8:149">
       <c r="H1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="J1" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="V1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AB1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AW1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="BA1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="BT1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="CO1" t="s">
-        <v>811</v>
+        <v>818</v>
       </c>
       <c r="CQ1" t="s">
-        <v>821</v>
+        <v>828</v>
       </c>
       <c r="CV1" t="s">
-        <v>837</v>
+        <v>844</v>
       </c>
       <c r="DK1" t="s">
-        <v>872</v>
+        <v>879</v>
       </c>
       <c r="ES1" t="s">
-        <v>949</v>
+        <v>956</v>
       </c>
     </row>
     <row r="2" spans="8:149">
       <c r="H2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="J2" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="V2" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AB2" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AW2" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="BA2" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="BT2" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="CO2" t="s">
-        <v>812</v>
+        <v>819</v>
       </c>
       <c r="CQ2" t="s">
-        <v>822</v>
+        <v>829</v>
       </c>
       <c r="CV2" t="s">
-        <v>838</v>
+        <v>845</v>
       </c>
       <c r="DK2" t="s">
-        <v>873</v>
+        <v>880</v>
       </c>
       <c r="ES2" t="s">
-        <v>950</v>
+        <v>957</v>
       </c>
     </row>
     <row r="3" spans="8:149">
       <c r="H3" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J3" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="V3" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AW3" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="BT3" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="CO3" t="s">
-        <v>813</v>
+        <v>820</v>
       </c>
       <c r="CQ3" t="s">
-        <v>823</v>
+        <v>830</v>
       </c>
       <c r="CV3" t="s">
-        <v>839</v>
+        <v>846</v>
       </c>
       <c r="DK3" t="s">
-        <v>874</v>
+        <v>881</v>
       </c>
       <c r="ES3" t="s">
-        <v>951</v>
+        <v>958</v>
       </c>
     </row>
     <row r="4" spans="8:149">
       <c r="H4" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="J4" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="V4" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="BT4" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="CO4" t="s">
-        <v>814</v>
+        <v>821</v>
       </c>
       <c r="CQ4" t="s">
-        <v>824</v>
+        <v>831</v>
       </c>
       <c r="CV4" t="s">
-        <v>840</v>
+        <v>847</v>
       </c>
       <c r="DK4" t="s">
-        <v>875</v>
+        <v>882</v>
       </c>
       <c r="ES4" t="s">
-        <v>952</v>
+        <v>959</v>
       </c>
     </row>
     <row r="5" spans="8:149">
       <c r="H5" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J5" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="V5" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="BT5" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="CO5" t="s">
-        <v>815</v>
+        <v>822</v>
       </c>
       <c r="CQ5" t="s">
-        <v>825</v>
+        <v>832</v>
       </c>
       <c r="CV5" t="s">
-        <v>841</v>
+        <v>848</v>
       </c>
       <c r="DK5" t="s">
-        <v>876</v>
+        <v>883</v>
       </c>
     </row>
     <row r="6" spans="8:149">
       <c r="H6" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="J6" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="V6" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="BT6" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="CO6" t="s">
-        <v>816</v>
+        <v>823</v>
       </c>
       <c r="CQ6" t="s">
-        <v>826</v>
+        <v>833</v>
       </c>
       <c r="DK6" t="s">
-        <v>877</v>
+        <v>884</v>
       </c>
     </row>
     <row r="7" spans="8:149">
       <c r="H7" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J7" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="V7" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="BT7" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="DK7" t="s">
-        <v>878</v>
+        <v>885</v>
       </c>
     </row>
     <row r="8" spans="8:149">
       <c r="H8" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="V8" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="BT8" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="DK8" t="s">
-        <v>879</v>
+        <v>886</v>
       </c>
     </row>
     <row r="9" spans="8:149">
       <c r="H9" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="V9" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="BT9" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="DK9" t="s">
-        <v>880</v>
+        <v>887</v>
       </c>
     </row>
     <row r="10" spans="8:149">
       <c r="H10" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="V10" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="BT10" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="11" spans="8:149">
       <c r="H11" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="V11" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="BT11" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="12" spans="8:149">
       <c r="H12" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="V12" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="BT12" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="13" spans="8:149">
       <c r="H13" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="V13" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="BT13" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="14" spans="8:149">
       <c r="H14" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="V14" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="BT14" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="15" spans="8:149">
       <c r="H15" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="V15" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="BT15" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="16" spans="8:149">
       <c r="H16" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="V16" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="BT16" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="17" spans="8:72">
       <c r="H17" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="V17" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="BT17" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="18" spans="8:72">
       <c r="H18" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="V18" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="BT18" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="19" spans="8:72">
       <c r="H19" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="V19" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="BT19" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="20" spans="8:72">
       <c r="H20" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="V20" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="BT20" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="21" spans="8:72">
       <c r="H21" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="V21" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="BT21" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="22" spans="8:72">
       <c r="H22" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="V22" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="BT22" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="23" spans="8:72">
       <c r="H23" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="V23" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="BT23" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="24" spans="8:72">
       <c r="H24" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="V24" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="BT24" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="25" spans="8:72">
       <c r="H25" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="V25" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="BT25" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="26" spans="8:72">
       <c r="H26" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="V26" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="BT26" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="27" spans="8:72">
       <c r="H27" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="V27" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="BT27" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="28" spans="8:72">
       <c r="H28" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="V28" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="BT28" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="29" spans="8:72">
       <c r="H29" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="V29" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="BT29" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="30" spans="8:72">
       <c r="H30" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="V30" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="BT30" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="31" spans="8:72">
       <c r="V31" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="BT31" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="32" spans="8:72">
       <c r="V32" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="BT32" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="33" spans="72:72">
       <c r="BT33" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="34" spans="72:72">
       <c r="BT34" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="35" spans="72:72">
       <c r="BT35" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="36" spans="72:72">
       <c r="BT36" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="37" spans="72:72">
       <c r="BT37" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="38" spans="72:72">
       <c r="BT38" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="39" spans="72:72">
       <c r="BT39" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="40" spans="72:72">
       <c r="BT40" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="41" spans="72:72">
       <c r="BT41" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="42" spans="72:72">
       <c r="BT42" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="43" spans="72:72">
       <c r="BT43" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="44" spans="72:72">
       <c r="BT44" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="45" spans="72:72">
       <c r="BT45" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="46" spans="72:72">
       <c r="BT46" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="47" spans="72:72">
       <c r="BT47" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="48" spans="72:72">
       <c r="BT48" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="49" spans="72:72">
       <c r="BT49" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="50" spans="72:72">
       <c r="BT50" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="51" spans="72:72">
       <c r="BT51" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="52" spans="72:72">
       <c r="BT52" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="53" spans="72:72">
       <c r="BT53" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="54" spans="72:72">
       <c r="BT54" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="55" spans="72:72">
       <c r="BT55" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="56" spans="72:72">
       <c r="BT56" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="57" spans="72:72">
       <c r="BT57" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="58" spans="72:72">
       <c r="BT58" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="59" spans="72:72">
       <c r="BT59" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="60" spans="72:72">
       <c r="BT60" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="61" spans="72:72">
       <c r="BT61" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="62" spans="72:72">
       <c r="BT62" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="63" spans="72:72">
       <c r="BT63" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="64" spans="72:72">
       <c r="BT64" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="65" spans="72:72">
       <c r="BT65" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="66" spans="72:72">
       <c r="BT66" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="67" spans="72:72">
       <c r="BT67" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="68" spans="72:72">
       <c r="BT68" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="69" spans="72:72">
       <c r="BT69" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="70" spans="72:72">
       <c r="BT70" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="71" spans="72:72">
       <c r="BT71" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="72" spans="72:72">
       <c r="BT72" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="73" spans="72:72">
       <c r="BT73" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="74" spans="72:72">
       <c r="BT74" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="75" spans="72:72">
       <c r="BT75" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="76" spans="72:72">
       <c r="BT76" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="77" spans="72:72">
       <c r="BT77" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="78" spans="72:72">
       <c r="BT78" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="79" spans="72:72">
       <c r="BT79" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="80" spans="72:72">
       <c r="BT80" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="81" spans="72:72">
       <c r="BT81" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="82" spans="72:72">
       <c r="BT82" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="83" spans="72:72">
       <c r="BT83" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="84" spans="72:72">
       <c r="BT84" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="85" spans="72:72">
       <c r="BT85" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="86" spans="72:72">
       <c r="BT86" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="87" spans="72:72">
       <c r="BT87" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="88" spans="72:72">
       <c r="BT88" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="89" spans="72:72">
       <c r="BT89" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="90" spans="72:72">
       <c r="BT90" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="91" spans="72:72">
       <c r="BT91" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="92" spans="72:72">
       <c r="BT92" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="93" spans="72:72">
       <c r="BT93" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="94" spans="72:72">
       <c r="BT94" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="95" spans="72:72">
       <c r="BT95" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="96" spans="72:72">
       <c r="BT96" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="97" spans="72:72">
       <c r="BT97" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="98" spans="72:72">
       <c r="BT98" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="99" spans="72:72">
       <c r="BT99" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="100" spans="72:72">
       <c r="BT100" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="101" spans="72:72">
       <c r="BT101" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="102" spans="72:72">
       <c r="BT102" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="103" spans="72:72">
       <c r="BT103" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="104" spans="72:72">
       <c r="BT104" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="105" spans="72:72">
       <c r="BT105" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="106" spans="72:72">
       <c r="BT106" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="107" spans="72:72">
       <c r="BT107" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="108" spans="72:72">
       <c r="BT108" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="109" spans="72:72">
       <c r="BT109" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="110" spans="72:72">
       <c r="BT110" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="111" spans="72:72">
       <c r="BT111" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="112" spans="72:72">
       <c r="BT112" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="113" spans="72:72">
       <c r="BT113" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="114" spans="72:72">
       <c r="BT114" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="115" spans="72:72">
       <c r="BT115" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="116" spans="72:72">
       <c r="BT116" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="117" spans="72:72">
       <c r="BT117" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="118" spans="72:72">
       <c r="BT118" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="119" spans="72:72">
       <c r="BT119" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="120" spans="72:72">
       <c r="BT120" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="121" spans="72:72">
       <c r="BT121" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="122" spans="72:72">
       <c r="BT122" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="123" spans="72:72">
       <c r="BT123" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="124" spans="72:72">
       <c r="BT124" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="125" spans="72:72">
       <c r="BT125" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="126" spans="72:72">
       <c r="BT126" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="127" spans="72:72">
       <c r="BT127" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="128" spans="72:72">
       <c r="BT128" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="129" spans="72:72">
       <c r="BT129" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="130" spans="72:72">
       <c r="BT130" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="131" spans="72:72">
       <c r="BT131" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="132" spans="72:72">
       <c r="BT132" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="133" spans="72:72">
       <c r="BT133" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="134" spans="72:72">
       <c r="BT134" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="135" spans="72:72">
       <c r="BT135" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="136" spans="72:72">
       <c r="BT136" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="137" spans="72:72">
       <c r="BT137" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="138" spans="72:72">
       <c r="BT138" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="139" spans="72:72">
       <c r="BT139" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="140" spans="72:72">
       <c r="BT140" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
     </row>
     <row r="141" spans="72:72">
       <c r="BT141" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="142" spans="72:72">
       <c r="BT142" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
     </row>
     <row r="143" spans="72:72">
       <c r="BT143" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
     </row>
     <row r="144" spans="72:72">
       <c r="BT144" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
     </row>
     <row r="145" spans="72:72">
       <c r="BT145" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="146" spans="72:72">
       <c r="BT146" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
     </row>
     <row r="147" spans="72:72">
       <c r="BT147" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="148" spans="72:72">
       <c r="BT148" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
     <row r="149" spans="72:72">
       <c r="BT149" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
     </row>
     <row r="150" spans="72:72">
       <c r="BT150" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
     </row>
     <row r="151" spans="72:72">
       <c r="BT151" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
     <row r="152" spans="72:72">
       <c r="BT152" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
     </row>
     <row r="153" spans="72:72">
       <c r="BT153" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="154" spans="72:72">
       <c r="BT154" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
     </row>
     <row r="155" spans="72:72">
       <c r="BT155" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
     </row>
     <row r="156" spans="72:72">
       <c r="BT156" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
     </row>
     <row r="157" spans="72:72">
       <c r="BT157" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
     </row>
     <row r="158" spans="72:72">
       <c r="BT158" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
     </row>
     <row r="159" spans="72:72">
       <c r="BT159" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
     </row>
     <row r="160" spans="72:72">
       <c r="BT160" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
     </row>
     <row r="161" spans="72:72">
       <c r="BT161" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
     <row r="162" spans="72:72">
       <c r="BT162" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
     </row>
     <row r="163" spans="72:72">
       <c r="BT163" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="164" spans="72:72">
       <c r="BT164" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
     </row>
     <row r="165" spans="72:72">
       <c r="BT165" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="166" spans="72:72">
       <c r="BT166" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
     </row>
     <row r="167" spans="72:72">
       <c r="BT167" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
     <row r="168" spans="72:72">
       <c r="BT168" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
     </row>
     <row r="169" spans="72:72">
       <c r="BT169" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
     </row>
     <row r="170" spans="72:72">
       <c r="BT170" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
     </row>
     <row r="171" spans="72:72">
       <c r="BT171" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="172" spans="72:72">
       <c r="BT172" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="173" spans="72:72">
       <c r="BT173" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="174" spans="72:72">
       <c r="BT174" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="175" spans="72:72">
       <c r="BT175" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="176" spans="72:72">
       <c r="BT176" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
     </row>
     <row r="177" spans="72:72">
       <c r="BT177" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
     <row r="178" spans="72:72">
       <c r="BT178" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
     </row>
     <row r="179" spans="72:72">
       <c r="BT179" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="180" spans="72:72">
       <c r="BT180" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
     </row>
     <row r="181" spans="72:72">
       <c r="BT181" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="182" spans="72:72">
       <c r="BT182" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
     <row r="183" spans="72:72">
       <c r="BT183" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="184" spans="72:72">
       <c r="BT184" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="185" spans="72:72">
       <c r="BT185" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="186" spans="72:72">
       <c r="BT186" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
     </row>
     <row r="187" spans="72:72">
       <c r="BT187" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="188" spans="72:72">
       <c r="BT188" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="189" spans="72:72">
       <c r="BT189" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
     </row>
     <row r="190" spans="72:72">
       <c r="BT190" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
     </row>
     <row r="191" spans="72:72">
       <c r="BT191" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
     </row>
     <row r="192" spans="72:72">
       <c r="BT192" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
     <row r="193" spans="72:72">
       <c r="BT193" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
     </row>
     <row r="194" spans="72:72">
       <c r="BT194" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
     </row>
     <row r="195" spans="72:72">
       <c r="BT195" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="196" spans="72:72">
       <c r="BT196" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
     </row>
     <row r="197" spans="72:72">
       <c r="BT197" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="198" spans="72:72">
       <c r="BT198" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
     </row>
     <row r="199" spans="72:72">
       <c r="BT199" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
     </row>
     <row r="200" spans="72:72">
       <c r="BT200" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
     </row>
     <row r="201" spans="72:72">
       <c r="BT201" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
     </row>
     <row r="202" spans="72:72">
       <c r="BT202" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
     </row>
     <row r="203" spans="72:72">
       <c r="BT203" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
     </row>
     <row r="204" spans="72:72">
       <c r="BT204" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
     </row>
     <row r="205" spans="72:72">
       <c r="BT205" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
     </row>
     <row r="206" spans="72:72">
       <c r="BT206" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
     </row>
     <row r="207" spans="72:72">
       <c r="BT207" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
     </row>
     <row r="208" spans="72:72">
       <c r="BT208" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
     </row>
     <row r="209" spans="72:72">
       <c r="BT209" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
     </row>
     <row r="210" spans="72:72">
       <c r="BT210" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
     </row>
     <row r="211" spans="72:72">
       <c r="BT211" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
     </row>
     <row r="212" spans="72:72">
       <c r="BT212" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
     </row>
     <row r="213" spans="72:72">
       <c r="BT213" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
     </row>
     <row r="214" spans="72:72">
       <c r="BT214" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
     </row>
     <row r="215" spans="72:72">
       <c r="BT215" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
     </row>
     <row r="216" spans="72:72">
       <c r="BT216" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
     </row>
     <row r="217" spans="72:72">
       <c r="BT217" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
     </row>
     <row r="218" spans="72:72">
       <c r="BT218" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
     </row>
     <row r="219" spans="72:72">
       <c r="BT219" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
     </row>
     <row r="220" spans="72:72">
       <c r="BT220" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
     </row>
     <row r="221" spans="72:72">
       <c r="BT221" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
     </row>
     <row r="222" spans="72:72">
       <c r="BT222" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
     </row>
     <row r="223" spans="72:72">
       <c r="BT223" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
     </row>
     <row r="224" spans="72:72">
       <c r="BT224" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
     </row>
     <row r="225" spans="72:72">
       <c r="BT225" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
     </row>
     <row r="226" spans="72:72">
       <c r="BT226" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
     </row>
     <row r="227" spans="72:72">
       <c r="BT227" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
     </row>
     <row r="228" spans="72:72">
       <c r="BT228" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
     </row>
     <row r="229" spans="72:72">
       <c r="BT229" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
     </row>
     <row r="230" spans="72:72">
       <c r="BT230" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
     </row>
     <row r="231" spans="72:72">
       <c r="BT231" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
     </row>
     <row r="232" spans="72:72">
       <c r="BT232" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
     </row>
     <row r="233" spans="72:72">
       <c r="BT233" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
     </row>
     <row r="234" spans="72:72">
       <c r="BT234" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
     </row>
     <row r="235" spans="72:72">
       <c r="BT235" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
     </row>
     <row r="236" spans="72:72">
       <c r="BT236" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
     </row>
     <row r="237" spans="72:72">
       <c r="BT237" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
     </row>
     <row r="238" spans="72:72">
       <c r="BT238" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
     </row>
     <row r="239" spans="72:72">
       <c r="BT239" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
     </row>
     <row r="240" spans="72:72">
       <c r="BT240" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
     </row>
     <row r="241" spans="72:72">
       <c r="BT241" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
     </row>
     <row r="242" spans="72:72">
       <c r="BT242" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
     </row>
     <row r="243" spans="72:72">
       <c r="BT243" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
     </row>
     <row r="244" spans="72:72">
       <c r="BT244" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
     </row>
     <row r="245" spans="72:72">
       <c r="BT245" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
     </row>
     <row r="246" spans="72:72">
       <c r="BT246" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
     </row>
     <row r="247" spans="72:72">
       <c r="BT247" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
     </row>
     <row r="248" spans="72:72">
       <c r="BT248" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
     </row>
     <row r="249" spans="72:72">
       <c r="BT249" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
     </row>
     <row r="250" spans="72:72">
       <c r="BT250" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
     </row>
     <row r="251" spans="72:72">
       <c r="BT251" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
     </row>
     <row r="252" spans="72:72">
       <c r="BT252" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
     </row>
     <row r="253" spans="72:72">
       <c r="BT253" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
     </row>
     <row r="254" spans="72:72">
       <c r="BT254" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
     </row>
     <row r="255" spans="72:72">
       <c r="BT255" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
     </row>
     <row r="256" spans="72:72">
       <c r="BT256" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
     </row>
     <row r="257" spans="72:72">
       <c r="BT257" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
     </row>
     <row r="258" spans="72:72">
       <c r="BT258" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
     </row>
     <row r="259" spans="72:72">
       <c r="BT259" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
     </row>
     <row r="260" spans="72:72">
       <c r="BT260" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
     </row>
     <row r="261" spans="72:72">
       <c r="BT261" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
     </row>
     <row r="262" spans="72:72">
       <c r="BT262" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
     </row>
     <row r="263" spans="72:72">
       <c r="BT263" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
     </row>
     <row r="264" spans="72:72">
       <c r="BT264" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
     </row>
     <row r="265" spans="72:72">
       <c r="BT265" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
     </row>
     <row r="266" spans="72:72">
       <c r="BT266" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="267" spans="72:72">
       <c r="BT267" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
     </row>
     <row r="268" spans="72:72">
       <c r="BT268" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
     </row>
     <row r="269" spans="72:72">
       <c r="BT269" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
     </row>
     <row r="270" spans="72:72">
       <c r="BT270" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
     </row>
     <row r="271" spans="72:72">
       <c r="BT271" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
     </row>
     <row r="272" spans="72:72">
       <c r="BT272" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
     </row>
     <row r="273" spans="72:72">
       <c r="BT273" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
     </row>
     <row r="274" spans="72:72">
       <c r="BT274" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
     </row>
     <row r="275" spans="72:72">
       <c r="BT275" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
     </row>
     <row r="276" spans="72:72">
       <c r="BT276" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
     </row>
     <row r="277" spans="72:72">
       <c r="BT277" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
     </row>
     <row r="278" spans="72:72">
       <c r="BT278" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
     </row>
     <row r="279" spans="72:72">
       <c r="BT279" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
     </row>
     <row r="280" spans="72:72">
       <c r="BT280" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
     </row>
     <row r="281" spans="72:72">
       <c r="BT281" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
     </row>
     <row r="282" spans="72:72">
       <c r="BT282" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
     </row>
     <row r="283" spans="72:72">
       <c r="BT283" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
     </row>
     <row r="284" spans="72:72">
       <c r="BT284" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
     </row>
     <row r="285" spans="72:72">
       <c r="BT285" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
     </row>
     <row r="286" spans="72:72">
       <c r="BT286" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
     </row>
     <row r="287" spans="72:72">
       <c r="BT287" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
     </row>
     <row r="288" spans="72:72">
       <c r="BT288" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
     </row>
     <row r="289" spans="72:72">
       <c r="BT289" t="s">
-        <v>768</v>
+        <v>770</v>
+      </c>
+    </row>
+    <row r="290" spans="72:72">
+      <c r="BT290" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="291" spans="72:72">
+      <c r="BT291" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="292" spans="72:72">
+      <c r="BT292" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="293" spans="72:72">
+      <c r="BT293" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="294" spans="72:72">
+      <c r="BT294" t="s">
+        <v>775</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000055/metadata_template_ERC000055.xlsx
+++ b/templates/ERC000055/metadata_template_ERC000055.xlsx
@@ -1279,7 +1279,7 @@
     <t>food production characteristics</t>
   </si>
   <si>
-    <t>(Optional) Descriptors of the food production system such as wild caught, free-range, organic, free-range, industrial, dairy, beef. (Units: °C)</t>
+    <t>(Optional) Descriptors of the food production system such as wild caught, free-range, organic, free-range, industrial, dairy, beef.</t>
   </si>
   <si>
     <t>fertilizer administration date</t>
@@ -2908,7 +2908,7 @@
     <t>lot number</t>
   </si>
   <si>
-    <t>(Optional) A distinctive alpha-numeric identification code assigned by the manufacturer or distributor to a specific quantity of manufactured material or product within a batch. synonym: batch number. the submitter should provide lot number of the item followed by the item name for which the lot number was provided. (Units: %)</t>
+    <t>(Optional) A distinctive alpha-numeric identification code assigned by the manufacturer or distributor to a specific quantity of manufactured material or product within a batch. synonym: batch number. the submitter should provide lot number of the item followed by the item name for which the lot number was provided.</t>
   </si>
   <si>
     <t>chemical</t>

--- a/templates/ERC000055/metadata_template_ERC000055.xlsx
+++ b/templates/ERC000055/metadata_template_ERC000055.xlsx
@@ -21,7 +21,7 @@
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
     <definedName name="geographiclocationcountryandorsea">'cv_sample'!$BT$1:$BT$294</definedName>
     <definedName name="historytillage">'cv_sample'!$DK$1:$DK$9</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$89</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1038" uniqueCount="1030">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1039" uniqueCount="1031">
   <si>
     <t>alias</t>
   </si>
@@ -737,6 +737,9 @@
   </si>
   <si>
     <t>UG 100</t>
+  </si>
+  <si>
+    <t>UG 200</t>
   </si>
   <si>
     <t>Vega</t>
@@ -3660,7 +3663,7 @@
         <v>144</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -3704,7 +3707,7 @@
         <v>145</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>
@@ -3731,7 +3734,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N88"/>
+  <dimension ref="G1:N89"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -4468,6 +4471,11 @@
     </row>
     <row r="88" spans="14:14">
       <c r="N88" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="89" spans="14:14">
+      <c r="N89" t="s">
         <v>117</v>
       </c>
     </row>
@@ -4489,27 +4497,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
   </sheetData>
@@ -4529,122 +4537,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
   </sheetData>
@@ -4668,1098 +4676,1098 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="BK1" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="BM1" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="BN1" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="BO1" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="BP1" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="BQ1" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="BS1" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="BT1" s="1" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="BU1" s="1" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="BV1" s="1" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="BW1" s="1" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="BX1" s="1" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="BY1" s="1" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="BZ1" s="1" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="CA1" s="1" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="CB1" s="1" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="CC1" s="1" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="CD1" s="1" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="CE1" s="1" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="CF1" s="1" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="CG1" s="1" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="CH1" s="1" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="CI1" s="1" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="CJ1" s="1" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="CK1" s="1" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="CL1" s="1" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="CM1" s="1" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="CN1" s="1" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="CO1" s="1" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="CP1" s="1" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="CQ1" s="1" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="CR1" s="1" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="CS1" s="1" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="CT1" s="1" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="CU1" s="1" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="CV1" s="1" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="CW1" s="1" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="CX1" s="1" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="CY1" s="1" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="CZ1" s="1" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="DA1" s="1" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="DB1" s="1" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="DC1" s="1" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="DD1" s="1" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="DE1" s="1" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="DF1" s="1" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="DG1" s="1" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="DH1" s="1" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="DI1" s="1" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="DJ1" s="1" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="DK1" s="1" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="DL1" s="1" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="DM1" s="1" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="DN1" s="1" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="DO1" s="1" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="DP1" s="1" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="DQ1" s="1" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="DR1" s="1" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="DS1" s="1" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="DT1" s="1" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="DU1" s="1" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="DV1" s="1" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="DW1" s="1" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="DX1" s="1" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="DY1" s="1" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="DZ1" s="1" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="EA1" s="1" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="EB1" s="1" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="EC1" s="1" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="ED1" s="1" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="EE1" s="1" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="EF1" s="1" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="EG1" s="1" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="EH1" s="1" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="EI1" s="1" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="EJ1" s="1" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="EK1" s="1" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="EL1" s="1" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="EM1" s="1" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="EN1" s="1" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="EO1" s="1" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="EP1" s="1" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="EQ1" s="1" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="ER1" s="1" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="ES1" s="1" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="ET1" s="1" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="EU1" s="1" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="EV1" s="1" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="EW1" s="1" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="EX1" s="1" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="EY1" s="1" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="EZ1" s="1" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="FA1" s="1" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="FB1" s="1" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="FC1" s="1" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="FD1" s="1" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="FE1" s="1" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="FF1" s="1" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="FG1" s="1" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="FH1" s="1" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="FI1" s="1" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="FJ1" s="1" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="FK1" s="1" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="FL1" s="1" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="FM1" s="1" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="FN1" s="1" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="FO1" s="1" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="FP1" s="1" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="FQ1" s="1" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="FR1" s="1" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="FS1" s="1" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="FT1" s="1" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="FU1" s="1" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="FV1" s="1" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="FW1" s="1" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="FX1" s="1" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="FY1" s="1" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="FZ1" s="1" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="GA1" s="1" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="2" spans="1:183" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AP2" s="2" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AQ2" s="2" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AR2" s="2" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AS2" s="2" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AU2" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AV2" s="2" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AW2" s="2" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AX2" s="2" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AY2" s="2" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AZ2" s="2" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="BA2" s="2" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="BB2" s="2" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="BC2" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="BD2" s="2" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="BE2" s="2" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="BF2" s="2" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="BG2" s="2" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="BH2" s="2" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="BI2" s="2" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="BJ2" s="2" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="BK2" s="2" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="BL2" s="2" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="BM2" s="2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="BN2" s="2" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="BO2" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="BP2" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="BQ2" s="2" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="BR2" s="2" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="BS2" s="2" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="BT2" s="2" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="BU2" s="2" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="BV2" s="2" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="BW2" s="2" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="BX2" s="2" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="BY2" s="2" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="BZ2" s="2" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="CA2" s="2" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="CB2" s="2" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="CC2" s="2" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="CD2" s="2" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="CE2" s="2" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="CF2" s="2" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="CG2" s="2" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="CH2" s="2" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="CI2" s="2" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="CJ2" s="2" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="CK2" s="2" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="CL2" s="2" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="CM2" s="2" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="CN2" s="2" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="CO2" s="2" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="CP2" s="2" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="CQ2" s="2" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="CR2" s="2" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="CS2" s="2" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="CT2" s="2" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="CU2" s="2" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="CV2" s="2" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="CW2" s="2" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="CX2" s="2" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="CY2" s="2" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="CZ2" s="2" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="DA2" s="2" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="DB2" s="2" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="DC2" s="2" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="DD2" s="2" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="DE2" s="2" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="DF2" s="2" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="DG2" s="2" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="DH2" s="2" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="DI2" s="2" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="DJ2" s="2" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="DK2" s="2" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="DL2" s="2" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="DM2" s="2" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="DN2" s="2" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="DO2" s="2" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="DP2" s="2" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="DQ2" s="2" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="DR2" s="2" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="DS2" s="2" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="DT2" s="2" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="DU2" s="2" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="DV2" s="2" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="DW2" s="2" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="DX2" s="2" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="DY2" s="2" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="DZ2" s="2" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="EA2" s="2" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="EB2" s="2" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="EC2" s="2" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="ED2" s="2" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="EE2" s="2" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="EF2" s="2" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="EG2" s="2" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="EH2" s="2" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="EI2" s="2" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="EJ2" s="2" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="EK2" s="2" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="EL2" s="2" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="EM2" s="2" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="EN2" s="2" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="EO2" s="2" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="EP2" s="2" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="EQ2" s="2" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="ER2" s="2" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="ES2" s="2" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="ET2" s="2" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="EU2" s="2" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="EV2" s="2" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="EW2" s="2" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="EX2" s="2" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="EY2" s="2" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="EZ2" s="2" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="FA2" s="2" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="FB2" s="2" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="FC2" s="2" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="FD2" s="2" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="FE2" s="2" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="FF2" s="2" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="FG2" s="2" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="FH2" s="2" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="FI2" s="2" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="FJ2" s="2" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="FK2" s="2" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="FL2" s="2" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="FM2" s="2" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="FN2" s="2" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="FO2" s="2" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="FP2" s="2" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="FQ2" s="2" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="FR2" s="2" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="FS2" s="2" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="FT2" s="2" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="FU2" s="2" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="FV2" s="2" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="FW2" s="2" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="FX2" s="2" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="FY2" s="2" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="FZ2" s="2" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="GA2" s="2" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
     </row>
   </sheetData>
@@ -5812,1790 +5820,1790 @@
   <sheetData>
     <row r="1" spans="8:149">
       <c r="H1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="J1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="V1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AB1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AW1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="BA1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="BT1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="CO1" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="CQ1" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="CV1" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="DK1" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="ES1" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
     </row>
     <row r="2" spans="8:149">
       <c r="H2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="J2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="V2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AB2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AW2" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="BA2" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="BT2" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="CO2" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="CQ2" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="CV2" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="DK2" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="ES2" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
     </row>
     <row r="3" spans="8:149">
       <c r="H3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J3" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="V3" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AW3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="BT3" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="CO3" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="CQ3" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="CV3" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="DK3" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="ES3" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
     </row>
     <row r="4" spans="8:149">
       <c r="H4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="J4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="V4" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="BT4" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="CO4" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="CQ4" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="CV4" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="DK4" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="ES4" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
     </row>
     <row r="5" spans="8:149">
       <c r="H5" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="J5" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="V5" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="BT5" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="CO5" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="CQ5" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="CV5" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="DK5" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
     </row>
     <row r="6" spans="8:149">
       <c r="H6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="J6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="V6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="BT6" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="CO6" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="CQ6" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="DK6" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
     </row>
     <row r="7" spans="8:149">
       <c r="H7" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="J7" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="V7" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="BT7" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="DK7" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
     </row>
     <row r="8" spans="8:149">
       <c r="H8" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="V8" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="BT8" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="DK8" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
     </row>
     <row r="9" spans="8:149">
       <c r="H9" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="V9" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="BT9" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="DK9" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
     </row>
     <row r="10" spans="8:149">
       <c r="H10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="V10" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="BT10" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="11" spans="8:149">
       <c r="H11" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="V11" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="BT11" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="12" spans="8:149">
       <c r="H12" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="V12" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="BT12" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="13" spans="8:149">
       <c r="H13" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="V13" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="BT13" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="14" spans="8:149">
       <c r="H14" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="V14" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="BT14" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="15" spans="8:149">
       <c r="H15" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="V15" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="BT15" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="16" spans="8:149">
       <c r="H16" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="V16" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="BT16" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="17" spans="8:72">
       <c r="H17" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="V17" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="BT17" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="18" spans="8:72">
       <c r="H18" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="V18" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="BT18" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="19" spans="8:72">
       <c r="H19" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="V19" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="BT19" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="20" spans="8:72">
       <c r="H20" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="V20" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="BT20" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="21" spans="8:72">
       <c r="H21" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="V21" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="BT21" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="22" spans="8:72">
       <c r="H22" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="V22" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="BT22" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="23" spans="8:72">
       <c r="H23" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="V23" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="BT23" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="24" spans="8:72">
       <c r="H24" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="V24" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="BT24" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="25" spans="8:72">
       <c r="H25" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="V25" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="BT25" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="26" spans="8:72">
       <c r="H26" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="V26" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="BT26" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="27" spans="8:72">
       <c r="H27" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="V27" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="BT27" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="28" spans="8:72">
       <c r="H28" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="V28" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="BT28" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="29" spans="8:72">
       <c r="H29" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="V29" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="BT29" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="30" spans="8:72">
       <c r="H30" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="V30" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="BT30" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="31" spans="8:72">
       <c r="V31" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="BT31" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="32" spans="8:72">
       <c r="V32" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="BT32" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="33" spans="72:72">
       <c r="BT33" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="34" spans="72:72">
       <c r="BT34" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="35" spans="72:72">
       <c r="BT35" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="36" spans="72:72">
       <c r="BT36" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="37" spans="72:72">
       <c r="BT37" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="38" spans="72:72">
       <c r="BT38" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="39" spans="72:72">
       <c r="BT39" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="40" spans="72:72">
       <c r="BT40" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="41" spans="72:72">
       <c r="BT41" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="42" spans="72:72">
       <c r="BT42" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="43" spans="72:72">
       <c r="BT43" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="44" spans="72:72">
       <c r="BT44" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="45" spans="72:72">
       <c r="BT45" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="46" spans="72:72">
       <c r="BT46" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="47" spans="72:72">
       <c r="BT47" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="48" spans="72:72">
       <c r="BT48" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="49" spans="72:72">
       <c r="BT49" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="50" spans="72:72">
       <c r="BT50" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="51" spans="72:72">
       <c r="BT51" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="52" spans="72:72">
       <c r="BT52" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="53" spans="72:72">
       <c r="BT53" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="54" spans="72:72">
       <c r="BT54" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="55" spans="72:72">
       <c r="BT55" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="56" spans="72:72">
       <c r="BT56" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="57" spans="72:72">
       <c r="BT57" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="58" spans="72:72">
       <c r="BT58" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="59" spans="72:72">
       <c r="BT59" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="60" spans="72:72">
       <c r="BT60" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="61" spans="72:72">
       <c r="BT61" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="62" spans="72:72">
       <c r="BT62" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="63" spans="72:72">
       <c r="BT63" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="64" spans="72:72">
       <c r="BT64" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="65" spans="72:72">
       <c r="BT65" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="66" spans="72:72">
       <c r="BT66" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="67" spans="72:72">
       <c r="BT67" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="68" spans="72:72">
       <c r="BT68" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="69" spans="72:72">
       <c r="BT69" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="70" spans="72:72">
       <c r="BT70" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="71" spans="72:72">
       <c r="BT71" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="72" spans="72:72">
       <c r="BT72" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="73" spans="72:72">
       <c r="BT73" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="74" spans="72:72">
       <c r="BT74" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="75" spans="72:72">
       <c r="BT75" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="76" spans="72:72">
       <c r="BT76" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="77" spans="72:72">
       <c r="BT77" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="78" spans="72:72">
       <c r="BT78" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="79" spans="72:72">
       <c r="BT79" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="80" spans="72:72">
       <c r="BT80" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="81" spans="72:72">
       <c r="BT81" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="82" spans="72:72">
       <c r="BT82" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="83" spans="72:72">
       <c r="BT83" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="84" spans="72:72">
       <c r="BT84" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="85" spans="72:72">
       <c r="BT85" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="86" spans="72:72">
       <c r="BT86" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="87" spans="72:72">
       <c r="BT87" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="88" spans="72:72">
       <c r="BT88" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="89" spans="72:72">
       <c r="BT89" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="90" spans="72:72">
       <c r="BT90" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="91" spans="72:72">
       <c r="BT91" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="92" spans="72:72">
       <c r="BT92" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="93" spans="72:72">
       <c r="BT93" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="94" spans="72:72">
       <c r="BT94" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="95" spans="72:72">
       <c r="BT95" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="96" spans="72:72">
       <c r="BT96" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="97" spans="72:72">
       <c r="BT97" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="98" spans="72:72">
       <c r="BT98" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="99" spans="72:72">
       <c r="BT99" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="100" spans="72:72">
       <c r="BT100" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="101" spans="72:72">
       <c r="BT101" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="102" spans="72:72">
       <c r="BT102" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="103" spans="72:72">
       <c r="BT103" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="104" spans="72:72">
       <c r="BT104" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="105" spans="72:72">
       <c r="BT105" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="106" spans="72:72">
       <c r="BT106" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="107" spans="72:72">
       <c r="BT107" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="108" spans="72:72">
       <c r="BT108" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="109" spans="72:72">
       <c r="BT109" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="110" spans="72:72">
       <c r="BT110" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="111" spans="72:72">
       <c r="BT111" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="112" spans="72:72">
       <c r="BT112" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="113" spans="72:72">
       <c r="BT113" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="114" spans="72:72">
       <c r="BT114" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="115" spans="72:72">
       <c r="BT115" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="116" spans="72:72">
       <c r="BT116" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="117" spans="72:72">
       <c r="BT117" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="118" spans="72:72">
       <c r="BT118" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="119" spans="72:72">
       <c r="BT119" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="120" spans="72:72">
       <c r="BT120" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="121" spans="72:72">
       <c r="BT121" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="122" spans="72:72">
       <c r="BT122" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="123" spans="72:72">
       <c r="BT123" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="124" spans="72:72">
       <c r="BT124" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="125" spans="72:72">
       <c r="BT125" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="126" spans="72:72">
       <c r="BT126" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="127" spans="72:72">
       <c r="BT127" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="128" spans="72:72">
       <c r="BT128" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="129" spans="72:72">
       <c r="BT129" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="130" spans="72:72">
       <c r="BT130" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="131" spans="72:72">
       <c r="BT131" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="132" spans="72:72">
       <c r="BT132" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="133" spans="72:72">
       <c r="BT133" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="134" spans="72:72">
       <c r="BT134" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="135" spans="72:72">
       <c r="BT135" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="136" spans="72:72">
       <c r="BT136" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="137" spans="72:72">
       <c r="BT137" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="138" spans="72:72">
       <c r="BT138" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="139" spans="72:72">
       <c r="BT139" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="140" spans="72:72">
       <c r="BT140" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="141" spans="72:72">
       <c r="BT141" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="142" spans="72:72">
       <c r="BT142" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="143" spans="72:72">
       <c r="BT143" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="144" spans="72:72">
       <c r="BT144" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="145" spans="72:72">
       <c r="BT145" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="146" spans="72:72">
       <c r="BT146" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="147" spans="72:72">
       <c r="BT147" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="148" spans="72:72">
       <c r="BT148" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="149" spans="72:72">
       <c r="BT149" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="150" spans="72:72">
       <c r="BT150" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="151" spans="72:72">
       <c r="BT151" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="152" spans="72:72">
       <c r="BT152" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="153" spans="72:72">
       <c r="BT153" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="154" spans="72:72">
       <c r="BT154" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="155" spans="72:72">
       <c r="BT155" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="156" spans="72:72">
       <c r="BT156" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="157" spans="72:72">
       <c r="BT157" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
     </row>
     <row r="158" spans="72:72">
       <c r="BT158" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="159" spans="72:72">
       <c r="BT159" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="160" spans="72:72">
       <c r="BT160" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
     </row>
     <row r="161" spans="72:72">
       <c r="BT161" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="162" spans="72:72">
       <c r="BT162" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="163" spans="72:72">
       <c r="BT163" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="164" spans="72:72">
       <c r="BT164" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="165" spans="72:72">
       <c r="BT165" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="166" spans="72:72">
       <c r="BT166" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="167" spans="72:72">
       <c r="BT167" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="168" spans="72:72">
       <c r="BT168" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="169" spans="72:72">
       <c r="BT169" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="170" spans="72:72">
       <c r="BT170" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="171" spans="72:72">
       <c r="BT171" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="172" spans="72:72">
       <c r="BT172" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="173" spans="72:72">
       <c r="BT173" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="174" spans="72:72">
       <c r="BT174" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="175" spans="72:72">
       <c r="BT175" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="176" spans="72:72">
       <c r="BT176" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="177" spans="72:72">
       <c r="BT177" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="178" spans="72:72">
       <c r="BT178" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="179" spans="72:72">
       <c r="BT179" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="180" spans="72:72">
       <c r="BT180" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="181" spans="72:72">
       <c r="BT181" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="182" spans="72:72">
       <c r="BT182" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="183" spans="72:72">
       <c r="BT183" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="184" spans="72:72">
       <c r="BT184" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="185" spans="72:72">
       <c r="BT185" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="186" spans="72:72">
       <c r="BT186" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="187" spans="72:72">
       <c r="BT187" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="188" spans="72:72">
       <c r="BT188" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
     <row r="189" spans="72:72">
       <c r="BT189" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="190" spans="72:72">
       <c r="BT190" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="191" spans="72:72">
       <c r="BT191" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="192" spans="72:72">
       <c r="BT192" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="193" spans="72:72">
       <c r="BT193" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="194" spans="72:72">
       <c r="BT194" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="195" spans="72:72">
       <c r="BT195" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="196" spans="72:72">
       <c r="BT196" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="197" spans="72:72">
       <c r="BT197" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="198" spans="72:72">
       <c r="BT198" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="199" spans="72:72">
       <c r="BT199" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="200" spans="72:72">
       <c r="BT200" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="201" spans="72:72">
       <c r="BT201" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="202" spans="72:72">
       <c r="BT202" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="203" spans="72:72">
       <c r="BT203" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
     </row>
     <row r="204" spans="72:72">
       <c r="BT204" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
     </row>
     <row r="205" spans="72:72">
       <c r="BT205" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="206" spans="72:72">
       <c r="BT206" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="207" spans="72:72">
       <c r="BT207" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
     </row>
     <row r="208" spans="72:72">
       <c r="BT208" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="209" spans="72:72">
       <c r="BT209" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
     </row>
     <row r="210" spans="72:72">
       <c r="BT210" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
     </row>
     <row r="211" spans="72:72">
       <c r="BT211" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
     </row>
     <row r="212" spans="72:72">
       <c r="BT212" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="213" spans="72:72">
       <c r="BT213" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="214" spans="72:72">
       <c r="BT214" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
     </row>
     <row r="215" spans="72:72">
       <c r="BT215" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
     </row>
     <row r="216" spans="72:72">
       <c r="BT216" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="217" spans="72:72">
       <c r="BT217" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
     </row>
     <row r="218" spans="72:72">
       <c r="BT218" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
     <row r="219" spans="72:72">
       <c r="BT219" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
     </row>
     <row r="220" spans="72:72">
       <c r="BT220" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
     <row r="221" spans="72:72">
       <c r="BT221" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="222" spans="72:72">
       <c r="BT222" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="223" spans="72:72">
       <c r="BT223" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="224" spans="72:72">
       <c r="BT224" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
     </row>
     <row r="225" spans="72:72">
       <c r="BT225" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
     </row>
     <row r="226" spans="72:72">
       <c r="BT226" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
     </row>
     <row r="227" spans="72:72">
       <c r="BT227" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
     </row>
     <row r="228" spans="72:72">
       <c r="BT228" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
     </row>
     <row r="229" spans="72:72">
       <c r="BT229" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
     </row>
     <row r="230" spans="72:72">
       <c r="BT230" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
     </row>
     <row r="231" spans="72:72">
       <c r="BT231" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
     </row>
     <row r="232" spans="72:72">
       <c r="BT232" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
     </row>
     <row r="233" spans="72:72">
       <c r="BT233" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
     </row>
     <row r="234" spans="72:72">
       <c r="BT234" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
     </row>
     <row r="235" spans="72:72">
       <c r="BT235" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
     </row>
     <row r="236" spans="72:72">
       <c r="BT236" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
     </row>
     <row r="237" spans="72:72">
       <c r="BT237" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
     </row>
     <row r="238" spans="72:72">
       <c r="BT238" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="239" spans="72:72">
       <c r="BT239" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
     </row>
     <row r="240" spans="72:72">
       <c r="BT240" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
     </row>
     <row r="241" spans="72:72">
       <c r="BT241" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
     </row>
     <row r="242" spans="72:72">
       <c r="BT242" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
     </row>
     <row r="243" spans="72:72">
       <c r="BT243" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
     </row>
     <row r="244" spans="72:72">
       <c r="BT244" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
     </row>
     <row r="245" spans="72:72">
       <c r="BT245" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
     </row>
     <row r="246" spans="72:72">
       <c r="BT246" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
     </row>
     <row r="247" spans="72:72">
       <c r="BT247" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
     </row>
     <row r="248" spans="72:72">
       <c r="BT248" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="249" spans="72:72">
       <c r="BT249" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
     </row>
     <row r="250" spans="72:72">
       <c r="BT250" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
     </row>
     <row r="251" spans="72:72">
       <c r="BT251" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
     </row>
     <row r="252" spans="72:72">
       <c r="BT252" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
     </row>
     <row r="253" spans="72:72">
       <c r="BT253" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
     </row>
     <row r="254" spans="72:72">
       <c r="BT254" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
     </row>
     <row r="255" spans="72:72">
       <c r="BT255" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
     </row>
     <row r="256" spans="72:72">
       <c r="BT256" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
     </row>
     <row r="257" spans="72:72">
       <c r="BT257" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
     </row>
     <row r="258" spans="72:72">
       <c r="BT258" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
     </row>
     <row r="259" spans="72:72">
       <c r="BT259" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
     </row>
     <row r="260" spans="72:72">
       <c r="BT260" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="261" spans="72:72">
       <c r="BT261" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="262" spans="72:72">
       <c r="BT262" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="263" spans="72:72">
       <c r="BT263" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="264" spans="72:72">
       <c r="BT264" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="265" spans="72:72">
       <c r="BT265" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="266" spans="72:72">
       <c r="BT266" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="267" spans="72:72">
       <c r="BT267" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="268" spans="72:72">
       <c r="BT268" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
     </row>
     <row r="269" spans="72:72">
       <c r="BT269" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
     </row>
     <row r="270" spans="72:72">
       <c r="BT270" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
     </row>
     <row r="271" spans="72:72">
       <c r="BT271" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
     </row>
     <row r="272" spans="72:72">
       <c r="BT272" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
     </row>
     <row r="273" spans="72:72">
       <c r="BT273" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
     </row>
     <row r="274" spans="72:72">
       <c r="BT274" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
     </row>
     <row r="275" spans="72:72">
       <c r="BT275" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
     </row>
     <row r="276" spans="72:72">
       <c r="BT276" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
     </row>
     <row r="277" spans="72:72">
       <c r="BT277" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
     </row>
     <row r="278" spans="72:72">
       <c r="BT278" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
     </row>
     <row r="279" spans="72:72">
       <c r="BT279" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
     </row>
     <row r="280" spans="72:72">
       <c r="BT280" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
     </row>
     <row r="281" spans="72:72">
       <c r="BT281" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
     </row>
     <row r="282" spans="72:72">
       <c r="BT282" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
     </row>
     <row r="283" spans="72:72">
       <c r="BT283" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
     </row>
     <row r="284" spans="72:72">
       <c r="BT284" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
     </row>
     <row r="285" spans="72:72">
       <c r="BT285" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
     </row>
     <row r="286" spans="72:72">
       <c r="BT286" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
     </row>
     <row r="287" spans="72:72">
       <c r="BT287" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
     </row>
     <row r="288" spans="72:72">
       <c r="BT288" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
     </row>
     <row r="289" spans="72:72">
       <c r="BT289" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
     </row>
     <row r="290" spans="72:72">
       <c r="BT290" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
     </row>
     <row r="291" spans="72:72">
       <c r="BT291" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
     </row>
     <row r="292" spans="72:72">
       <c r="BT292" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
     </row>
     <row r="293" spans="72:72">
       <c r="BT293" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
     </row>
     <row r="294" spans="72:72">
       <c r="BT294" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
     </row>
   </sheetData>
